--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Anton Lundberg, Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY168"/>
+  <dimension ref="A1:AY170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anton Lundberg, Alva Dahlqvist Cederstrand</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -6120,48 +6120,51 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135356208</v>
+        <v>135420258</v>
       </c>
       <c r="B51" t="n">
-        <v>92320</v>
+        <v>92827</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2063</v>
+        <v>2037</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Kristallskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Metulodontia nivea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P. Karst.) Parmasto</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>598597</v>
+        <v>598637</v>
       </c>
       <c r="R51" t="n">
-        <v>7330356</v>
+        <v>7330348</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6190,7 +6193,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6200,7 +6203,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På grov granlåga av hög kvalitet, i sent nedbrytningsstadie. Högproduktiv, kalkpåverkad högörtsgranskog ovan fjällnäragränsen. Mikroskoperad av Johan Råghall, som fann båda typer av cystidier. Kollekt finns sparat. Uppseendeväckande utseende om man tittat på en del lågor, bl.a. för att det var rätt tjockt, väl avgränsat från substratet, och hade en tydlig grynig ytstruktur med en liten bård mot kanten av fruktkroppen. Hela fruktkroppen var rätt stor, uppskattningsvis ca 50x30cm</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6209,18 +6217,52 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AT51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6231,7 +6273,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135356239</v>
+        <v>135356208</v>
       </c>
       <c r="B52" t="n">
         <v>92320</v>
@@ -6266,10 +6308,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>598515</v>
+        <v>598597</v>
       </c>
       <c r="R52" t="n">
-        <v>7330567</v>
+        <v>7330356</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6301,7 +6343,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6311,7 +6353,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6342,48 +6384,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135357125</v>
+        <v>135356239</v>
       </c>
       <c r="B53" t="n">
-        <v>80489</v>
+        <v>92320</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>2063</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>598552</v>
+        <v>598515</v>
       </c>
       <c r="R53" t="n">
-        <v>7330359</v>
+        <v>7330567</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6412,7 +6454,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6422,7 +6464,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6437,12 +6479,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6453,32 +6495,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135357118</v>
+        <v>135357125</v>
       </c>
       <c r="B54" t="n">
-        <v>96410</v>
+        <v>80489</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2812</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6488,10 +6530,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>598517</v>
+        <v>598552</v>
       </c>
       <c r="R54" t="n">
-        <v>7330356</v>
+        <v>7330359</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6523,7 +6565,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6533,7 +6575,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6564,7 +6606,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135357124</v>
+        <v>135357118</v>
       </c>
       <c r="B55" t="n">
         <v>96410</v>
@@ -6599,10 +6641,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>598552</v>
+        <v>598517</v>
       </c>
       <c r="R55" t="n">
-        <v>7330359</v>
+        <v>7330356</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6634,7 +6676,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6644,7 +6686,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6675,7 +6717,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135357203</v>
+        <v>135357124</v>
       </c>
       <c r="B56" t="n">
         <v>96410</v>
@@ -6710,10 +6752,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>598553</v>
+        <v>598552</v>
       </c>
       <c r="R56" t="n">
-        <v>7330578</v>
+        <v>7330359</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6745,7 +6787,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6755,7 +6797,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6786,7 +6828,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135357207</v>
+        <v>135357203</v>
       </c>
       <c r="B57" t="n">
         <v>96410</v>
@@ -6821,10 +6863,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>598521</v>
+        <v>598553</v>
       </c>
       <c r="R57" t="n">
-        <v>7330581</v>
+        <v>7330578</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6856,7 +6898,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6866,7 +6908,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6897,7 +6939,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135357208</v>
+        <v>135357207</v>
       </c>
       <c r="B58" t="n">
         <v>96410</v>
@@ -6932,10 +6974,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>598512</v>
+        <v>598521</v>
       </c>
       <c r="R58" t="n">
-        <v>7330582</v>
+        <v>7330581</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6967,7 +7009,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6977,7 +7019,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7008,7 +7050,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135382719</v>
+        <v>135357208</v>
       </c>
       <c r="B59" t="n">
         <v>96410</v>
@@ -7039,14 +7081,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>598507</v>
+        <v>598512</v>
       </c>
       <c r="R59" t="n">
-        <v>7330626</v>
+        <v>7330582</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7073,22 +7115,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7119,48 +7161,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135358275</v>
+        <v>135382719</v>
       </c>
       <c r="B60" t="n">
-        <v>87625</v>
+        <v>96410</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3639</v>
+        <v>2812</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rutspindling</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius ionophyllus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>598533</v>
+        <v>598507</v>
       </c>
       <c r="R60" t="n">
-        <v>7330307</v>
+        <v>7330626</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7187,43 +7226,42 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF60" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7234,48 +7272,51 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135356210</v>
+        <v>135358275</v>
       </c>
       <c r="B61" t="n">
-        <v>92370</v>
+        <v>87625</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4217</v>
+        <v>3639</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rutspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Cortinarius ionophyllus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>598603</v>
+        <v>598533</v>
       </c>
       <c r="R61" t="n">
-        <v>7330411</v>
+        <v>7330307</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7304,7 +7345,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7314,27 +7355,28 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7345,7 +7387,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135356372</v>
+        <v>135356210</v>
       </c>
       <c r="B62" t="n">
         <v>92370</v>
@@ -7376,17 +7418,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>598544</v>
+        <v>598603</v>
       </c>
       <c r="R62" t="n">
-        <v>7330366</v>
+        <v>7330411</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7415,7 +7457,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7425,7 +7467,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7440,12 +7482,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7456,10 +7498,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135353513</v>
+        <v>135356372</v>
       </c>
       <c r="B63" t="n">
-        <v>91937</v>
+        <v>92370</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7467,37 +7509,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>598811</v>
+        <v>598544</v>
       </c>
       <c r="R63" t="n">
-        <v>7330371</v>
+        <v>7330366</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7526,7 +7568,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7536,7 +7578,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7551,12 +7593,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7567,32 +7609,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135353495</v>
+        <v>135353513</v>
       </c>
       <c r="B64" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7602,10 +7644,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>598630</v>
+        <v>598811</v>
       </c>
       <c r="R64" t="n">
-        <v>7330381</v>
+        <v>7330371</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7637,7 +7679,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7647,7 +7689,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7678,7 +7720,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135353515</v>
+        <v>135353495</v>
       </c>
       <c r="B65" t="n">
         <v>79373</v>
@@ -7713,10 +7755,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>598809</v>
+        <v>598630</v>
       </c>
       <c r="R65" t="n">
-        <v>7330378</v>
+        <v>7330381</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7748,7 +7790,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7758,7 +7800,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7789,7 +7831,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135356240</v>
+        <v>135353515</v>
       </c>
       <c r="B66" t="n">
         <v>79373</v>
@@ -7820,14 +7862,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>598519</v>
+        <v>598809</v>
       </c>
       <c r="R66" t="n">
-        <v>7330561</v>
+        <v>7330378</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7859,7 +7901,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7869,7 +7911,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7884,12 +7926,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7900,7 +7942,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135356837</v>
+        <v>135356240</v>
       </c>
       <c r="B67" t="n">
         <v>79373</v>
@@ -7931,17 +7973,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>598555</v>
+        <v>598519</v>
       </c>
       <c r="R67" t="n">
-        <v>7330375</v>
+        <v>7330561</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7970,7 +8012,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7980,7 +8022,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7995,12 +8037,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8011,7 +8053,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135382466</v>
+        <v>135356837</v>
       </c>
       <c r="B68" t="n">
         <v>79373</v>
@@ -8042,17 +8084,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>598537</v>
+        <v>598555</v>
       </c>
       <c r="R68" t="n">
-        <v>7330657</v>
+        <v>7330375</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8076,22 +8118,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8106,12 +8148,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8122,7 +8164,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135384252</v>
+        <v>135382466</v>
       </c>
       <c r="B69" t="n">
         <v>79373</v>
@@ -8153,17 +8195,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>598474</v>
+        <v>598537</v>
       </c>
       <c r="R69" t="n">
-        <v>7330641</v>
+        <v>7330657</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8192,7 +8234,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8202,7 +8244,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8217,12 +8259,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8233,48 +8275,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135353509</v>
+        <v>135384252</v>
       </c>
       <c r="B70" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>598768</v>
+        <v>598474</v>
       </c>
       <c r="R70" t="n">
-        <v>7330331</v>
+        <v>7330641</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8298,22 +8340,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8328,12 +8370,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8344,7 +8386,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135356841</v>
+        <v>135353509</v>
       </c>
       <c r="B71" t="n">
         <v>83358</v>
@@ -8375,14 +8417,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>598580</v>
+        <v>598768</v>
       </c>
       <c r="R71" t="n">
-        <v>7330406</v>
+        <v>7330331</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8414,7 +8456,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8424,7 +8466,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8439,12 +8481,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8455,48 +8497,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135357126</v>
+        <v>135356841</v>
       </c>
       <c r="B72" t="n">
-        <v>80493</v>
+        <v>83358</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>598552</v>
+        <v>598580</v>
       </c>
       <c r="R72" t="n">
-        <v>7330359</v>
+        <v>7330406</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8525,7 +8567,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8535,7 +8577,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8550,12 +8592,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8566,53 +8608,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135353488</v>
+        <v>135357126</v>
       </c>
       <c r="B73" t="n">
-        <v>57975</v>
+        <v>80493</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>598564</v>
+        <v>598552</v>
       </c>
       <c r="R73" t="n">
-        <v>7330345</v>
+        <v>7330359</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8641,7 +8678,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8651,7 +8688,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8666,12 +8703,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8682,7 +8719,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135353503</v>
+        <v>135353488</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -8713,7 +8750,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8722,10 +8759,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>598672</v>
+        <v>598564</v>
       </c>
       <c r="R74" t="n">
-        <v>7330311</v>
+        <v>7330345</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8757,7 +8794,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8767,7 +8804,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8798,7 +8835,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135356216</v>
+        <v>135353503</v>
       </c>
       <c r="B75" t="n">
         <v>57975</v>
@@ -8827,19 +8864,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>598747</v>
+        <v>598672</v>
       </c>
       <c r="R75" t="n">
-        <v>7330309</v>
+        <v>7330311</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8868,7 +8910,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8878,12 +8920,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Gamla och nya ringhack</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8898,12 +8935,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8914,7 +8951,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135356376</v>
+        <v>135356216</v>
       </c>
       <c r="B76" t="n">
         <v>57975</v>
@@ -8943,27 +8980,19 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>598614</v>
+        <v>598747</v>
       </c>
       <c r="R76" t="n">
-        <v>7330356</v>
+        <v>7330309</v>
       </c>
       <c r="S76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8992,7 +9021,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9002,19 +9031,19 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Gamla och nya ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
@@ -9022,12 +9051,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -9038,7 +9067,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135356380</v>
+        <v>135356376</v>
       </c>
       <c r="B77" t="n">
         <v>57975</v>
@@ -9081,13 +9110,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>598877</v>
+        <v>598614</v>
       </c>
       <c r="R77" t="n">
-        <v>7330349</v>
+        <v>7330356</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9116,7 +9145,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9126,19 +9155,19 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG77" t="b">
         <v>0</v>
@@ -9151,7 +9180,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9162,7 +9191,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135357127</v>
+        <v>135356380</v>
       </c>
       <c r="B78" t="n">
         <v>57975</v>
@@ -9191,19 +9220,27 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>598569</v>
+        <v>598877</v>
       </c>
       <c r="R78" t="n">
-        <v>7330352</v>
+        <v>7330349</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9232,7 +9269,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9242,12 +9279,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9262,12 +9299,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9278,7 +9315,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135358283</v>
+        <v>135357127</v>
       </c>
       <c r="B79" t="n">
         <v>57975</v>
@@ -9309,17 +9346,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>598609</v>
+        <v>598569</v>
       </c>
       <c r="R79" t="n">
-        <v>7330298</v>
+        <v>7330352</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9348,7 +9385,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9358,7 +9395,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -9378,12 +9415,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9394,7 +9431,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135382716</v>
+        <v>135358283</v>
       </c>
       <c r="B80" t="n">
         <v>57975</v>
@@ -9423,27 +9460,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>598482</v>
+        <v>598609</v>
       </c>
       <c r="R80" t="n">
-        <v>7330489</v>
+        <v>7330298</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9467,27 +9496,27 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9502,12 +9531,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9518,7 +9547,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135382779</v>
+        <v>135382716</v>
       </c>
       <c r="B81" t="n">
         <v>57975</v>
@@ -9551,7 +9580,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -9561,10 +9590,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>598462</v>
+        <v>598482</v>
       </c>
       <c r="R81" t="n">
-        <v>7330447</v>
+        <v>7330489</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9596,7 +9625,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9606,12 +9635,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9642,7 +9671,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135384126</v>
+        <v>135382779</v>
       </c>
       <c r="B82" t="n">
         <v>57975</v>
@@ -9685,10 +9714,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>598485</v>
+        <v>598462</v>
       </c>
       <c r="R82" t="n">
-        <v>7330673</v>
+        <v>7330447</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9720,7 +9749,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9730,19 +9759,19 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="b">
         <v>0</v>
@@ -9750,12 +9779,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9766,10 +9795,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135357215</v>
+        <v>135384126</v>
       </c>
       <c r="B83" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9777,21 +9806,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9799,20 +9828,20 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>598501</v>
+        <v>598485</v>
       </c>
       <c r="R83" t="n">
-        <v>7330475</v>
+        <v>7330673</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9839,34 +9868,34 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG83" t="b">
         <v>0</v>
@@ -9874,12 +9903,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9890,7 +9919,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135382711</v>
+        <v>135357215</v>
       </c>
       <c r="B84" t="n">
         <v>58136</v>
@@ -9929,14 +9958,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>598464</v>
+        <v>598501</v>
       </c>
       <c r="R84" t="n">
-        <v>7330416</v>
+        <v>7330475</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9963,22 +9992,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10009,7 +10043,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135385939</v>
+        <v>135382711</v>
       </c>
       <c r="B85" t="n">
         <v>58136</v>
@@ -10038,16 +10072,24 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>598491</v>
+        <v>598464</v>
       </c>
       <c r="R85" t="n">
-        <v>7330361</v>
+        <v>7330416</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10079,7 +10121,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10089,7 +10131,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10104,12 +10146,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -10120,48 +10162,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135382469</v>
+        <v>135385939</v>
       </c>
       <c r="B86" t="n">
-        <v>99112</v>
+        <v>58136</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>598453</v>
+        <v>598491</v>
       </c>
       <c r="R86" t="n">
-        <v>7330444</v>
+        <v>7330361</v>
       </c>
       <c r="S86" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10190,7 +10232,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10200,7 +10242,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10215,12 +10257,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10231,7 +10273,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135384124</v>
+        <v>135382469</v>
       </c>
       <c r="B87" t="n">
         <v>99112</v>
@@ -10262,17 +10304,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>598499</v>
+        <v>598453</v>
       </c>
       <c r="R87" t="n">
-        <v>7330637</v>
+        <v>7330444</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10301,7 +10343,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10311,7 +10353,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10326,12 +10368,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10342,7 +10384,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135384162</v>
+        <v>135384124</v>
       </c>
       <c r="B88" t="n">
         <v>99112</v>
@@ -10377,10 +10419,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>598449</v>
+        <v>598499</v>
       </c>
       <c r="R88" t="n">
-        <v>7330355</v>
+        <v>7330637</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10412,7 +10454,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10422,7 +10464,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10453,10 +10495,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>94770073</v>
+        <v>135384162</v>
       </c>
       <c r="B89" t="n">
-        <v>99120</v>
+        <v>99112</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10464,43 +10506,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Laisan, Arjeplog, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>598453</v>
+        <v>598449</v>
       </c>
       <c r="R89" t="n">
-        <v>7330315</v>
+        <v>7330355</v>
       </c>
       <c r="S89" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10524,12 +10560,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10544,22 +10590,26 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Thomas Strid, Tiina Laantee</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135356843</v>
+        <v>94770073</v>
       </c>
       <c r="B90" t="n">
-        <v>99099</v>
+        <v>99120</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10567,37 +10617,43 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Laisan, Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>598607</v>
+        <v>598453</v>
       </c>
       <c r="R90" t="n">
-        <v>7330382</v>
+        <v>7330315</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10621,22 +10677,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10651,26 +10697,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Thomas Strid, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135353481</v>
+        <v>135356843</v>
       </c>
       <c r="B91" t="n">
-        <v>109924</v>
+        <v>99099</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10678,34 +10720,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221184</v>
+        <v>220093</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>598529</v>
+        <v>598607</v>
       </c>
       <c r="R91" t="n">
-        <v>7330341</v>
+        <v>7330382</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10737,7 +10779,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10747,7 +10789,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10762,12 +10804,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10778,7 +10820,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135353512</v>
+        <v>135353481</v>
       </c>
       <c r="B92" t="n">
         <v>109924</v>
@@ -10813,10 +10855,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>598793</v>
+        <v>598529</v>
       </c>
       <c r="R92" t="n">
-        <v>7330350</v>
+        <v>7330341</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10848,7 +10890,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10858,7 +10900,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10889,7 +10931,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135356205</v>
+        <v>135353512</v>
       </c>
       <c r="B93" t="n">
         <v>109924</v>
@@ -10920,14 +10962,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>598518</v>
+        <v>598793</v>
       </c>
       <c r="R93" t="n">
-        <v>7330341</v>
+        <v>7330350</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10959,7 +11001,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10969,7 +11011,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10984,12 +11026,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -11000,7 +11042,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135356241</v>
+        <v>135356205</v>
       </c>
       <c r="B94" t="n">
         <v>109924</v>
@@ -11035,10 +11077,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>598490</v>
+        <v>598518</v>
       </c>
       <c r="R94" t="n">
-        <v>7330565</v>
+        <v>7330341</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11070,7 +11112,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11080,7 +11122,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11111,7 +11153,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135357137</v>
+        <v>135356241</v>
       </c>
       <c r="B95" t="n">
         <v>109924</v>
@@ -11142,17 +11184,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>598751</v>
+        <v>598490</v>
       </c>
       <c r="R95" t="n">
-        <v>7330316</v>
+        <v>7330565</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11181,7 +11223,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11191,7 +11233,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11206,12 +11248,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11222,7 +11264,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135357141</v>
+        <v>135357137</v>
       </c>
       <c r="B96" t="n">
         <v>109924</v>
@@ -11257,10 +11299,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>598770</v>
+        <v>598751</v>
       </c>
       <c r="R96" t="n">
-        <v>7330338</v>
+        <v>7330316</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11292,7 +11334,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11302,7 +11344,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11333,7 +11375,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135357201</v>
+        <v>135357141</v>
       </c>
       <c r="B97" t="n">
         <v>109924</v>
@@ -11368,10 +11410,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>598553</v>
+        <v>598770</v>
       </c>
       <c r="R97" t="n">
-        <v>7330578</v>
+        <v>7330338</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11403,7 +11445,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11413,7 +11455,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11444,7 +11486,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135357211</v>
+        <v>135357201</v>
       </c>
       <c r="B98" t="n">
         <v>109924</v>
@@ -11479,10 +11521,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>598501</v>
+        <v>598553</v>
       </c>
       <c r="R98" t="n">
-        <v>7330515</v>
+        <v>7330578</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11514,7 +11556,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11524,7 +11566,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11555,7 +11597,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135357212</v>
+        <v>135357211</v>
       </c>
       <c r="B99" t="n">
         <v>109924</v>
@@ -11590,10 +11632,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>598498</v>
+        <v>598501</v>
       </c>
       <c r="R99" t="n">
-        <v>7330492</v>
+        <v>7330515</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11625,7 +11667,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11635,7 +11677,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11666,7 +11708,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135358269</v>
+        <v>135357212</v>
       </c>
       <c r="B100" t="n">
         <v>109924</v>
@@ -11697,17 +11739,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>598578</v>
+        <v>598498</v>
       </c>
       <c r="R100" t="n">
-        <v>7330329</v>
+        <v>7330492</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11736,7 +11778,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11746,7 +11788,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11761,12 +11803,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11777,7 +11819,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135358276</v>
+        <v>135358269</v>
       </c>
       <c r="B101" t="n">
         <v>109924</v>
@@ -11812,10 +11854,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>598542</v>
+        <v>598578</v>
       </c>
       <c r="R101" t="n">
-        <v>7330305</v>
+        <v>7330329</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11847,7 +11889,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11857,7 +11899,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11888,7 +11930,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135358292</v>
+        <v>135358276</v>
       </c>
       <c r="B102" t="n">
         <v>109924</v>
@@ -11923,10 +11965,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>598827</v>
+        <v>598542</v>
       </c>
       <c r="R102" t="n">
-        <v>7330278</v>
+        <v>7330305</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11958,7 +12000,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11968,7 +12010,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11999,7 +12041,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135358342</v>
+        <v>135358292</v>
       </c>
       <c r="B103" t="n">
         <v>109924</v>
@@ -12034,10 +12076,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>598546</v>
+        <v>598827</v>
       </c>
       <c r="R103" t="n">
-        <v>7330653</v>
+        <v>7330278</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12069,7 +12111,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12079,7 +12121,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12110,7 +12152,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135382720</v>
+        <v>135358342</v>
       </c>
       <c r="B104" t="n">
         <v>109924</v>
@@ -12141,17 +12183,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>598507</v>
+        <v>598546</v>
       </c>
       <c r="R104" t="n">
-        <v>7330626</v>
+        <v>7330653</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12175,22 +12217,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12205,12 +12247,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12221,7 +12263,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135382723</v>
+        <v>135382720</v>
       </c>
       <c r="B105" t="n">
         <v>109924</v>
@@ -12256,10 +12298,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>598467</v>
+        <v>598507</v>
       </c>
       <c r="R105" t="n">
-        <v>7330649</v>
+        <v>7330626</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12291,7 +12333,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12301,7 +12343,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12332,10 +12374,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135353491</v>
+        <v>135382723</v>
       </c>
       <c r="B106" t="n">
-        <v>106309</v>
+        <v>109924</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12343,16 +12385,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221725</v>
+        <v>221184</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -12363,17 +12405,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>598592</v>
+        <v>598467</v>
       </c>
       <c r="R106" t="n">
-        <v>7330348</v>
+        <v>7330649</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12397,22 +12439,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12427,12 +12469,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12443,7 +12485,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135356209</v>
+        <v>135353491</v>
       </c>
       <c r="B107" t="n">
         <v>106309</v>
@@ -12474,14 +12516,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>598597</v>
+        <v>598592</v>
       </c>
       <c r="R107" t="n">
-        <v>7330383</v>
+        <v>7330348</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12513,7 +12555,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12523,7 +12565,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12538,12 +12580,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -12554,7 +12596,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135356218</v>
+        <v>135356209</v>
       </c>
       <c r="B108" t="n">
         <v>106309</v>
@@ -12589,10 +12631,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>598785</v>
+        <v>598597</v>
       </c>
       <c r="R108" t="n">
-        <v>7330366</v>
+        <v>7330383</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12624,7 +12666,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12634,7 +12676,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12665,7 +12707,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135356839</v>
+        <v>135356218</v>
       </c>
       <c r="B109" t="n">
         <v>106309</v>
@@ -12696,17 +12738,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>598557</v>
+        <v>598785</v>
       </c>
       <c r="R109" t="n">
-        <v>7330411</v>
+        <v>7330366</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12735,7 +12777,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12745,7 +12787,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12760,12 +12802,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12776,7 +12818,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135356886</v>
+        <v>135356839</v>
       </c>
       <c r="B110" t="n">
         <v>106309</v>
@@ -12811,13 +12853,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>598518</v>
+        <v>598557</v>
       </c>
       <c r="R110" t="n">
-        <v>7330476</v>
+        <v>7330411</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12846,7 +12888,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12856,7 +12898,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12887,7 +12929,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135358270</v>
+        <v>135356886</v>
       </c>
       <c r="B111" t="n">
         <v>106309</v>
@@ -12918,17 +12960,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>598568</v>
+        <v>598518</v>
       </c>
       <c r="R111" t="n">
-        <v>7330339</v>
+        <v>7330476</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12957,7 +12999,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12967,7 +13009,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12982,12 +13024,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12998,7 +13040,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135358287</v>
+        <v>135358270</v>
       </c>
       <c r="B112" t="n">
         <v>106309</v>
@@ -13033,10 +13075,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>598754</v>
+        <v>598568</v>
       </c>
       <c r="R112" t="n">
-        <v>7330326</v>
+        <v>7330339</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13068,7 +13110,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13078,7 +13120,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13109,10 +13151,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135356206</v>
+        <v>135358287</v>
       </c>
       <c r="B113" t="n">
-        <v>98060</v>
+        <v>106309</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13120,37 +13162,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>598569</v>
+        <v>598754</v>
       </c>
       <c r="R113" t="n">
-        <v>7330354</v>
+        <v>7330326</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13179,7 +13221,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13189,7 +13231,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13204,12 +13246,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13220,7 +13262,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135356243</v>
+        <v>135356206</v>
       </c>
       <c r="B114" t="n">
         <v>98060</v>
@@ -13255,10 +13297,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>598482</v>
+        <v>598569</v>
       </c>
       <c r="R114" t="n">
-        <v>7330539</v>
+        <v>7330354</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13290,7 +13332,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13300,7 +13342,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13331,7 +13373,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135356845</v>
+        <v>135356243</v>
       </c>
       <c r="B115" t="n">
         <v>98060</v>
@@ -13362,17 +13404,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>598624</v>
+        <v>598482</v>
       </c>
       <c r="R115" t="n">
-        <v>7330372</v>
+        <v>7330539</v>
       </c>
       <c r="S115" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13401,7 +13443,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13411,7 +13453,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13426,12 +13468,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -13442,7 +13484,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135356884</v>
+        <v>135356845</v>
       </c>
       <c r="B116" t="n">
         <v>98060</v>
@@ -13477,13 +13519,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>598495</v>
+        <v>598624</v>
       </c>
       <c r="R116" t="n">
-        <v>7330628</v>
+        <v>7330372</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13512,7 +13554,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13522,7 +13564,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13553,7 +13595,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135358281</v>
+        <v>135356884</v>
       </c>
       <c r="B117" t="n">
         <v>98060</v>
@@ -13584,14 +13626,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>598605</v>
+        <v>598495</v>
       </c>
       <c r="R117" t="n">
-        <v>7330324</v>
+        <v>7330628</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13623,7 +13665,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13633,7 +13675,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13648,12 +13690,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -13664,7 +13706,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135382031</v>
+        <v>135358281</v>
       </c>
       <c r="B118" t="n">
         <v>98060</v>
@@ -13695,17 +13737,17 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>598459</v>
+        <v>598605</v>
       </c>
       <c r="R118" t="n">
-        <v>7330572</v>
+        <v>7330324</v>
       </c>
       <c r="S118" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13729,22 +13771,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13759,12 +13801,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -13775,7 +13817,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135382032</v>
+        <v>135382031</v>
       </c>
       <c r="B119" t="n">
         <v>98060</v>
@@ -13810,13 +13852,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>598472</v>
+        <v>598459</v>
       </c>
       <c r="R119" t="n">
-        <v>7330674</v>
+        <v>7330572</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13886,7 +13928,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135384245</v>
+        <v>135382032</v>
       </c>
       <c r="B120" t="n">
         <v>98060</v>
@@ -13917,14 +13959,14 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>598522</v>
+        <v>598472</v>
       </c>
       <c r="R120" t="n">
-        <v>7330575</v>
+        <v>7330674</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13956,7 +13998,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13966,7 +14008,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13981,12 +14023,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13997,7 +14039,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135384249</v>
+        <v>135384245</v>
       </c>
       <c r="B121" t="n">
         <v>98060</v>
@@ -14032,13 +14074,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>598492</v>
+        <v>598522</v>
       </c>
       <c r="R121" t="n">
-        <v>7330652</v>
+        <v>7330575</v>
       </c>
       <c r="S121" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14067,7 +14109,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14077,7 +14119,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14108,10 +14150,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135353486</v>
+        <v>135384249</v>
       </c>
       <c r="B122" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14119,37 +14161,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>598555</v>
+        <v>598492</v>
       </c>
       <c r="R122" t="n">
-        <v>7330349</v>
+        <v>7330652</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14173,22 +14215,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14203,12 +14245,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -14219,7 +14261,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135353494</v>
+        <v>135353486</v>
       </c>
       <c r="B123" t="n">
         <v>99217</v>
@@ -14254,10 +14296,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>598634</v>
+        <v>598555</v>
       </c>
       <c r="R123" t="n">
-        <v>7330375</v>
+        <v>7330349</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14289,7 +14331,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14299,7 +14341,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14330,7 +14372,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135353497</v>
+        <v>135353494</v>
       </c>
       <c r="B124" t="n">
         <v>99217</v>
@@ -14365,10 +14407,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>598665</v>
+        <v>598634</v>
       </c>
       <c r="R124" t="n">
-        <v>7330360</v>
+        <v>7330375</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14400,7 +14442,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14410,7 +14452,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14441,7 +14483,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135356211</v>
+        <v>135353497</v>
       </c>
       <c r="B125" t="n">
         <v>99217</v>
@@ -14472,14 +14514,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>598644</v>
+        <v>598665</v>
       </c>
       <c r="R125" t="n">
-        <v>7330364</v>
+        <v>7330360</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14511,7 +14553,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14521,7 +14563,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14536,12 +14578,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -14552,7 +14594,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135356213</v>
+        <v>135356211</v>
       </c>
       <c r="B126" t="n">
         <v>99217</v>
@@ -14587,13 +14629,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>598651</v>
+        <v>598644</v>
       </c>
       <c r="R126" t="n">
-        <v>7330373</v>
+        <v>7330364</v>
       </c>
       <c r="S126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14622,7 +14664,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14632,7 +14674,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14663,7 +14705,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135356844</v>
+        <v>135356213</v>
       </c>
       <c r="B127" t="n">
         <v>99217</v>
@@ -14694,17 +14736,17 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>598607</v>
+        <v>598651</v>
       </c>
       <c r="R127" t="n">
-        <v>7330382</v>
+        <v>7330373</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14733,7 +14775,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14743,7 +14785,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14758,12 +14800,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -14774,7 +14816,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135356846</v>
+        <v>135356844</v>
       </c>
       <c r="B128" t="n">
         <v>99217</v>
@@ -14809,10 +14851,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>598653</v>
+        <v>598607</v>
       </c>
       <c r="R128" t="n">
-        <v>7330343</v>
+        <v>7330382</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14844,7 +14886,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14854,7 +14896,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14885,7 +14927,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>135356856</v>
+        <v>135356846</v>
       </c>
       <c r="B129" t="n">
         <v>99217</v>
@@ -14920,13 +14962,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>598841</v>
+        <v>598653</v>
       </c>
       <c r="R129" t="n">
-        <v>7330355</v>
+        <v>7330343</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14955,7 +14997,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14965,7 +15007,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14996,7 +15038,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>135362163</v>
+        <v>135356856</v>
       </c>
       <c r="B130" t="n">
         <v>99217</v>
@@ -15027,17 +15069,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>598808</v>
+        <v>598841</v>
       </c>
       <c r="R130" t="n">
-        <v>7330337</v>
+        <v>7330355</v>
       </c>
       <c r="S130" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15064,9 +15106,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15081,12 +15133,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -15097,7 +15149,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>135382721</v>
+        <v>135362163</v>
       </c>
       <c r="B131" t="n">
         <v>99217</v>
@@ -15128,17 +15180,17 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>598467</v>
+        <v>598808</v>
       </c>
       <c r="R131" t="n">
-        <v>7330649</v>
+        <v>7330337</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15162,22 +15214,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15192,12 +15234,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -15208,7 +15250,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>135384251</v>
+        <v>135382721</v>
       </c>
       <c r="B132" t="n">
         <v>99217</v>
@@ -15239,14 +15281,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>598482</v>
+        <v>598467</v>
       </c>
       <c r="R132" t="n">
-        <v>7330639</v>
+        <v>7330649</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15278,7 +15320,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15288,7 +15330,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15303,12 +15345,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -15319,10 +15361,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135353490</v>
+        <v>135384251</v>
       </c>
       <c r="B133" t="n">
-        <v>104707</v>
+        <v>99217</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15330,37 +15372,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>222412</v>
+        <v>221952</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>598591</v>
+        <v>598482</v>
       </c>
       <c r="R133" t="n">
-        <v>7330353</v>
+        <v>7330639</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15384,22 +15426,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15414,12 +15456,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -15430,7 +15472,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>135357136</v>
+        <v>135353490</v>
       </c>
       <c r="B134" t="n">
         <v>104707</v>
@@ -15461,17 +15503,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>598751</v>
+        <v>598591</v>
       </c>
       <c r="R134" t="n">
-        <v>7330316</v>
+        <v>7330353</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15500,7 +15542,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15510,7 +15552,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15525,12 +15567,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -15541,7 +15583,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>135362160</v>
+        <v>135357136</v>
       </c>
       <c r="B135" t="n">
         <v>104707</v>
@@ -15576,13 +15618,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>598552</v>
+        <v>598751</v>
       </c>
       <c r="R135" t="n">
-        <v>7330368</v>
+        <v>7330316</v>
       </c>
       <c r="S135" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15609,9 +15651,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15626,12 +15678,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -15642,10 +15694,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135358271</v>
+        <v>135362160</v>
       </c>
       <c r="B136" t="n">
-        <v>99205</v>
+        <v>104707</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15653,41 +15705,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>222495</v>
+        <v>222412</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Myggblomster</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hammarbya paludosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Kuntze</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>598585</v>
+        <v>598552</v>
       </c>
       <c r="R136" t="n">
-        <v>7330354</v>
+        <v>7330368</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15714,40 +15762,29 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -15758,7 +15795,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>135358274</v>
+        <v>135358271</v>
       </c>
       <c r="B137" t="n">
         <v>99205</v>
@@ -15797,13 +15834,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>598543</v>
+        <v>598585</v>
       </c>
       <c r="R137" t="n">
-        <v>7330322</v>
+        <v>7330354</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15832,7 +15869,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15842,7 +15879,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15874,7 +15911,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>135358278</v>
+        <v>135358274</v>
       </c>
       <c r="B138" t="n">
         <v>99205</v>
@@ -15913,13 +15950,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>598566</v>
+        <v>598543</v>
       </c>
       <c r="R138" t="n">
-        <v>7330282</v>
+        <v>7330322</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15948,7 +15985,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15958,7 +15995,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15990,10 +16027,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>135356838</v>
+        <v>135358278</v>
       </c>
       <c r="B139" t="n">
-        <v>98214</v>
+        <v>99205</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16001,37 +16038,41 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>222741</v>
+        <v>222495</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Myggblomster</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hammarbya paludosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Kuntze</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>598555</v>
+        <v>598566</v>
       </c>
       <c r="R139" t="n">
-        <v>7330375</v>
+        <v>7330282</v>
       </c>
       <c r="S139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16060,7 +16101,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16070,7 +16111,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16079,18 +16120,19 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -16101,7 +16143,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>135357146</v>
+        <v>135356838</v>
       </c>
       <c r="B140" t="n">
         <v>98214</v>
@@ -16132,17 +16174,17 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>598911</v>
+        <v>598555</v>
       </c>
       <c r="R140" t="n">
-        <v>7330350</v>
+        <v>7330375</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16171,7 +16213,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16181,7 +16223,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16196,12 +16238,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -16212,7 +16254,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>135357209</v>
+        <v>135357146</v>
       </c>
       <c r="B141" t="n">
         <v>98214</v>
@@ -16247,10 +16289,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>598519</v>
+        <v>598911</v>
       </c>
       <c r="R141" t="n">
-        <v>7330570</v>
+        <v>7330350</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16282,7 +16324,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16292,7 +16334,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16323,10 +16365,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>135357123</v>
+        <v>135357209</v>
       </c>
       <c r="B142" t="n">
-        <v>102871</v>
+        <v>98214</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16334,21 +16376,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>223037</v>
+        <v>222741</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16358,10 +16400,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>598552</v>
+        <v>598519</v>
       </c>
       <c r="R142" t="n">
-        <v>7330359</v>
+        <v>7330570</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16393,7 +16435,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16403,7 +16445,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16434,7 +16476,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>135357202</v>
+        <v>135357123</v>
       </c>
       <c r="B143" t="n">
         <v>102871</v>
@@ -16469,10 +16511,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>598553</v>
+        <v>598552</v>
       </c>
       <c r="R143" t="n">
-        <v>7330578</v>
+        <v>7330359</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16504,7 +16546,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16514,7 +16556,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16545,7 +16587,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>135382713</v>
+        <v>135357202</v>
       </c>
       <c r="B144" t="n">
         <v>102871</v>
@@ -16576,14 +16618,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>598464</v>
+        <v>598553</v>
       </c>
       <c r="R144" t="n">
-        <v>7330416</v>
+        <v>7330578</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16610,22 +16652,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16656,7 +16698,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>135382724</v>
+        <v>135382713</v>
       </c>
       <c r="B145" t="n">
         <v>102871</v>
@@ -16691,10 +16733,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>598467</v>
+        <v>598464</v>
       </c>
       <c r="R145" t="n">
-        <v>7330649</v>
+        <v>7330416</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16726,7 +16768,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16736,7 +16778,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16767,10 +16809,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>135357122</v>
+        <v>135382724</v>
       </c>
       <c r="B146" t="n">
-        <v>98249</v>
+        <v>102871</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16778,34 +16820,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>223358</v>
+        <v>223037</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>598552</v>
+        <v>598467</v>
       </c>
       <c r="R146" t="n">
-        <v>7330359</v>
+        <v>7330649</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16832,22 +16874,22 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16878,7 +16920,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>135357145</v>
+        <v>135357122</v>
       </c>
       <c r="B147" t="n">
         <v>98249</v>
@@ -16913,10 +16955,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>598911</v>
+        <v>598552</v>
       </c>
       <c r="R147" t="n">
-        <v>7330350</v>
+        <v>7330359</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16948,7 +16990,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16958,7 +17000,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16989,7 +17031,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>135358277</v>
+        <v>135357145</v>
       </c>
       <c r="B148" t="n">
         <v>98249</v>
@@ -17020,17 +17062,17 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>598551</v>
+        <v>598911</v>
       </c>
       <c r="R148" t="n">
-        <v>7330296</v>
+        <v>7330350</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17059,7 +17101,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17069,7 +17111,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17084,12 +17126,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -17100,7 +17142,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>135382718</v>
+        <v>135358277</v>
       </c>
       <c r="B149" t="n">
         <v>98249</v>
@@ -17131,17 +17173,17 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>598507</v>
+        <v>598551</v>
       </c>
       <c r="R149" t="n">
-        <v>7330626</v>
+        <v>7330296</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17165,22 +17207,22 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17195,12 +17237,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -17211,10 +17253,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>135353482</v>
+        <v>135382718</v>
       </c>
       <c r="B150" t="n">
-        <v>101293</v>
+        <v>98249</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17222,37 +17264,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>598530</v>
+        <v>598507</v>
       </c>
       <c r="R150" t="n">
-        <v>7330340</v>
+        <v>7330626</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17276,22 +17318,22 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17306,12 +17348,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -17322,7 +17364,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>135357117</v>
+        <v>135353482</v>
       </c>
       <c r="B151" t="n">
         <v>101293</v>
@@ -17353,17 +17395,17 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>598525</v>
+        <v>598530</v>
       </c>
       <c r="R151" t="n">
-        <v>7330346</v>
+        <v>7330340</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17417,12 +17459,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -17433,7 +17475,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>135357120</v>
+        <v>135357117</v>
       </c>
       <c r="B152" t="n">
         <v>101293</v>
@@ -17468,10 +17510,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>598552</v>
+        <v>598525</v>
       </c>
       <c r="R152" t="n">
-        <v>7330359</v>
+        <v>7330346</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17503,7 +17545,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17513,7 +17555,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17544,7 +17586,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>135357138</v>
+        <v>135357120</v>
       </c>
       <c r="B153" t="n">
         <v>101293</v>
@@ -17579,10 +17621,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>598751</v>
+        <v>598552</v>
       </c>
       <c r="R153" t="n">
-        <v>7330316</v>
+        <v>7330359</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17614,7 +17656,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17624,7 +17666,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17655,7 +17697,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>135357140</v>
+        <v>135357138</v>
       </c>
       <c r="B154" t="n">
         <v>101293</v>
@@ -17690,10 +17732,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>598770</v>
+        <v>598751</v>
       </c>
       <c r="R154" t="n">
-        <v>7330338</v>
+        <v>7330316</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17725,7 +17767,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17735,7 +17777,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17766,7 +17808,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>135357147</v>
+        <v>135357140</v>
       </c>
       <c r="B155" t="n">
         <v>101293</v>
@@ -17801,10 +17843,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>598911</v>
+        <v>598770</v>
       </c>
       <c r="R155" t="n">
-        <v>7330350</v>
+        <v>7330338</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17836,7 +17878,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17846,7 +17888,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17877,7 +17919,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>135357205</v>
+        <v>135357147</v>
       </c>
       <c r="B156" t="n">
         <v>101293</v>
@@ -17912,10 +17954,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>598553</v>
+        <v>598911</v>
       </c>
       <c r="R156" t="n">
-        <v>7330578</v>
+        <v>7330350</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17947,7 +17989,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17957,7 +17999,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17988,7 +18030,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>135357206</v>
+        <v>135357205</v>
       </c>
       <c r="B157" t="n">
         <v>101293</v>
@@ -18023,10 +18065,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>598521</v>
+        <v>598553</v>
       </c>
       <c r="R157" t="n">
-        <v>7330581</v>
+        <v>7330578</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18058,7 +18100,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18068,7 +18110,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18099,7 +18141,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>135357213</v>
+        <v>135357206</v>
       </c>
       <c r="B158" t="n">
         <v>101293</v>
@@ -18134,10 +18176,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>598501</v>
+        <v>598521</v>
       </c>
       <c r="R158" t="n">
-        <v>7330475</v>
+        <v>7330581</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18169,7 +18211,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18179,7 +18221,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18210,7 +18252,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>135358268</v>
+        <v>135357213</v>
       </c>
       <c r="B159" t="n">
         <v>101293</v>
@@ -18241,17 +18283,17 @@
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>598580</v>
+        <v>598501</v>
       </c>
       <c r="R159" t="n">
-        <v>7330339</v>
+        <v>7330475</v>
       </c>
       <c r="S159" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18280,7 +18322,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18290,7 +18332,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18305,12 +18347,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -18321,7 +18363,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>135358284</v>
+        <v>135358268</v>
       </c>
       <c r="B160" t="n">
         <v>101293</v>
@@ -18356,10 +18398,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>598610</v>
+        <v>598580</v>
       </c>
       <c r="R160" t="n">
-        <v>7330295</v>
+        <v>7330339</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -18391,7 +18433,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18401,7 +18443,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18432,7 +18474,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>135358293</v>
+        <v>135358284</v>
       </c>
       <c r="B161" t="n">
         <v>101293</v>
@@ -18467,10 +18509,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>598830</v>
+        <v>598610</v>
       </c>
       <c r="R161" t="n">
-        <v>7330303</v>
+        <v>7330295</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -18502,7 +18544,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18512,7 +18554,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18543,7 +18585,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>135358341</v>
+        <v>135358293</v>
       </c>
       <c r="B162" t="n">
         <v>101293</v>
@@ -18578,10 +18620,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>598546</v>
+        <v>598830</v>
       </c>
       <c r="R162" t="n">
-        <v>7330653</v>
+        <v>7330303</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -18613,7 +18655,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18623,7 +18665,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18654,7 +18696,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>135382388</v>
+        <v>135358341</v>
       </c>
       <c r="B163" t="n">
         <v>101293</v>
@@ -18685,14 +18727,14 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>598483</v>
+        <v>598546</v>
       </c>
       <c r="R163" t="n">
-        <v>7330403</v>
+        <v>7330653</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -18719,22 +18761,22 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18749,12 +18791,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -18765,7 +18807,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>135382712</v>
+        <v>135382388</v>
       </c>
       <c r="B164" t="n">
         <v>101293</v>
@@ -18796,17 +18838,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>598464</v>
+        <v>598483</v>
       </c>
       <c r="R164" t="n">
-        <v>7330416</v>
+        <v>7330403</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18860,12 +18902,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -18876,7 +18918,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>135382717</v>
+        <v>135382712</v>
       </c>
       <c r="B165" t="n">
         <v>101293</v>
@@ -18911,10 +18953,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>598507</v>
+        <v>598464</v>
       </c>
       <c r="R165" t="n">
-        <v>7330626</v>
+        <v>7330416</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18946,7 +18988,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18956,7 +18998,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18987,7 +19029,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>135382722</v>
+        <v>135382717</v>
       </c>
       <c r="B166" t="n">
         <v>101293</v>
@@ -19022,10 +19064,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>598467</v>
+        <v>598507</v>
       </c>
       <c r="R166" t="n">
-        <v>7330649</v>
+        <v>7330626</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19057,7 +19099,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19067,7 +19109,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19098,48 +19140,48 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>135356852</v>
+        <v>135382722</v>
       </c>
       <c r="B167" t="n">
-        <v>92366</v>
+        <v>101293</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6040186</v>
+        <v>224885</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>598735</v>
+        <v>598467</v>
       </c>
       <c r="R167" t="n">
-        <v>7330341</v>
+        <v>7330649</v>
       </c>
       <c r="S167" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -19163,22 +19205,22 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19187,19 +19229,18 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -19210,45 +19251,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>135357134</v>
+        <v>135357130</v>
       </c>
       <c r="B168" t="n">
-        <v>92366</v>
+        <v>101952</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6040186</v>
+        <v>225188</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vanliga skogsvinbär</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
+          <t>Ribes spicatum subsp. spicatum</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>598723</v>
+        <v>598613</v>
       </c>
       <c r="R168" t="n">
-        <v>7330305</v>
+        <v>7330353</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19280,7 +19321,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19290,7 +19331,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19315,6 +19356,230 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>135356852</v>
+      </c>
+      <c r="B169" t="n">
+        <v>92366</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Muorkenåive S, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>598735</v>
+      </c>
+      <c r="R169" t="n">
+        <v>7330341</v>
+      </c>
+      <c r="S169" t="n">
+        <v>5</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>135357134</v>
+      </c>
+      <c r="B170" t="n">
+        <v>92366</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>598723</v>
+      </c>
+      <c r="R170" t="n">
+        <v>7330305</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY170"/>
+  <dimension ref="A1:AZ170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353510</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356842</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356375</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353501</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353508</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353519</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356244</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1562,6 +1602,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356379</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,6 +1718,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356849</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1784,6 +1834,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356851</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1895,6 +1950,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356854</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2006,6 +2066,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356883</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2117,6 +2182,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356888</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2228,6 +2298,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356889</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2339,6 +2414,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357129</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2450,6 +2530,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357135</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2561,6 +2646,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358290</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2672,6 +2762,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382781</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2783,6 +2878,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353493</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2894,6 +2994,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353499</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3005,6 +3110,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353520</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3116,6 +3226,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356887</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3227,6 +3342,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382780</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3338,6 +3458,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353492</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3449,6 +3574,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353498</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3560,6 +3690,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353502</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3671,6 +3806,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356215</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3782,6 +3922,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356221</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3893,6 +4038,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356242</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4004,6 +4154,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356847</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4115,6 +4270,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356848</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4226,6 +4386,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358272</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4337,6 +4502,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358273</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4448,6 +4618,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358280</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4559,6 +4734,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356220</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4670,6 +4850,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356374</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4781,6 +4966,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356850</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4892,6 +5082,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382715</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5001,6 +5196,11 @@
       <c r="AY40" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353517</t>
         </is>
       </c>
     </row>
@@ -5118,6 +5318,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356378</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5229,6 +5434,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358288</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5340,6 +5550,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382714</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5451,6 +5666,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353500</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5562,6 +5782,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356212</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5673,6 +5898,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356853</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5784,6 +6014,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357133</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5895,6 +6130,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357142</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6006,6 +6246,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382782</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6115,6 +6360,11 @@
       <c r="AY50" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356855</t>
         </is>
       </c>
     </row>
@@ -6270,6 +6520,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135420258</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6381,6 +6636,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356208</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6492,6 +6752,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356239</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6603,6 +6868,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357125</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6714,6 +6984,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357118</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6825,6 +7100,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357124</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6936,6 +7216,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357203</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7047,6 +7332,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357207</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7158,6 +7448,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357208</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7267,6 +7562,11 @@
       <c r="AY60" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382719</t>
         </is>
       </c>
     </row>
@@ -7384,6 +7684,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358275</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7495,6 +7800,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356210</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7606,6 +7916,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356372</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7717,6 +8032,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353513</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7828,6 +8148,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353495</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7939,6 +8264,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353515</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8050,6 +8380,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356240</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8161,6 +8496,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356837</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8272,6 +8612,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382466</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8383,6 +8728,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384252</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8494,6 +8844,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353509</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8605,6 +8960,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356841</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8716,6 +9076,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357126</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8832,6 +9197,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353488</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8948,6 +9318,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353503</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9064,6 +9439,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356216</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9188,6 +9568,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356376</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9312,6 +9697,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356380</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9428,6 +9818,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357127</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9544,6 +9939,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358283</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9668,6 +10068,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382716</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9792,6 +10197,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382779</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9916,6 +10326,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384126</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10040,6 +10455,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357215</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10159,6 +10579,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382711</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10270,6 +10695,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385939</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10381,6 +10811,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382469</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10492,6 +10927,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384124</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10603,6 +11043,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384162</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10706,6 +11151,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94770073</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10817,6 +11267,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356843</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10928,6 +11383,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353481</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11039,6 +11499,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353512</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11150,6 +11615,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356205</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11261,6 +11731,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356241</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11372,6 +11847,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357137</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11483,6 +11963,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357141</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11594,6 +12079,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357201</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11705,6 +12195,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357211</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11816,6 +12311,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357212</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11927,6 +12427,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358269</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12038,6 +12543,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358276</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12149,6 +12659,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358292</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12260,6 +12775,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358342</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12371,6 +12891,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382720</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12482,6 +13007,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382723</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12593,6 +13123,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353491</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12704,6 +13239,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356209</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12815,6 +13355,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356218</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12926,6 +13471,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356839</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13037,6 +13587,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356886</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13148,6 +13703,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358270</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13259,6 +13819,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358287</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13370,6 +13935,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356206</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13481,6 +14051,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356243</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13592,6 +14167,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356845</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13703,6 +14283,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356884</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13814,6 +14399,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358281</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13925,6 +14515,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382031</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14036,6 +14631,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382032</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14147,6 +14747,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384245</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14258,6 +14863,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384249</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14369,6 +14979,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353486</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14480,6 +15095,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353494</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14591,6 +15211,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353497</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14702,6 +15327,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356211</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14813,6 +15443,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356213</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14924,6 +15559,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356844</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15035,6 +15675,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356846</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15146,6 +15791,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356856</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15247,6 +15897,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362163</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15358,6 +16013,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382721</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15469,6 +16129,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384251</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15580,6 +16245,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353490</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15691,6 +16361,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357136</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15790,6 +16465,11 @@
       <c r="AY136" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362160</t>
         </is>
       </c>
     </row>
@@ -15908,6 +16588,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358271</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16024,6 +16709,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358274</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16140,6 +16830,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358278</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16251,6 +16946,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356838</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16362,6 +17062,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357146</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16473,6 +17178,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357209</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16584,6 +17294,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357123</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16695,6 +17410,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357202</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16806,6 +17526,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382713</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16917,6 +17642,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382724</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17028,6 +17758,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357122</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17139,6 +17874,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357145</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17250,6 +17990,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358277</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17361,6 +18106,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382718</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17472,6 +18222,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353482</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17583,6 +18338,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357117</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17694,6 +18454,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357120</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17805,6 +18570,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357138</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17916,6 +18686,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357140</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18027,6 +18802,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357147</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18138,6 +18918,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357205</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18249,6 +19034,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357206</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18360,6 +19150,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357213</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18471,6 +19266,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358268</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18582,6 +19382,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358284</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18693,6 +19498,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358293</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18804,6 +19614,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358341</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18915,6 +19730,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382388</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19026,6 +19846,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382712</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19137,6 +19962,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382717</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19246,6 +20076,11 @@
       <c r="AY167" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382722</t>
         </is>
       </c>
     </row>
@@ -19360,6 +20195,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357130</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19472,6 +20312,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356852</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19584,8 +20429,184 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357134</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135353510</v>
       </c>
       <c r="B2" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135356842</v>
       </c>
       <c r="B3" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135356375</v>
       </c>
       <c r="B4" t="n">
-        <v>92069</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135353501</v>
       </c>
       <c r="B5" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>135353508</v>
       </c>
       <c r="B6" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>135353519</v>
       </c>
       <c r="B7" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>135356244</v>
       </c>
       <c r="B8" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135356379</v>
       </c>
       <c r="B9" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135356849</v>
       </c>
       <c r="B10" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135356851</v>
       </c>
       <c r="B11" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135356854</v>
       </c>
       <c r="B12" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>135356883</v>
       </c>
       <c r="B13" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135356888</v>
       </c>
       <c r="B14" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>135356889</v>
       </c>
       <c r="B15" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>135357129</v>
       </c>
       <c r="B16" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>135357135</v>
       </c>
       <c r="B17" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>135358290</v>
       </c>
       <c r="B18" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>135382781</v>
       </c>
       <c r="B19" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>135353493</v>
       </c>
       <c r="B20" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>135353499</v>
       </c>
       <c r="B21" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>135353520</v>
       </c>
       <c r="B22" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>135356887</v>
       </c>
       <c r="B23" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135382780</v>
       </c>
       <c r="B24" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>135353492</v>
       </c>
       <c r="B25" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>135353498</v>
       </c>
       <c r="B26" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>135353502</v>
       </c>
       <c r="B27" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>135356215</v>
       </c>
       <c r="B28" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>135356221</v>
       </c>
       <c r="B29" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>135356242</v>
       </c>
       <c r="B30" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>135356847</v>
       </c>
       <c r="B31" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135356848</v>
       </c>
       <c r="B32" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>135358272</v>
       </c>
       <c r="B33" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>135358273</v>
       </c>
       <c r="B34" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>135358280</v>
       </c>
       <c r="B35" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>135356220</v>
       </c>
       <c r="B36" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135356374</v>
       </c>
       <c r="B37" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>135356850</v>
       </c>
       <c r="B38" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>135382715</v>
       </c>
       <c r="B39" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>135353517</v>
       </c>
       <c r="B40" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>135356378</v>
       </c>
       <c r="B41" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>135358288</v>
       </c>
       <c r="B42" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>135382714</v>
       </c>
       <c r="B43" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>135353500</v>
       </c>
       <c r="B44" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>135356212</v>
       </c>
       <c r="B45" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>135356853</v>
       </c>
       <c r="B46" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>135357133</v>
       </c>
       <c r="B47" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>135357142</v>
       </c>
       <c r="B48" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>135382782</v>
       </c>
       <c r="B49" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>135356855</v>
       </c>
       <c r="B50" t="n">
-        <v>92806</v>
+        <v>92848</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>135420258</v>
       </c>
       <c r="B51" t="n">
-        <v>92827</v>
+        <v>92869</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>135356208</v>
       </c>
       <c r="B52" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>135356239</v>
       </c>
       <c r="B53" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>135357125</v>
       </c>
       <c r="B54" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>135357118</v>
       </c>
       <c r="B55" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>135357124</v>
       </c>
       <c r="B56" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>135357203</v>
       </c>
       <c r="B57" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>135357207</v>
       </c>
       <c r="B58" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>135357208</v>
       </c>
       <c r="B59" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>135382719</v>
       </c>
       <c r="B60" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>135358275</v>
       </c>
       <c r="B61" t="n">
-        <v>87625</v>
+        <v>87665</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>135356210</v>
       </c>
       <c r="B62" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>135356372</v>
       </c>
       <c r="B63" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>135353513</v>
       </c>
       <c r="B64" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>135353495</v>
       </c>
       <c r="B65" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>135353515</v>
       </c>
       <c r="B66" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>135356240</v>
       </c>
       <c r="B67" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>135356837</v>
       </c>
       <c r="B68" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>135382466</v>
       </c>
       <c r="B69" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>135384252</v>
       </c>
       <c r="B70" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>135353509</v>
       </c>
       <c r="B71" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>135356841</v>
       </c>
       <c r="B72" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>135357126</v>
       </c>
       <c r="B73" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>135353488</v>
       </c>
       <c r="B74" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>135353503</v>
       </c>
       <c r="B75" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>135356216</v>
       </c>
       <c r="B76" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>135356376</v>
       </c>
       <c r="B77" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>135356380</v>
       </c>
       <c r="B78" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>135357127</v>
       </c>
       <c r="B79" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>135358283</v>
       </c>
       <c r="B80" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>135382716</v>
       </c>
       <c r="B81" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>135382779</v>
       </c>
       <c r="B82" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>135384126</v>
       </c>
       <c r="B83" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>135357215</v>
       </c>
       <c r="B84" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>135382711</v>
       </c>
       <c r="B85" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>135385939</v>
       </c>
       <c r="B86" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>135382469</v>
       </c>
       <c r="B87" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>135384124</v>
       </c>
       <c r="B88" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>135384162</v>
       </c>
       <c r="B89" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>135356843</v>
       </c>
       <c r="B91" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>135353481</v>
       </c>
       <c r="B92" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>135353512</v>
       </c>
       <c r="B93" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>135356205</v>
       </c>
       <c r="B94" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>135356241</v>
       </c>
       <c r="B95" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>135357137</v>
       </c>
       <c r="B96" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>135357141</v>
       </c>
       <c r="B97" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>135357201</v>
       </c>
       <c r="B98" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>135357211</v>
       </c>
       <c r="B99" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>135357212</v>
       </c>
       <c r="B100" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>135358269</v>
       </c>
       <c r="B101" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>135358276</v>
       </c>
       <c r="B102" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>135358292</v>
       </c>
       <c r="B103" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>135358342</v>
       </c>
       <c r="B104" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>135382720</v>
       </c>
       <c r="B105" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>135382723</v>
       </c>
       <c r="B106" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>135353491</v>
       </c>
       <c r="B107" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>135356209</v>
       </c>
       <c r="B108" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>135356218</v>
       </c>
       <c r="B109" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>135356839</v>
       </c>
       <c r="B110" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>135356886</v>
       </c>
       <c r="B111" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>135358270</v>
       </c>
       <c r="B112" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>135358287</v>
       </c>
       <c r="B113" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>135356206</v>
       </c>
       <c r="B114" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>135356243</v>
       </c>
       <c r="B115" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>135356845</v>
       </c>
       <c r="B116" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>135356884</v>
       </c>
       <c r="B117" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>135358281</v>
       </c>
       <c r="B118" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>135382031</v>
       </c>
       <c r="B119" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>135382032</v>
       </c>
       <c r="B120" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>135384245</v>
       </c>
       <c r="B121" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>135384249</v>
       </c>
       <c r="B122" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>135353486</v>
       </c>
       <c r="B123" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>135353494</v>
       </c>
       <c r="B124" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>135353497</v>
       </c>
       <c r="B125" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>135356211</v>
       </c>
       <c r="B126" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>135356213</v>
       </c>
       <c r="B127" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>135356844</v>
       </c>
       <c r="B128" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>135356846</v>
       </c>
       <c r="B129" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>135356856</v>
       </c>
       <c r="B130" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>135362163</v>
       </c>
       <c r="B131" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>135382721</v>
       </c>
       <c r="B132" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>135384251</v>
       </c>
       <c r="B133" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>135353490</v>
       </c>
       <c r="B134" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>135357136</v>
       </c>
       <c r="B135" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>135362160</v>
       </c>
       <c r="B136" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>135358271</v>
       </c>
       <c r="B137" t="n">
-        <v>99205</v>
+        <v>99252</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>135358274</v>
       </c>
       <c r="B138" t="n">
-        <v>99205</v>
+        <v>99252</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>135358278</v>
       </c>
       <c r="B139" t="n">
-        <v>99205</v>
+        <v>99252</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>135356838</v>
       </c>
       <c r="B140" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>135357146</v>
       </c>
       <c r="B141" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>135357209</v>
       </c>
       <c r="B142" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>135357123</v>
       </c>
       <c r="B143" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>135357202</v>
       </c>
       <c r="B144" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>135382713</v>
       </c>
       <c r="B145" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>135382724</v>
       </c>
       <c r="B146" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>135357122</v>
       </c>
       <c r="B147" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>135357145</v>
       </c>
       <c r="B148" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>135358277</v>
       </c>
       <c r="B149" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>135382718</v>
       </c>
       <c r="B150" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>135353482</v>
       </c>
       <c r="B151" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>135357117</v>
       </c>
       <c r="B152" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>135357120</v>
       </c>
       <c r="B153" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>135357138</v>
       </c>
       <c r="B154" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>135357140</v>
       </c>
       <c r="B155" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>135357147</v>
       </c>
       <c r="B156" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>135357205</v>
       </c>
       <c r="B157" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>135357206</v>
       </c>
       <c r="B158" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>135357213</v>
       </c>
       <c r="B159" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>135358268</v>
       </c>
       <c r="B160" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>135358284</v>
       </c>
       <c r="B161" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>135358293</v>
       </c>
       <c r="B162" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>135358341</v>
       </c>
       <c r="B163" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>135382388</v>
       </c>
       <c r="B164" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>135382712</v>
       </c>
       <c r="B165" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>135382717</v>
       </c>
       <c r="B166" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>135382722</v>
       </c>
       <c r="B167" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>135357130</v>
       </c>
       <c r="B168" t="n">
-        <v>101952</v>
+        <v>102000</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>135356852</v>
       </c>
       <c r="B169" t="n">
-        <v>92366</v>
+        <v>92408</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>135357134</v>
       </c>
       <c r="B170" t="n">
-        <v>92366</v>
+        <v>92408</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135353510</v>
       </c>
       <c r="B2" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135356842</v>
       </c>
       <c r="B3" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135356375</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135353501</v>
       </c>
       <c r="B5" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>135353508</v>
       </c>
       <c r="B6" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>135353519</v>
       </c>
       <c r="B7" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>135356244</v>
       </c>
       <c r="B8" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135356379</v>
       </c>
       <c r="B9" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135356849</v>
       </c>
       <c r="B10" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135356851</v>
       </c>
       <c r="B11" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135356854</v>
       </c>
       <c r="B12" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>135356883</v>
       </c>
       <c r="B13" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135356888</v>
       </c>
       <c r="B14" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>135356889</v>
       </c>
       <c r="B15" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>135357129</v>
       </c>
       <c r="B16" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>135357135</v>
       </c>
       <c r="B17" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>135358290</v>
       </c>
       <c r="B18" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>135382781</v>
       </c>
       <c r="B19" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>135353493</v>
       </c>
       <c r="B20" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>135353499</v>
       </c>
       <c r="B21" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>135353520</v>
       </c>
       <c r="B22" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>135356887</v>
       </c>
       <c r="B23" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135382780</v>
       </c>
       <c r="B24" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>135353492</v>
       </c>
       <c r="B25" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>135353498</v>
       </c>
       <c r="B26" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>135353502</v>
       </c>
       <c r="B27" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>135356215</v>
       </c>
       <c r="B28" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>135356221</v>
       </c>
       <c r="B29" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>135356242</v>
       </c>
       <c r="B30" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>135356847</v>
       </c>
       <c r="B31" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135356848</v>
       </c>
       <c r="B32" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>135358272</v>
       </c>
       <c r="B33" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>135358273</v>
       </c>
       <c r="B34" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>135358280</v>
       </c>
       <c r="B35" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>135356220</v>
       </c>
       <c r="B36" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135356374</v>
       </c>
       <c r="B37" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>135356850</v>
       </c>
       <c r="B38" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>135382715</v>
       </c>
       <c r="B39" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>135353517</v>
       </c>
       <c r="B40" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>135356378</v>
       </c>
       <c r="B41" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>135358288</v>
       </c>
       <c r="B42" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>135382714</v>
       </c>
       <c r="B43" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>135353500</v>
       </c>
       <c r="B44" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>135356212</v>
       </c>
       <c r="B45" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>135356853</v>
       </c>
       <c r="B46" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>135357133</v>
       </c>
       <c r="B47" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>135357142</v>
       </c>
       <c r="B48" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>135382782</v>
       </c>
       <c r="B49" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>135356855</v>
       </c>
       <c r="B50" t="n">
-        <v>92848</v>
+        <v>92875</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>135420258</v>
       </c>
       <c r="B51" t="n">
-        <v>92869</v>
+        <v>92896</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>135356208</v>
       </c>
       <c r="B52" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>135356239</v>
       </c>
       <c r="B53" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>135357125</v>
       </c>
       <c r="B54" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>135357118</v>
       </c>
       <c r="B55" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>135357124</v>
       </c>
       <c r="B56" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>135357203</v>
       </c>
       <c r="B57" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>135357207</v>
       </c>
       <c r="B58" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>135357208</v>
       </c>
       <c r="B59" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>135382719</v>
       </c>
       <c r="B60" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>135358275</v>
       </c>
       <c r="B61" t="n">
-        <v>87665</v>
+        <v>87692</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>135356210</v>
       </c>
       <c r="B62" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>135356372</v>
       </c>
       <c r="B63" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>135353513</v>
       </c>
       <c r="B64" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>135353495</v>
       </c>
       <c r="B65" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>135353515</v>
       </c>
       <c r="B66" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>135356240</v>
       </c>
       <c r="B67" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>135356837</v>
       </c>
       <c r="B68" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>135382466</v>
       </c>
       <c r="B69" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>135384252</v>
       </c>
       <c r="B70" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>135353509</v>
       </c>
       <c r="B71" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>135356841</v>
       </c>
       <c r="B72" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>135357126</v>
       </c>
       <c r="B73" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>135382469</v>
       </c>
       <c r="B87" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>135384124</v>
       </c>
       <c r="B88" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>135384162</v>
       </c>
       <c r="B89" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>135356843</v>
       </c>
       <c r="B91" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>135353481</v>
       </c>
       <c r="B92" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>135353512</v>
       </c>
       <c r="B93" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>135356205</v>
       </c>
       <c r="B94" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>135356241</v>
       </c>
       <c r="B95" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>135357137</v>
       </c>
       <c r="B96" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>135357141</v>
       </c>
       <c r="B97" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>135357201</v>
       </c>
       <c r="B98" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>135357211</v>
       </c>
       <c r="B99" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>135357212</v>
       </c>
       <c r="B100" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>135358269</v>
       </c>
       <c r="B101" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>135358276</v>
       </c>
       <c r="B102" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>135358292</v>
       </c>
       <c r="B103" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>135358342</v>
       </c>
       <c r="B104" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>135382720</v>
       </c>
       <c r="B105" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>135382723</v>
       </c>
       <c r="B106" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>135353491</v>
       </c>
       <c r="B107" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>135356209</v>
       </c>
       <c r="B108" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>135356218</v>
       </c>
       <c r="B109" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>135356839</v>
       </c>
       <c r="B110" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>135356886</v>
       </c>
       <c r="B111" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>135358270</v>
       </c>
       <c r="B112" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>135358287</v>
       </c>
       <c r="B113" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>135356206</v>
       </c>
       <c r="B114" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>135356243</v>
       </c>
       <c r="B115" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>135356845</v>
       </c>
       <c r="B116" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>135356884</v>
       </c>
       <c r="B117" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>135358281</v>
       </c>
       <c r="B118" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>135382031</v>
       </c>
       <c r="B119" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>135382032</v>
       </c>
       <c r="B120" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>135384245</v>
       </c>
       <c r="B121" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>135384249</v>
       </c>
       <c r="B122" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>135353486</v>
       </c>
       <c r="B123" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>135353494</v>
       </c>
       <c r="B124" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>135353497</v>
       </c>
       <c r="B125" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>135356211</v>
       </c>
       <c r="B126" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>135356213</v>
       </c>
       <c r="B127" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>135356844</v>
       </c>
       <c r="B128" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>135356846</v>
       </c>
       <c r="B129" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>135356856</v>
       </c>
       <c r="B130" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>135362163</v>
       </c>
       <c r="B131" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>135382721</v>
       </c>
       <c r="B132" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>135384251</v>
       </c>
       <c r="B133" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>135353490</v>
       </c>
       <c r="B134" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>135357136</v>
       </c>
       <c r="B135" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>135362160</v>
       </c>
       <c r="B136" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>135358271</v>
       </c>
       <c r="B137" t="n">
-        <v>99252</v>
+        <v>99279</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>135358274</v>
       </c>
       <c r="B138" t="n">
-        <v>99252</v>
+        <v>99279</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>135358278</v>
       </c>
       <c r="B139" t="n">
-        <v>99252</v>
+        <v>99279</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>135356838</v>
       </c>
       <c r="B140" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>135357146</v>
       </c>
       <c r="B141" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>135357209</v>
       </c>
       <c r="B142" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>135357123</v>
       </c>
       <c r="B143" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>135357202</v>
       </c>
       <c r="B144" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>135382713</v>
       </c>
       <c r="B145" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>135382724</v>
       </c>
       <c r="B146" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>135357122</v>
       </c>
       <c r="B147" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>135357145</v>
       </c>
       <c r="B148" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>135358277</v>
       </c>
       <c r="B149" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>135382718</v>
       </c>
       <c r="B150" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>135353482</v>
       </c>
       <c r="B151" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>135357117</v>
       </c>
       <c r="B152" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>135357120</v>
       </c>
       <c r="B153" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>135357138</v>
       </c>
       <c r="B154" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>135357140</v>
       </c>
       <c r="B155" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>135357147</v>
       </c>
       <c r="B156" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>135357205</v>
       </c>
       <c r="B157" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>135357206</v>
       </c>
       <c r="B158" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>135357213</v>
       </c>
       <c r="B159" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>135358268</v>
       </c>
       <c r="B160" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>135358284</v>
       </c>
       <c r="B161" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>135358293</v>
       </c>
       <c r="B162" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>135358341</v>
       </c>
       <c r="B163" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>135382388</v>
       </c>
       <c r="B164" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>135382712</v>
       </c>
       <c r="B165" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>135382717</v>
       </c>
       <c r="B166" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>135382722</v>
       </c>
       <c r="B167" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>135357130</v>
       </c>
       <c r="B168" t="n">
-        <v>102000</v>
+        <v>102027</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>135356852</v>
       </c>
       <c r="B169" t="n">
-        <v>92408</v>
+        <v>92435</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>135357134</v>
       </c>
       <c r="B170" t="n">
-        <v>92408</v>
+        <v>92435</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>135356375</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135353501</v>
       </c>
       <c r="B5" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>135353508</v>
       </c>
       <c r="B6" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>135353519</v>
       </c>
       <c r="B7" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>135356244</v>
       </c>
       <c r="B8" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135356379</v>
       </c>
       <c r="B9" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135356849</v>
       </c>
       <c r="B10" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135356851</v>
       </c>
       <c r="B11" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135356854</v>
       </c>
       <c r="B12" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>135356883</v>
       </c>
       <c r="B13" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135356888</v>
       </c>
       <c r="B14" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>135356889</v>
       </c>
       <c r="B15" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>135357129</v>
       </c>
       <c r="B16" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>135357135</v>
       </c>
       <c r="B17" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>135358290</v>
       </c>
       <c r="B18" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>135382781</v>
       </c>
       <c r="B19" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>135353493</v>
       </c>
       <c r="B20" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>135353499</v>
       </c>
       <c r="B21" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>135353520</v>
       </c>
       <c r="B22" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>135356887</v>
       </c>
       <c r="B23" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135382780</v>
       </c>
       <c r="B24" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>135353492</v>
       </c>
       <c r="B25" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>135353498</v>
       </c>
       <c r="B26" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>135353502</v>
       </c>
       <c r="B27" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>135356215</v>
       </c>
       <c r="B28" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>135356221</v>
       </c>
       <c r="B29" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>135356242</v>
       </c>
       <c r="B30" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>135356847</v>
       </c>
       <c r="B31" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>135356848</v>
       </c>
       <c r="B32" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>135358272</v>
       </c>
       <c r="B33" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>135358273</v>
       </c>
       <c r="B34" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>135358280</v>
       </c>
       <c r="B35" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>135356220</v>
       </c>
       <c r="B36" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135356374</v>
       </c>
       <c r="B37" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>135356850</v>
       </c>
       <c r="B38" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>135382715</v>
       </c>
       <c r="B39" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>135353517</v>
       </c>
       <c r="B40" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>135356378</v>
       </c>
       <c r="B41" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>135358288</v>
       </c>
       <c r="B42" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>135382714</v>
       </c>
       <c r="B43" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>135353500</v>
       </c>
       <c r="B44" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>135356212</v>
       </c>
       <c r="B45" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>135356853</v>
       </c>
       <c r="B46" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>135357133</v>
       </c>
       <c r="B47" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>135357142</v>
       </c>
       <c r="B48" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>135382782</v>
       </c>
       <c r="B49" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>135356855</v>
       </c>
       <c r="B50" t="n">
-        <v>92880</v>
+        <v>92882</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>135420258</v>
       </c>
       <c r="B51" t="n">
-        <v>92901</v>
+        <v>92903</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>135356208</v>
       </c>
       <c r="B52" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>135356239</v>
       </c>
       <c r="B53" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>135357118</v>
       </c>
       <c r="B55" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>135357124</v>
       </c>
       <c r="B56" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>135357203</v>
       </c>
       <c r="B57" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>135357207</v>
       </c>
       <c r="B58" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>135357208</v>
       </c>
       <c r="B59" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>135382719</v>
       </c>
       <c r="B60" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>135358275</v>
       </c>
       <c r="B61" t="n">
-        <v>87695</v>
+        <v>87697</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>135356210</v>
       </c>
       <c r="B62" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>135356372</v>
       </c>
       <c r="B63" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>135353513</v>
       </c>
       <c r="B64" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>135382469</v>
       </c>
       <c r="B87" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>135384124</v>
       </c>
       <c r="B88" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>135384162</v>
       </c>
       <c r="B89" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>135356843</v>
       </c>
       <c r="B91" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>135353481</v>
       </c>
       <c r="B92" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>135353512</v>
       </c>
       <c r="B93" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>135356205</v>
       </c>
       <c r="B94" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>135356241</v>
       </c>
       <c r="B95" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>135357137</v>
       </c>
       <c r="B96" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>135357141</v>
       </c>
       <c r="B97" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>135357201</v>
       </c>
       <c r="B98" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>135357211</v>
       </c>
       <c r="B99" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>135357212</v>
       </c>
       <c r="B100" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>135358269</v>
       </c>
       <c r="B101" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>135358276</v>
       </c>
       <c r="B102" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>135358292</v>
       </c>
       <c r="B103" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>135358342</v>
       </c>
       <c r="B104" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>135382720</v>
       </c>
       <c r="B105" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>135382723</v>
       </c>
       <c r="B106" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>135353491</v>
       </c>
       <c r="B107" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>135356209</v>
       </c>
       <c r="B108" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>135356218</v>
       </c>
       <c r="B109" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>135356839</v>
       </c>
       <c r="B110" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>135356886</v>
       </c>
       <c r="B111" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>135358270</v>
       </c>
       <c r="B112" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>135358287</v>
       </c>
       <c r="B113" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>135356206</v>
       </c>
       <c r="B114" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>135356243</v>
       </c>
       <c r="B115" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>135356845</v>
       </c>
       <c r="B116" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>135356884</v>
       </c>
       <c r="B117" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>135358281</v>
       </c>
       <c r="B118" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>135382031</v>
       </c>
       <c r="B119" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>135382032</v>
       </c>
       <c r="B120" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>135384245</v>
       </c>
       <c r="B121" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>135384249</v>
       </c>
       <c r="B122" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>135353486</v>
       </c>
       <c r="B123" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>135353494</v>
       </c>
       <c r="B124" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>135353497</v>
       </c>
       <c r="B125" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>135356211</v>
       </c>
       <c r="B126" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>135356213</v>
       </c>
       <c r="B127" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>135356844</v>
       </c>
       <c r="B128" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>135356846</v>
       </c>
       <c r="B129" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>135356856</v>
       </c>
       <c r="B130" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>135362163</v>
       </c>
       <c r="B131" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>135382721</v>
       </c>
       <c r="B132" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>135384251</v>
       </c>
       <c r="B133" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>135353490</v>
       </c>
       <c r="B134" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>135357136</v>
       </c>
       <c r="B135" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>135362160</v>
       </c>
       <c r="B136" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>135358271</v>
       </c>
       <c r="B137" t="n">
-        <v>99284</v>
+        <v>99286</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>135358274</v>
       </c>
       <c r="B138" t="n">
-        <v>99284</v>
+        <v>99286</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>135358278</v>
       </c>
       <c r="B139" t="n">
-        <v>99284</v>
+        <v>99286</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>135356838</v>
       </c>
       <c r="B140" t="n">
-        <v>98290</v>
+        <v>98292</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>135357146</v>
       </c>
       <c r="B141" t="n">
-        <v>98290</v>
+        <v>98292</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>135357209</v>
       </c>
       <c r="B142" t="n">
-        <v>98290</v>
+        <v>98292</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>135357123</v>
       </c>
       <c r="B143" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>135357202</v>
       </c>
       <c r="B144" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>135382713</v>
       </c>
       <c r="B145" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>135382724</v>
       </c>
       <c r="B146" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>135357122</v>
       </c>
       <c r="B147" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>135357145</v>
       </c>
       <c r="B148" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>135358277</v>
       </c>
       <c r="B149" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>135382718</v>
       </c>
       <c r="B150" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>135353482</v>
       </c>
       <c r="B151" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>135357117</v>
       </c>
       <c r="B152" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>135357120</v>
       </c>
       <c r="B153" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>135357138</v>
       </c>
       <c r="B154" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>135357140</v>
       </c>
       <c r="B155" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>135357147</v>
       </c>
       <c r="B156" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>135357205</v>
       </c>
       <c r="B157" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>135357206</v>
       </c>
       <c r="B158" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>135357213</v>
       </c>
       <c r="B159" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>135358268</v>
       </c>
       <c r="B160" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>135358284</v>
       </c>
       <c r="B161" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>135358293</v>
       </c>
       <c r="B162" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>135358341</v>
       </c>
       <c r="B163" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>135382388</v>
       </c>
       <c r="B164" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>135382712</v>
       </c>
       <c r="B165" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>135382717</v>
       </c>
       <c r="B166" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>135382722</v>
       </c>
       <c r="B167" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>135357130</v>
       </c>
       <c r="B168" t="n">
-        <v>102032</v>
+        <v>102034</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>135356852</v>
       </c>
       <c r="B169" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>135357134</v>
       </c>
       <c r="B170" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ170"/>
+  <dimension ref="A1:AZ169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6373,7 +6373,7 @@
         <v>135420258</v>
       </c>
       <c r="B51" t="n">
-        <v>92903</v>
+        <v>92918</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7572,51 +7572,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135358275</v>
+        <v>135356210</v>
       </c>
       <c r="B61" t="n">
-        <v>87697</v>
+        <v>92446</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3639</v>
+        <v>4217</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rutspindling</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius ionophyllus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>598533</v>
+        <v>598603</v>
       </c>
       <c r="R61" t="n">
-        <v>7330307</v>
+        <v>7330411</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7645,7 +7642,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7655,28 +7652,27 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF61" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7686,13 +7682,13 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358275</t>
+          <t>https://artportalen.se/Sighting/135356210</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135356210</v>
+        <v>135356372</v>
       </c>
       <c r="B62" t="n">
         <v>92446</v>
@@ -7723,17 +7719,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>598603</v>
+        <v>598544</v>
       </c>
       <c r="R62" t="n">
-        <v>7330411</v>
+        <v>7330366</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7762,7 +7758,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7772,7 +7768,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7787,12 +7783,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7802,16 +7798,16 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356210</t>
+          <t>https://artportalen.se/Sighting/135356372</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135356372</v>
+        <v>135353513</v>
       </c>
       <c r="B63" t="n">
-        <v>92446</v>
+        <v>92013</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7819,37 +7815,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>598544</v>
+        <v>598811</v>
       </c>
       <c r="R63" t="n">
-        <v>7330366</v>
+        <v>7330371</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7878,7 +7874,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7888,7 +7884,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7903,12 +7899,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7918,38 +7914,38 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356372</t>
+          <t>https://artportalen.se/Sighting/135353513</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135353513</v>
+        <v>135353495</v>
       </c>
       <c r="B64" t="n">
-        <v>92013</v>
+        <v>79441</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7959,10 +7955,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>598811</v>
+        <v>598630</v>
       </c>
       <c r="R64" t="n">
-        <v>7330371</v>
+        <v>7330381</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7994,7 +7990,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8004,7 +8000,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8034,13 +8030,13 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353513</t>
+          <t>https://artportalen.se/Sighting/135353495</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135353495</v>
+        <v>135353515</v>
       </c>
       <c r="B65" t="n">
         <v>79441</v>
@@ -8075,10 +8071,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>598630</v>
+        <v>598809</v>
       </c>
       <c r="R65" t="n">
-        <v>7330381</v>
+        <v>7330378</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8110,7 +8106,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8120,7 +8116,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8150,13 +8146,13 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353495</t>
+          <t>https://artportalen.se/Sighting/135353515</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135353515</v>
+        <v>135356240</v>
       </c>
       <c r="B66" t="n">
         <v>79441</v>
@@ -8187,14 +8183,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>598809</v>
+        <v>598519</v>
       </c>
       <c r="R66" t="n">
-        <v>7330378</v>
+        <v>7330561</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8226,7 +8222,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8236,7 +8232,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8251,12 +8247,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -8266,13 +8262,13 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353515</t>
+          <t>https://artportalen.se/Sighting/135356240</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135356240</v>
+        <v>135356837</v>
       </c>
       <c r="B67" t="n">
         <v>79441</v>
@@ -8303,17 +8299,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>598519</v>
+        <v>598555</v>
       </c>
       <c r="R67" t="n">
-        <v>7330561</v>
+        <v>7330375</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8342,7 +8338,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8352,7 +8348,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8367,12 +8363,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8382,13 +8378,13 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356240</t>
+          <t>https://artportalen.se/Sighting/135356837</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135356837</v>
+        <v>135382466</v>
       </c>
       <c r="B68" t="n">
         <v>79441</v>
@@ -8419,17 +8415,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>598555</v>
+        <v>598537</v>
       </c>
       <c r="R68" t="n">
-        <v>7330375</v>
+        <v>7330657</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8453,22 +8449,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8483,12 +8479,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8498,13 +8494,13 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356837</t>
+          <t>https://artportalen.se/Sighting/135382466</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135382466</v>
+        <v>135384252</v>
       </c>
       <c r="B69" t="n">
         <v>79441</v>
@@ -8535,17 +8531,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>598537</v>
+        <v>598474</v>
       </c>
       <c r="R69" t="n">
-        <v>7330657</v>
+        <v>7330641</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8574,7 +8570,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8584,7 +8580,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8599,12 +8595,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8614,54 +8610,54 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382466</t>
+          <t>https://artportalen.se/Sighting/135384252</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135384252</v>
+        <v>135353509</v>
       </c>
       <c r="B70" t="n">
-        <v>79441</v>
+        <v>83428</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>598474</v>
+        <v>598768</v>
       </c>
       <c r="R70" t="n">
-        <v>7330641</v>
+        <v>7330331</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8685,22 +8681,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8715,12 +8711,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8730,13 +8726,13 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384252</t>
+          <t>https://artportalen.se/Sighting/135353509</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135353509</v>
+        <v>135356841</v>
       </c>
       <c r="B71" t="n">
         <v>83428</v>
@@ -8767,14 +8763,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>598768</v>
+        <v>598580</v>
       </c>
       <c r="R71" t="n">
-        <v>7330331</v>
+        <v>7330406</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8806,7 +8802,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8816,7 +8812,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8831,12 +8827,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8846,54 +8842,54 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353509</t>
+          <t>https://artportalen.se/Sighting/135356841</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135356841</v>
+        <v>135357126</v>
       </c>
       <c r="B72" t="n">
-        <v>83428</v>
+        <v>80561</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>598580</v>
+        <v>598552</v>
       </c>
       <c r="R72" t="n">
-        <v>7330406</v>
+        <v>7330359</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8922,7 +8918,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8932,7 +8928,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8947,12 +8943,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8962,54 +8958,59 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356841</t>
+          <t>https://artportalen.se/Sighting/135357126</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135357126</v>
+        <v>135353488</v>
       </c>
       <c r="B73" t="n">
-        <v>80561</v>
+        <v>57980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>598552</v>
+        <v>598564</v>
       </c>
       <c r="R73" t="n">
-        <v>7330359</v>
+        <v>7330345</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9038,7 +9039,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9048,7 +9049,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9063,12 +9064,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -9078,13 +9079,13 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357126</t>
+          <t>https://artportalen.se/Sighting/135353488</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135353488</v>
+        <v>135353503</v>
       </c>
       <c r="B74" t="n">
         <v>57980</v>
@@ -9115,7 +9116,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9124,10 +9125,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>598564</v>
+        <v>598672</v>
       </c>
       <c r="R74" t="n">
-        <v>7330345</v>
+        <v>7330311</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9159,7 +9160,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9169,7 +9170,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9199,13 +9200,13 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353488</t>
+          <t>https://artportalen.se/Sighting/135353503</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135353503</v>
+        <v>135356216</v>
       </c>
       <c r="B75" t="n">
         <v>57980</v>
@@ -9234,24 +9235,19 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>598672</v>
+        <v>598747</v>
       </c>
       <c r="R75" t="n">
-        <v>7330311</v>
+        <v>7330309</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9280,7 +9276,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9290,7 +9286,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Gamla och nya ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9305,12 +9306,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -9320,13 +9321,13 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353503</t>
+          <t>https://artportalen.se/Sighting/135356216</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135356216</v>
+        <v>135356376</v>
       </c>
       <c r="B76" t="n">
         <v>57980</v>
@@ -9355,19 +9356,27 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>598747</v>
+        <v>598614</v>
       </c>
       <c r="R76" t="n">
-        <v>7330309</v>
+        <v>7330356</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9396,7 +9405,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9406,19 +9415,19 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Gamla och nya ringhack</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
@@ -9426,12 +9435,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -9441,13 +9450,13 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356216</t>
+          <t>https://artportalen.se/Sighting/135356376</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135356376</v>
+        <v>135356380</v>
       </c>
       <c r="B77" t="n">
         <v>57980</v>
@@ -9490,13 +9499,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>598614</v>
+        <v>598877</v>
       </c>
       <c r="R77" t="n">
-        <v>7330356</v>
+        <v>7330349</v>
       </c>
       <c r="S77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9525,7 +9534,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9535,19 +9544,19 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="b">
         <v>0</v>
@@ -9560,7 +9569,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9570,13 +9579,13 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356376</t>
+          <t>https://artportalen.se/Sighting/135356380</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135356380</v>
+        <v>135357127</v>
       </c>
       <c r="B78" t="n">
         <v>57980</v>
@@ -9605,27 +9614,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>598877</v>
+        <v>598569</v>
       </c>
       <c r="R78" t="n">
-        <v>7330349</v>
+        <v>7330352</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9654,7 +9655,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9664,12 +9665,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9684,12 +9685,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9699,13 +9700,13 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356380</t>
+          <t>https://artportalen.se/Sighting/135357127</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135357127</v>
+        <v>135358283</v>
       </c>
       <c r="B79" t="n">
         <v>57980</v>
@@ -9736,17 +9737,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>598569</v>
+        <v>598609</v>
       </c>
       <c r="R79" t="n">
-        <v>7330352</v>
+        <v>7330298</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9775,7 +9776,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9785,7 +9786,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -9805,12 +9806,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9820,13 +9821,13 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357127</t>
+          <t>https://artportalen.se/Sighting/135358283</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135358283</v>
+        <v>135382716</v>
       </c>
       <c r="B80" t="n">
         <v>57980</v>
@@ -9855,19 +9856,27 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>598609</v>
+        <v>598482</v>
       </c>
       <c r="R80" t="n">
-        <v>7330298</v>
+        <v>7330489</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9891,27 +9900,27 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9926,12 +9935,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9941,13 +9950,13 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358283</t>
+          <t>https://artportalen.se/Sighting/135382716</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135382716</v>
+        <v>135382779</v>
       </c>
       <c r="B81" t="n">
         <v>57980</v>
@@ -9980,7 +9989,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -9990,10 +9999,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>598482</v>
+        <v>598462</v>
       </c>
       <c r="R81" t="n">
-        <v>7330489</v>
+        <v>7330447</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10025,7 +10034,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10035,12 +10044,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10070,13 +10079,13 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382716</t>
+          <t>https://artportalen.se/Sighting/135382779</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135382779</v>
+        <v>135384126</v>
       </c>
       <c r="B82" t="n">
         <v>57980</v>
@@ -10119,10 +10128,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>598462</v>
+        <v>598485</v>
       </c>
       <c r="R82" t="n">
-        <v>7330447</v>
+        <v>7330673</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10154,7 +10163,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10164,19 +10173,19 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG82" t="b">
         <v>0</v>
@@ -10184,12 +10193,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -10199,16 +10208,16 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382779</t>
+          <t>https://artportalen.se/Sighting/135384126</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135384126</v>
+        <v>135357215</v>
       </c>
       <c r="B83" t="n">
-        <v>57980</v>
+        <v>58141</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10216,21 +10225,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10238,20 +10247,20 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>598485</v>
+        <v>598501</v>
       </c>
       <c r="R83" t="n">
-        <v>7330673</v>
+        <v>7330475</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10278,34 +10287,34 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="b">
         <v>0</v>
@@ -10313,12 +10322,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -10328,13 +10337,13 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384126</t>
+          <t>https://artportalen.se/Sighting/135357215</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135357215</v>
+        <v>135382711</v>
       </c>
       <c r="B84" t="n">
         <v>58141</v>
@@ -10373,14 +10382,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>598501</v>
+        <v>598464</v>
       </c>
       <c r="R84" t="n">
-        <v>7330475</v>
+        <v>7330416</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10407,27 +10416,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10457,13 +10461,13 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357215</t>
+          <t>https://artportalen.se/Sighting/135382711</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135382711</v>
+        <v>135385939</v>
       </c>
       <c r="B85" t="n">
         <v>58141</v>
@@ -10492,24 +10496,16 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>598464</v>
+        <v>598491</v>
       </c>
       <c r="R85" t="n">
-        <v>7330416</v>
+        <v>7330361</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10541,7 +10537,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10551,7 +10547,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10566,12 +10562,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -10581,54 +10577,54 @@
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382711</t>
+          <t>https://artportalen.se/Sighting/135385939</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135385939</v>
+        <v>135382469</v>
       </c>
       <c r="B86" t="n">
-        <v>58141</v>
+        <v>99193</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>598491</v>
+        <v>598453</v>
       </c>
       <c r="R86" t="n">
-        <v>7330361</v>
+        <v>7330444</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10657,7 +10653,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10667,7 +10663,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10682,12 +10678,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10697,13 +10693,13 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135385939</t>
+          <t>https://artportalen.se/Sighting/135382469</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135382469</v>
+        <v>135384124</v>
       </c>
       <c r="B87" t="n">
         <v>99193</v>
@@ -10734,17 +10730,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>598453</v>
+        <v>598499</v>
       </c>
       <c r="R87" t="n">
-        <v>7330444</v>
+        <v>7330637</v>
       </c>
       <c r="S87" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10773,7 +10769,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10783,7 +10779,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10798,12 +10794,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10813,13 +10809,13 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382469</t>
+          <t>https://artportalen.se/Sighting/135384124</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135384124</v>
+        <v>135384162</v>
       </c>
       <c r="B88" t="n">
         <v>99193</v>
@@ -10854,10 +10850,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>598499</v>
+        <v>598449</v>
       </c>
       <c r="R88" t="n">
-        <v>7330637</v>
+        <v>7330355</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10889,7 +10885,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10899,7 +10895,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10929,16 +10925,16 @@
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384124</t>
+          <t>https://artportalen.se/Sighting/135384162</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135384162</v>
+        <v>94770073</v>
       </c>
       <c r="B89" t="n">
-        <v>99193</v>
+        <v>99120</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10946,37 +10942,43 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Laisan, Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>598449</v>
+        <v>598453</v>
       </c>
       <c r="R89" t="n">
-        <v>7330355</v>
+        <v>7330315</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11000,22 +11002,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11030,31 +11022,27 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Thomas Strid, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384162</t>
+          <t>https://artportalen.se/Sighting/94770073</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>94770073</v>
+        <v>135356843</v>
       </c>
       <c r="B90" t="n">
-        <v>99120</v>
+        <v>99180</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11062,43 +11050,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219811</v>
+        <v>220093</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Laisan, Arjeplog, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>598453</v>
+        <v>598607</v>
       </c>
       <c r="R90" t="n">
-        <v>7330315</v>
+        <v>7330382</v>
       </c>
       <c r="S90" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11122,12 +11104,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11142,27 +11134,31 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Thomas Strid, Tiina Laantee</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94770073</t>
+          <t>https://artportalen.se/Sighting/135356843</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135356843</v>
+        <v>135353481</v>
       </c>
       <c r="B91" t="n">
-        <v>99180</v>
+        <v>110014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11170,34 +11166,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220093</v>
+        <v>221184</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>598607</v>
+        <v>598529</v>
       </c>
       <c r="R91" t="n">
-        <v>7330382</v>
+        <v>7330341</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -11229,7 +11225,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11239,7 +11235,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11254,12 +11250,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11269,13 +11265,13 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356843</t>
+          <t>https://artportalen.se/Sighting/135353481</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135353481</v>
+        <v>135353512</v>
       </c>
       <c r="B92" t="n">
         <v>110014</v>
@@ -11310,10 +11306,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>598529</v>
+        <v>598793</v>
       </c>
       <c r="R92" t="n">
-        <v>7330341</v>
+        <v>7330350</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -11345,7 +11341,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11355,7 +11351,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11385,13 +11381,13 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353481</t>
+          <t>https://artportalen.se/Sighting/135353512</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135353512</v>
+        <v>135356205</v>
       </c>
       <c r="B93" t="n">
         <v>110014</v>
@@ -11422,14 +11418,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>598793</v>
+        <v>598518</v>
       </c>
       <c r="R93" t="n">
-        <v>7330350</v>
+        <v>7330341</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11461,7 +11457,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11471,7 +11467,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11486,12 +11482,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -11501,13 +11497,13 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353512</t>
+          <t>https://artportalen.se/Sighting/135356205</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135356205</v>
+        <v>135356241</v>
       </c>
       <c r="B94" t="n">
         <v>110014</v>
@@ -11542,10 +11538,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>598518</v>
+        <v>598490</v>
       </c>
       <c r="R94" t="n">
-        <v>7330341</v>
+        <v>7330565</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11577,7 +11573,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11587,7 +11583,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11617,13 +11613,13 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356205</t>
+          <t>https://artportalen.se/Sighting/135356241</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135356241</v>
+        <v>135357137</v>
       </c>
       <c r="B95" t="n">
         <v>110014</v>
@@ -11654,17 +11650,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>598490</v>
+        <v>598751</v>
       </c>
       <c r="R95" t="n">
-        <v>7330565</v>
+        <v>7330316</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11693,7 +11689,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11703,7 +11699,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11718,12 +11714,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11733,13 +11729,13 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356241</t>
+          <t>https://artportalen.se/Sighting/135357137</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135357137</v>
+        <v>135357141</v>
       </c>
       <c r="B96" t="n">
         <v>110014</v>
@@ -11774,10 +11770,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>598751</v>
+        <v>598770</v>
       </c>
       <c r="R96" t="n">
-        <v>7330316</v>
+        <v>7330338</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11809,7 +11805,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11819,7 +11815,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11849,13 +11845,13 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357137</t>
+          <t>https://artportalen.se/Sighting/135357141</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135357141</v>
+        <v>135357201</v>
       </c>
       <c r="B97" t="n">
         <v>110014</v>
@@ -11890,10 +11886,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>598770</v>
+        <v>598553</v>
       </c>
       <c r="R97" t="n">
-        <v>7330338</v>
+        <v>7330578</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11925,7 +11921,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11935,7 +11931,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11965,13 +11961,13 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357141</t>
+          <t>https://artportalen.se/Sighting/135357201</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135357201</v>
+        <v>135357211</v>
       </c>
       <c r="B98" t="n">
         <v>110014</v>
@@ -12006,10 +12002,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>598553</v>
+        <v>598501</v>
       </c>
       <c r="R98" t="n">
-        <v>7330578</v>
+        <v>7330515</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12041,7 +12037,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12051,7 +12047,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12081,13 +12077,13 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357201</t>
+          <t>https://artportalen.se/Sighting/135357211</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135357211</v>
+        <v>135357212</v>
       </c>
       <c r="B99" t="n">
         <v>110014</v>
@@ -12122,10 +12118,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>598501</v>
+        <v>598498</v>
       </c>
       <c r="R99" t="n">
-        <v>7330515</v>
+        <v>7330492</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12157,7 +12153,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12167,7 +12163,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12197,13 +12193,13 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357211</t>
+          <t>https://artportalen.se/Sighting/135357212</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135357212</v>
+        <v>135358269</v>
       </c>
       <c r="B100" t="n">
         <v>110014</v>
@@ -12234,17 +12230,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>598498</v>
+        <v>598578</v>
       </c>
       <c r="R100" t="n">
-        <v>7330492</v>
+        <v>7330329</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12273,7 +12269,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12283,7 +12279,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12298,12 +12294,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12313,13 +12309,13 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357212</t>
+          <t>https://artportalen.se/Sighting/135358269</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135358269</v>
+        <v>135358276</v>
       </c>
       <c r="B101" t="n">
         <v>110014</v>
@@ -12354,10 +12350,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>598578</v>
+        <v>598542</v>
       </c>
       <c r="R101" t="n">
-        <v>7330329</v>
+        <v>7330305</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12389,7 +12385,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12399,7 +12395,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12429,13 +12425,13 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358269</t>
+          <t>https://artportalen.se/Sighting/135358276</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135358276</v>
+        <v>135358292</v>
       </c>
       <c r="B102" t="n">
         <v>110014</v>
@@ -12470,10 +12466,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>598542</v>
+        <v>598827</v>
       </c>
       <c r="R102" t="n">
-        <v>7330305</v>
+        <v>7330278</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12505,7 +12501,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12515,7 +12511,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12545,13 +12541,13 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358276</t>
+          <t>https://artportalen.se/Sighting/135358292</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135358292</v>
+        <v>135358342</v>
       </c>
       <c r="B103" t="n">
         <v>110014</v>
@@ -12586,10 +12582,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>598827</v>
+        <v>598546</v>
       </c>
       <c r="R103" t="n">
-        <v>7330278</v>
+        <v>7330653</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12621,7 +12617,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12631,7 +12627,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12661,13 +12657,13 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358292</t>
+          <t>https://artportalen.se/Sighting/135358342</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135358342</v>
+        <v>135382720</v>
       </c>
       <c r="B104" t="n">
         <v>110014</v>
@@ -12698,17 +12694,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>598546</v>
+        <v>598507</v>
       </c>
       <c r="R104" t="n">
-        <v>7330653</v>
+        <v>7330626</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12732,22 +12728,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12762,12 +12758,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12777,13 +12773,13 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358342</t>
+          <t>https://artportalen.se/Sighting/135382720</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135382720</v>
+        <v>135382723</v>
       </c>
       <c r="B105" t="n">
         <v>110014</v>
@@ -12818,10 +12814,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>598507</v>
+        <v>598467</v>
       </c>
       <c r="R105" t="n">
-        <v>7330626</v>
+        <v>7330649</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12853,7 +12849,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12863,7 +12859,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12893,16 +12889,16 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382720</t>
+          <t>https://artportalen.se/Sighting/135382723</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135382723</v>
+        <v>135353491</v>
       </c>
       <c r="B106" t="n">
-        <v>110014</v>
+        <v>106398</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12910,16 +12906,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221184</v>
+        <v>221725</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -12930,17 +12926,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>598467</v>
+        <v>598592</v>
       </c>
       <c r="R106" t="n">
-        <v>7330649</v>
+        <v>7330348</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12964,22 +12960,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12994,12 +12990,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -13009,13 +13005,13 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382723</t>
+          <t>https://artportalen.se/Sighting/135353491</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135353491</v>
+        <v>135356209</v>
       </c>
       <c r="B107" t="n">
         <v>106398</v>
@@ -13046,14 +13042,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>598592</v>
+        <v>598597</v>
       </c>
       <c r="R107" t="n">
-        <v>7330348</v>
+        <v>7330383</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -13085,7 +13081,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13095,7 +13091,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13110,12 +13106,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -13125,13 +13121,13 @@
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353491</t>
+          <t>https://artportalen.se/Sighting/135356209</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135356209</v>
+        <v>135356218</v>
       </c>
       <c r="B108" t="n">
         <v>106398</v>
@@ -13166,10 +13162,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>598597</v>
+        <v>598785</v>
       </c>
       <c r="R108" t="n">
-        <v>7330383</v>
+        <v>7330366</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -13201,7 +13197,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13211,7 +13207,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13241,13 +13237,13 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356209</t>
+          <t>https://artportalen.se/Sighting/135356218</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135356218</v>
+        <v>135356839</v>
       </c>
       <c r="B109" t="n">
         <v>106398</v>
@@ -13278,17 +13274,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>598785</v>
+        <v>598557</v>
       </c>
       <c r="R109" t="n">
-        <v>7330366</v>
+        <v>7330411</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13317,7 +13313,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13327,7 +13323,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13342,12 +13338,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -13357,13 +13353,13 @@
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356218</t>
+          <t>https://artportalen.se/Sighting/135356839</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135356839</v>
+        <v>135356886</v>
       </c>
       <c r="B110" t="n">
         <v>106398</v>
@@ -13398,13 +13394,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>598557</v>
+        <v>598518</v>
       </c>
       <c r="R110" t="n">
-        <v>7330411</v>
+        <v>7330476</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13433,7 +13429,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13443,7 +13439,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13473,13 +13469,13 @@
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356839</t>
+          <t>https://artportalen.se/Sighting/135356886</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135356886</v>
+        <v>135358270</v>
       </c>
       <c r="B111" t="n">
         <v>106398</v>
@@ -13510,17 +13506,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>598518</v>
+        <v>598568</v>
       </c>
       <c r="R111" t="n">
-        <v>7330476</v>
+        <v>7330339</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13549,7 +13545,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13559,7 +13555,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13574,12 +13570,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -13589,13 +13585,13 @@
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356886</t>
+          <t>https://artportalen.se/Sighting/135358270</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135358270</v>
+        <v>135358287</v>
       </c>
       <c r="B112" t="n">
         <v>106398</v>
@@ -13630,10 +13626,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>598568</v>
+        <v>598754</v>
       </c>
       <c r="R112" t="n">
-        <v>7330339</v>
+        <v>7330326</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13665,7 +13661,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13675,7 +13671,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13705,16 +13701,16 @@
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358270</t>
+          <t>https://artportalen.se/Sighting/135358287</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135358287</v>
+        <v>135356206</v>
       </c>
       <c r="B113" t="n">
-        <v>106398</v>
+        <v>98138</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13722,37 +13718,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>598754</v>
+        <v>598569</v>
       </c>
       <c r="R113" t="n">
-        <v>7330326</v>
+        <v>7330354</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13781,7 +13777,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13791,7 +13787,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13806,12 +13802,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13821,13 +13817,13 @@
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358287</t>
+          <t>https://artportalen.se/Sighting/135356206</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135356206</v>
+        <v>135356243</v>
       </c>
       <c r="B114" t="n">
         <v>98138</v>
@@ -13862,10 +13858,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>598569</v>
+        <v>598482</v>
       </c>
       <c r="R114" t="n">
-        <v>7330354</v>
+        <v>7330539</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13897,7 +13893,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13907,7 +13903,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13937,13 +13933,13 @@
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356206</t>
+          <t>https://artportalen.se/Sighting/135356243</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135356243</v>
+        <v>135356845</v>
       </c>
       <c r="B115" t="n">
         <v>98138</v>
@@ -13974,17 +13970,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>598482</v>
+        <v>598624</v>
       </c>
       <c r="R115" t="n">
-        <v>7330539</v>
+        <v>7330372</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14013,7 +14009,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14023,7 +14019,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14038,12 +14034,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -14053,13 +14049,13 @@
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356243</t>
+          <t>https://artportalen.se/Sighting/135356845</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135356845</v>
+        <v>135356884</v>
       </c>
       <c r="B116" t="n">
         <v>98138</v>
@@ -14094,13 +14090,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>598624</v>
+        <v>598495</v>
       </c>
       <c r="R116" t="n">
-        <v>7330372</v>
+        <v>7330628</v>
       </c>
       <c r="S116" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14129,7 +14125,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14139,7 +14135,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14169,13 +14165,13 @@
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356845</t>
+          <t>https://artportalen.se/Sighting/135356884</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135356884</v>
+        <v>135358281</v>
       </c>
       <c r="B117" t="n">
         <v>98138</v>
@@ -14206,14 +14202,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>598495</v>
+        <v>598605</v>
       </c>
       <c r="R117" t="n">
-        <v>7330628</v>
+        <v>7330324</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14245,7 +14241,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14255,7 +14251,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14270,12 +14266,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -14285,13 +14281,13 @@
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356884</t>
+          <t>https://artportalen.se/Sighting/135358281</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135358281</v>
+        <v>135382031</v>
       </c>
       <c r="B118" t="n">
         <v>98138</v>
@@ -14322,17 +14318,17 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>598605</v>
+        <v>598459</v>
       </c>
       <c r="R118" t="n">
-        <v>7330324</v>
+        <v>7330572</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14356,22 +14352,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14386,12 +14382,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -14401,13 +14397,13 @@
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358281</t>
+          <t>https://artportalen.se/Sighting/135382031</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135382031</v>
+        <v>135382032</v>
       </c>
       <c r="B119" t="n">
         <v>98138</v>
@@ -14442,13 +14438,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>598459</v>
+        <v>598472</v>
       </c>
       <c r="R119" t="n">
-        <v>7330572</v>
+        <v>7330674</v>
       </c>
       <c r="S119" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14517,13 +14513,13 @@
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382031</t>
+          <t>https://artportalen.se/Sighting/135382032</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135382032</v>
+        <v>135384245</v>
       </c>
       <c r="B120" t="n">
         <v>98138</v>
@@ -14554,14 +14550,14 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>598472</v>
+        <v>598522</v>
       </c>
       <c r="R120" t="n">
-        <v>7330674</v>
+        <v>7330575</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14593,7 +14589,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14603,7 +14599,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14618,12 +14614,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -14633,13 +14629,13 @@
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382032</t>
+          <t>https://artportalen.se/Sighting/135384245</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135384245</v>
+        <v>135384249</v>
       </c>
       <c r="B121" t="n">
         <v>98138</v>
@@ -14674,13 +14670,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>598522</v>
+        <v>598492</v>
       </c>
       <c r="R121" t="n">
-        <v>7330575</v>
+        <v>7330652</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14709,7 +14705,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14719,7 +14715,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14749,16 +14745,16 @@
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384245</t>
+          <t>https://artportalen.se/Sighting/135384249</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135384249</v>
+        <v>135353486</v>
       </c>
       <c r="B122" t="n">
-        <v>98138</v>
+        <v>99298</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14766,37 +14762,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>598492</v>
+        <v>598555</v>
       </c>
       <c r="R122" t="n">
-        <v>7330652</v>
+        <v>7330349</v>
       </c>
       <c r="S122" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14820,22 +14816,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14850,12 +14846,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -14865,13 +14861,13 @@
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384249</t>
+          <t>https://artportalen.se/Sighting/135353486</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135353486</v>
+        <v>135353494</v>
       </c>
       <c r="B123" t="n">
         <v>99298</v>
@@ -14906,10 +14902,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>598555</v>
+        <v>598634</v>
       </c>
       <c r="R123" t="n">
-        <v>7330349</v>
+        <v>7330375</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14941,7 +14937,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14951,7 +14947,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14981,13 +14977,13 @@
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353486</t>
+          <t>https://artportalen.se/Sighting/135353494</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135353494</v>
+        <v>135353497</v>
       </c>
       <c r="B124" t="n">
         <v>99298</v>
@@ -15022,10 +15018,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>598634</v>
+        <v>598665</v>
       </c>
       <c r="R124" t="n">
-        <v>7330375</v>
+        <v>7330360</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -15057,7 +15053,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15067,7 +15063,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15097,13 +15093,13 @@
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353494</t>
+          <t>https://artportalen.se/Sighting/135353497</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135353497</v>
+        <v>135356211</v>
       </c>
       <c r="B125" t="n">
         <v>99298</v>
@@ -15134,14 +15130,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>598665</v>
+        <v>598644</v>
       </c>
       <c r="R125" t="n">
-        <v>7330360</v>
+        <v>7330364</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15173,7 +15169,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15183,7 +15179,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15198,12 +15194,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -15213,13 +15209,13 @@
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353497</t>
+          <t>https://artportalen.se/Sighting/135356211</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135356211</v>
+        <v>135356213</v>
       </c>
       <c r="B126" t="n">
         <v>99298</v>
@@ -15254,13 +15250,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>598644</v>
+        <v>598651</v>
       </c>
       <c r="R126" t="n">
-        <v>7330364</v>
+        <v>7330373</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15289,7 +15285,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15299,7 +15295,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15329,13 +15325,13 @@
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356211</t>
+          <t>https://artportalen.se/Sighting/135356213</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135356213</v>
+        <v>135356844</v>
       </c>
       <c r="B127" t="n">
         <v>99298</v>
@@ -15366,17 +15362,17 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>598651</v>
+        <v>598607</v>
       </c>
       <c r="R127" t="n">
-        <v>7330373</v>
+        <v>7330382</v>
       </c>
       <c r="S127" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15405,7 +15401,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15415,7 +15411,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15430,12 +15426,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -15445,13 +15441,13 @@
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356213</t>
+          <t>https://artportalen.se/Sighting/135356844</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135356844</v>
+        <v>135356846</v>
       </c>
       <c r="B128" t="n">
         <v>99298</v>
@@ -15486,10 +15482,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>598607</v>
+        <v>598653</v>
       </c>
       <c r="R128" t="n">
-        <v>7330382</v>
+        <v>7330343</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15521,7 +15517,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15531,7 +15527,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15561,13 +15557,13 @@
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356844</t>
+          <t>https://artportalen.se/Sighting/135356846</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>135356846</v>
+        <v>135356856</v>
       </c>
       <c r="B129" t="n">
         <v>99298</v>
@@ -15602,13 +15598,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>598653</v>
+        <v>598841</v>
       </c>
       <c r="R129" t="n">
-        <v>7330343</v>
+        <v>7330355</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15637,7 +15633,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15647,7 +15643,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15677,13 +15673,13 @@
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356846</t>
+          <t>https://artportalen.se/Sighting/135356856</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>135356856</v>
+        <v>135362163</v>
       </c>
       <c r="B130" t="n">
         <v>99298</v>
@@ -15714,17 +15710,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>598841</v>
+        <v>598808</v>
       </c>
       <c r="R130" t="n">
-        <v>7330355</v>
+        <v>7330337</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15751,19 +15747,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>11:49</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15778,12 +15764,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -15793,13 +15779,13 @@
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356856</t>
+          <t>https://artportalen.se/Sighting/135362163</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>135362163</v>
+        <v>135382721</v>
       </c>
       <c r="B131" t="n">
         <v>99298</v>
@@ -15830,17 +15816,17 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>598808</v>
+        <v>598467</v>
       </c>
       <c r="R131" t="n">
-        <v>7330337</v>
+        <v>7330649</v>
       </c>
       <c r="S131" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15864,12 +15850,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15884,12 +15880,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -15899,13 +15895,13 @@
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135362163</t>
+          <t>https://artportalen.se/Sighting/135382721</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>135382721</v>
+        <v>135384251</v>
       </c>
       <c r="B132" t="n">
         <v>99298</v>
@@ -15936,14 +15932,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>598467</v>
+        <v>598482</v>
       </c>
       <c r="R132" t="n">
-        <v>7330649</v>
+        <v>7330639</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15975,7 +15971,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15985,7 +15981,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16000,12 +15996,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -16015,16 +16011,16 @@
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382721</t>
+          <t>https://artportalen.se/Sighting/135384251</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135384251</v>
+        <v>135353490</v>
       </c>
       <c r="B133" t="n">
-        <v>99298</v>
+        <v>104795</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16032,37 +16028,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221952</v>
+        <v>222412</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>598482</v>
+        <v>598591</v>
       </c>
       <c r="R133" t="n">
-        <v>7330639</v>
+        <v>7330353</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16086,22 +16082,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16116,12 +16112,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -16131,13 +16127,13 @@
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384251</t>
+          <t>https://artportalen.se/Sighting/135353490</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>135353490</v>
+        <v>135357136</v>
       </c>
       <c r="B134" t="n">
         <v>104795</v>
@@ -16168,17 +16164,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>598591</v>
+        <v>598751</v>
       </c>
       <c r="R134" t="n">
-        <v>7330353</v>
+        <v>7330316</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16207,7 +16203,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16217,7 +16213,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16232,12 +16228,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -16247,13 +16243,13 @@
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353490</t>
+          <t>https://artportalen.se/Sighting/135357136</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>135357136</v>
+        <v>135362160</v>
       </c>
       <c r="B135" t="n">
         <v>104795</v>
@@ -16288,13 +16284,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>598751</v>
+        <v>598552</v>
       </c>
       <c r="R135" t="n">
-        <v>7330316</v>
+        <v>7330368</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16321,19 +16317,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16348,12 +16334,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -16363,16 +16349,16 @@
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357136</t>
+          <t>https://artportalen.se/Sighting/135362160</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135362160</v>
+        <v>135358271</v>
       </c>
       <c r="B136" t="n">
-        <v>104795</v>
+        <v>99286</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16380,37 +16366,41 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>222412</v>
+        <v>222495</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Myggblomster</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hammarbya paludosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Kuntze</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>598552</v>
+        <v>598585</v>
       </c>
       <c r="R136" t="n">
-        <v>7330368</v>
+        <v>7330354</v>
       </c>
       <c r="S136" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16437,29 +16427,40 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -16469,13 +16470,13 @@
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135362160</t>
+          <t>https://artportalen.se/Sighting/135358271</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>135358271</v>
+        <v>135358274</v>
       </c>
       <c r="B137" t="n">
         <v>99286</v>
@@ -16514,13 +16515,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>598585</v>
+        <v>598543</v>
       </c>
       <c r="R137" t="n">
-        <v>7330354</v>
+        <v>7330322</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16549,7 +16550,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16559,7 +16560,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16590,13 +16591,13 @@
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358271</t>
+          <t>https://artportalen.se/Sighting/135358274</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>135358274</v>
+        <v>135358278</v>
       </c>
       <c r="B138" t="n">
         <v>99286</v>
@@ -16635,13 +16636,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>598543</v>
+        <v>598566</v>
       </c>
       <c r="R138" t="n">
-        <v>7330322</v>
+        <v>7330282</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16670,7 +16671,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16680,7 +16681,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16711,16 +16712,16 @@
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358274</t>
+          <t>https://artportalen.se/Sighting/135358278</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>135358278</v>
+        <v>135356838</v>
       </c>
       <c r="B139" t="n">
-        <v>99286</v>
+        <v>98292</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16728,41 +16729,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>222495</v>
+        <v>222741</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Myggblomster</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hammarbya paludosa</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Kuntze</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>598566</v>
+        <v>598555</v>
       </c>
       <c r="R139" t="n">
-        <v>7330282</v>
+        <v>7330375</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16791,7 +16788,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16801,7 +16798,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16810,19 +16807,18 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -16832,13 +16828,13 @@
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358278</t>
+          <t>https://artportalen.se/Sighting/135356838</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>135356838</v>
+        <v>135357146</v>
       </c>
       <c r="B140" t="n">
         <v>98292</v>
@@ -16869,17 +16865,17 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>598555</v>
+        <v>598911</v>
       </c>
       <c r="R140" t="n">
-        <v>7330375</v>
+        <v>7330350</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16908,7 +16904,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16918,7 +16914,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16933,12 +16929,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -16948,13 +16944,13 @@
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356838</t>
+          <t>https://artportalen.se/Sighting/135357146</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>135357146</v>
+        <v>135357209</v>
       </c>
       <c r="B141" t="n">
         <v>98292</v>
@@ -16989,10 +16985,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>598911</v>
+        <v>598519</v>
       </c>
       <c r="R141" t="n">
-        <v>7330350</v>
+        <v>7330570</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17024,7 +17020,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17034,7 +17030,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17064,16 +17060,16 @@
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357146</t>
+          <t>https://artportalen.se/Sighting/135357209</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>135357209</v>
+        <v>135357123</v>
       </c>
       <c r="B142" t="n">
-        <v>98292</v>
+        <v>102956</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17081,21 +17077,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>222741</v>
+        <v>223037</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -17105,10 +17101,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>598519</v>
+        <v>598552</v>
       </c>
       <c r="R142" t="n">
-        <v>7330570</v>
+        <v>7330359</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17140,7 +17136,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17150,7 +17146,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17180,13 +17176,13 @@
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357209</t>
+          <t>https://artportalen.se/Sighting/135357123</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>135357123</v>
+        <v>135357202</v>
       </c>
       <c r="B143" t="n">
         <v>102956</v>
@@ -17221,10 +17217,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>598552</v>
+        <v>598553</v>
       </c>
       <c r="R143" t="n">
-        <v>7330359</v>
+        <v>7330578</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17256,7 +17252,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17266,7 +17262,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17296,13 +17292,13 @@
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357123</t>
+          <t>https://artportalen.se/Sighting/135357202</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>135357202</v>
+        <v>135382713</v>
       </c>
       <c r="B144" t="n">
         <v>102956</v>
@@ -17333,14 +17329,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>598553</v>
+        <v>598464</v>
       </c>
       <c r="R144" t="n">
-        <v>7330578</v>
+        <v>7330416</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17367,22 +17363,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17412,13 +17408,13 @@
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357202</t>
+          <t>https://artportalen.se/Sighting/135382713</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>135382713</v>
+        <v>135382724</v>
       </c>
       <c r="B145" t="n">
         <v>102956</v>
@@ -17453,10 +17449,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>598464</v>
+        <v>598467</v>
       </c>
       <c r="R145" t="n">
-        <v>7330416</v>
+        <v>7330649</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17488,7 +17484,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -17498,7 +17494,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17528,16 +17524,16 @@
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382713</t>
+          <t>https://artportalen.se/Sighting/135382724</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>135382724</v>
+        <v>135357122</v>
       </c>
       <c r="B146" t="n">
-        <v>102956</v>
+        <v>98327</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17545,34 +17541,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>223037</v>
+        <v>223358</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>598467</v>
+        <v>598552</v>
       </c>
       <c r="R146" t="n">
-        <v>7330649</v>
+        <v>7330359</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17599,22 +17595,22 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17644,13 +17640,13 @@
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382724</t>
+          <t>https://artportalen.se/Sighting/135357122</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>135357122</v>
+        <v>135357145</v>
       </c>
       <c r="B147" t="n">
         <v>98327</v>
@@ -17685,10 +17681,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>598552</v>
+        <v>598911</v>
       </c>
       <c r="R147" t="n">
-        <v>7330359</v>
+        <v>7330350</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17720,7 +17716,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17730,7 +17726,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17760,13 +17756,13 @@
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357122</t>
+          <t>https://artportalen.se/Sighting/135357145</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>135357145</v>
+        <v>135358277</v>
       </c>
       <c r="B148" t="n">
         <v>98327</v>
@@ -17797,17 +17793,17 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>598911</v>
+        <v>598551</v>
       </c>
       <c r="R148" t="n">
-        <v>7330350</v>
+        <v>7330296</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17836,7 +17832,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17846,7 +17842,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17861,12 +17857,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -17876,13 +17872,13 @@
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357145</t>
+          <t>https://artportalen.se/Sighting/135358277</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>135358277</v>
+        <v>135382718</v>
       </c>
       <c r="B149" t="n">
         <v>98327</v>
@@ -17913,17 +17909,17 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>598551</v>
+        <v>598507</v>
       </c>
       <c r="R149" t="n">
-        <v>7330296</v>
+        <v>7330626</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17947,22 +17943,22 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17977,12 +17973,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -17992,16 +17988,16 @@
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358277</t>
+          <t>https://artportalen.se/Sighting/135382718</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>135382718</v>
+        <v>135353482</v>
       </c>
       <c r="B150" t="n">
-        <v>98327</v>
+        <v>101375</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18009,37 +18005,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>598507</v>
+        <v>598530</v>
       </c>
       <c r="R150" t="n">
-        <v>7330626</v>
+        <v>7330340</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18063,22 +18059,22 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18093,12 +18089,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -18108,13 +18104,13 @@
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382718</t>
+          <t>https://artportalen.se/Sighting/135353482</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>135353482</v>
+        <v>135357117</v>
       </c>
       <c r="B151" t="n">
         <v>101375</v>
@@ -18145,17 +18141,17 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>598530</v>
+        <v>598525</v>
       </c>
       <c r="R151" t="n">
-        <v>7330340</v>
+        <v>7330346</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -18209,12 +18205,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -18224,13 +18220,13 @@
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353482</t>
+          <t>https://artportalen.se/Sighting/135357117</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>135357117</v>
+        <v>135357120</v>
       </c>
       <c r="B152" t="n">
         <v>101375</v>
@@ -18265,10 +18261,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>598525</v>
+        <v>598552</v>
       </c>
       <c r="R152" t="n">
-        <v>7330346</v>
+        <v>7330359</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18300,7 +18296,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18310,7 +18306,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18340,13 +18336,13 @@
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357117</t>
+          <t>https://artportalen.se/Sighting/135357120</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>135357120</v>
+        <v>135357138</v>
       </c>
       <c r="B153" t="n">
         <v>101375</v>
@@ -18381,10 +18377,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>598552</v>
+        <v>598751</v>
       </c>
       <c r="R153" t="n">
-        <v>7330359</v>
+        <v>7330316</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18416,7 +18412,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18426,7 +18422,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18456,13 +18452,13 @@
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357120</t>
+          <t>https://artportalen.se/Sighting/135357138</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>135357138</v>
+        <v>135357140</v>
       </c>
       <c r="B154" t="n">
         <v>101375</v>
@@ -18497,10 +18493,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>598751</v>
+        <v>598770</v>
       </c>
       <c r="R154" t="n">
-        <v>7330316</v>
+        <v>7330338</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18532,7 +18528,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -18542,7 +18538,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18572,13 +18568,13 @@
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357138</t>
+          <t>https://artportalen.se/Sighting/135357140</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>135357140</v>
+        <v>135357147</v>
       </c>
       <c r="B155" t="n">
         <v>101375</v>
@@ -18613,10 +18609,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>598770</v>
+        <v>598911</v>
       </c>
       <c r="R155" t="n">
-        <v>7330338</v>
+        <v>7330350</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18648,7 +18644,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18658,7 +18654,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18688,13 +18684,13 @@
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357140</t>
+          <t>https://artportalen.se/Sighting/135357147</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>135357147</v>
+        <v>135357205</v>
       </c>
       <c r="B156" t="n">
         <v>101375</v>
@@ -18729,10 +18725,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>598911</v>
+        <v>598553</v>
       </c>
       <c r="R156" t="n">
-        <v>7330350</v>
+        <v>7330578</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18764,7 +18760,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18774,7 +18770,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18804,13 +18800,13 @@
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357147</t>
+          <t>https://artportalen.se/Sighting/135357205</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>135357205</v>
+        <v>135357206</v>
       </c>
       <c r="B157" t="n">
         <v>101375</v>
@@ -18845,10 +18841,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>598553</v>
+        <v>598521</v>
       </c>
       <c r="R157" t="n">
-        <v>7330578</v>
+        <v>7330581</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18880,7 +18876,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18890,7 +18886,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18920,13 +18916,13 @@
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357205</t>
+          <t>https://artportalen.se/Sighting/135357206</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>135357206</v>
+        <v>135357213</v>
       </c>
       <c r="B158" t="n">
         <v>101375</v>
@@ -18961,10 +18957,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>598521</v>
+        <v>598501</v>
       </c>
       <c r="R158" t="n">
-        <v>7330581</v>
+        <v>7330475</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18996,7 +18992,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -19006,7 +19002,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19036,13 +19032,13 @@
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357206</t>
+          <t>https://artportalen.se/Sighting/135357213</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>135357213</v>
+        <v>135358268</v>
       </c>
       <c r="B159" t="n">
         <v>101375</v>
@@ -19073,17 +19069,17 @@
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>598501</v>
+        <v>598580</v>
       </c>
       <c r="R159" t="n">
-        <v>7330475</v>
+        <v>7330339</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -19112,7 +19108,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19122,7 +19118,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19137,12 +19133,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -19152,13 +19148,13 @@
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357213</t>
+          <t>https://artportalen.se/Sighting/135358268</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>135358268</v>
+        <v>135358284</v>
       </c>
       <c r="B160" t="n">
         <v>101375</v>
@@ -19193,10 +19189,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>598580</v>
+        <v>598610</v>
       </c>
       <c r="R160" t="n">
-        <v>7330339</v>
+        <v>7330295</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -19228,7 +19224,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19238,7 +19234,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19268,13 +19264,13 @@
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358268</t>
+          <t>https://artportalen.se/Sighting/135358284</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>135358284</v>
+        <v>135358293</v>
       </c>
       <c r="B161" t="n">
         <v>101375</v>
@@ -19309,10 +19305,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>598610</v>
+        <v>598830</v>
       </c>
       <c r="R161" t="n">
-        <v>7330295</v>
+        <v>7330303</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -19344,7 +19340,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19354,7 +19350,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19384,13 +19380,13 @@
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358284</t>
+          <t>https://artportalen.se/Sighting/135358293</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>135358293</v>
+        <v>135358341</v>
       </c>
       <c r="B162" t="n">
         <v>101375</v>
@@ -19425,10 +19421,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>598830</v>
+        <v>598546</v>
       </c>
       <c r="R162" t="n">
-        <v>7330303</v>
+        <v>7330653</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -19460,7 +19456,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19470,7 +19466,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19500,13 +19496,13 @@
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358293</t>
+          <t>https://artportalen.se/Sighting/135358341</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>135358341</v>
+        <v>135382388</v>
       </c>
       <c r="B163" t="n">
         <v>101375</v>
@@ -19537,14 +19533,14 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>598546</v>
+        <v>598483</v>
       </c>
       <c r="R163" t="n">
-        <v>7330653</v>
+        <v>7330403</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -19571,22 +19567,22 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19601,12 +19597,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -19616,13 +19612,13 @@
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358341</t>
+          <t>https://artportalen.se/Sighting/135382388</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>135382388</v>
+        <v>135382712</v>
       </c>
       <c r="B164" t="n">
         <v>101375</v>
@@ -19653,17 +19649,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>598483</v>
+        <v>598464</v>
       </c>
       <c r="R164" t="n">
-        <v>7330403</v>
+        <v>7330416</v>
       </c>
       <c r="S164" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -19717,12 +19713,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -19732,13 +19728,13 @@
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382388</t>
+          <t>https://artportalen.se/Sighting/135382712</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>135382712</v>
+        <v>135382717</v>
       </c>
       <c r="B165" t="n">
         <v>101375</v>
@@ -19773,10 +19769,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>598464</v>
+        <v>598507</v>
       </c>
       <c r="R165" t="n">
-        <v>7330416</v>
+        <v>7330626</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19808,7 +19804,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19818,7 +19814,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19848,13 +19844,13 @@
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382712</t>
+          <t>https://artportalen.se/Sighting/135382717</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>135382717</v>
+        <v>135382722</v>
       </c>
       <c r="B166" t="n">
         <v>101375</v>
@@ -19889,10 +19885,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>598507</v>
+        <v>598467</v>
       </c>
       <c r="R166" t="n">
-        <v>7330626</v>
+        <v>7330649</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19924,7 +19920,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19934,7 +19930,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19964,16 +19960,16 @@
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382717</t>
+          <t>https://artportalen.se/Sighting/135382722</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>135382722</v>
+        <v>135357130</v>
       </c>
       <c r="B167" t="n">
-        <v>101375</v>
+        <v>102051</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19981,34 +19977,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>224885</v>
+        <v>225188</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Vanliga skogsvinbär</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
+          <t>Ribes spicatum subsp. spicatum</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>598467</v>
+        <v>598613</v>
       </c>
       <c r="R167" t="n">
-        <v>7330649</v>
+        <v>7330353</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20035,22 +20031,22 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20059,6 +20055,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -20080,54 +20077,54 @@
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382722</t>
+          <t>https://artportalen.se/Sighting/135357130</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>135357130</v>
+        <v>135356852</v>
       </c>
       <c r="B168" t="n">
-        <v>102034</v>
+        <v>92442</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>225188</v>
+        <v>6040186</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vanliga skogsvinbär</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ribes spicatum subsp. spicatum</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr"/>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>598613</v>
+        <v>598735</v>
       </c>
       <c r="R168" t="n">
-        <v>7330353</v>
+        <v>7330341</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -20156,7 +20153,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -20166,7 +20163,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20182,12 +20179,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -20197,13 +20194,13 @@
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357130</t>
+          <t>https://artportalen.se/Sighting/135356852</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>135356852</v>
+        <v>135357134</v>
       </c>
       <c r="B169" t="n">
         <v>92442</v>
@@ -20234,17 +20231,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>598735</v>
+        <v>598723</v>
       </c>
       <c r="R169" t="n">
-        <v>7330341</v>
+        <v>7330305</v>
       </c>
       <c r="S169" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -20273,7 +20270,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -20283,7 +20280,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20299,12 +20296,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -20313,123 +20310,6 @@
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135356852</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>135357134</v>
-      </c>
-      <c r="B170" t="n">
-        <v>92442</v>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E170" t="n">
-        <v>6040186</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Kötticka</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="P170" t="inlineStr">
-        <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q170" t="n">
-        <v>598723</v>
-      </c>
-      <c r="R170" t="n">
-        <v>7330305</v>
-      </c>
-      <c r="S170" t="n">
-        <v>10</v>
-      </c>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AD170" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE170" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF170" t="inlineStr"/>
-      <c r="AG170" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT170" t="inlineStr"/>
-      <c r="AW170" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX170" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY170" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-      <c r="AZ170" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135357134</t>
         </is>
@@ -20605,7 +20485,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ169"/>
+  <dimension ref="A1:AZ170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7572,48 +7572,51 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135356210</v>
+        <v>135358275</v>
       </c>
       <c r="B61" t="n">
-        <v>92446</v>
+        <v>87699</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4217</v>
+        <v>3639</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rutspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Cortinarius ionophyllus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>598603</v>
+        <v>598533</v>
       </c>
       <c r="R61" t="n">
-        <v>7330411</v>
+        <v>7330307</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7642,7 +7645,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7652,7 +7655,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7661,18 +7664,19 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7682,13 +7686,13 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356210</t>
+          <t>https://artportalen.se/Sighting/135358275</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135356372</v>
+        <v>135356210</v>
       </c>
       <c r="B62" t="n">
         <v>92446</v>
@@ -7719,17 +7723,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>598544</v>
+        <v>598603</v>
       </c>
       <c r="R62" t="n">
-        <v>7330366</v>
+        <v>7330411</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7758,7 +7762,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7768,7 +7772,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7783,12 +7787,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7798,16 +7802,16 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356372</t>
+          <t>https://artportalen.se/Sighting/135356210</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135353513</v>
+        <v>135356372</v>
       </c>
       <c r="B63" t="n">
-        <v>92013</v>
+        <v>92446</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7815,37 +7819,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>598811</v>
+        <v>598544</v>
       </c>
       <c r="R63" t="n">
-        <v>7330371</v>
+        <v>7330366</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7874,7 +7878,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7884,7 +7888,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7899,12 +7903,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7914,38 +7918,38 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353513</t>
+          <t>https://artportalen.se/Sighting/135356372</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135353495</v>
+        <v>135353513</v>
       </c>
       <c r="B64" t="n">
-        <v>79441</v>
+        <v>92013</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7955,10 +7959,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>598630</v>
+        <v>598811</v>
       </c>
       <c r="R64" t="n">
-        <v>7330381</v>
+        <v>7330371</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7990,7 +7994,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8000,7 +8004,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8030,13 +8034,13 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353495</t>
+          <t>https://artportalen.se/Sighting/135353513</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135353515</v>
+        <v>135353495</v>
       </c>
       <c r="B65" t="n">
         <v>79441</v>
@@ -8071,10 +8075,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>598809</v>
+        <v>598630</v>
       </c>
       <c r="R65" t="n">
-        <v>7330378</v>
+        <v>7330381</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8106,7 +8110,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8116,7 +8120,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8146,13 +8150,13 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353515</t>
+          <t>https://artportalen.se/Sighting/135353495</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135356240</v>
+        <v>135353515</v>
       </c>
       <c r="B66" t="n">
         <v>79441</v>
@@ -8183,14 +8187,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>598519</v>
+        <v>598809</v>
       </c>
       <c r="R66" t="n">
-        <v>7330561</v>
+        <v>7330378</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8222,7 +8226,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8232,7 +8236,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8247,12 +8251,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -8262,13 +8266,13 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356240</t>
+          <t>https://artportalen.se/Sighting/135353515</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135356837</v>
+        <v>135356240</v>
       </c>
       <c r="B67" t="n">
         <v>79441</v>
@@ -8299,17 +8303,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>598555</v>
+        <v>598519</v>
       </c>
       <c r="R67" t="n">
-        <v>7330375</v>
+        <v>7330561</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8338,7 +8342,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8348,7 +8352,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8363,12 +8367,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8378,13 +8382,13 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356837</t>
+          <t>https://artportalen.se/Sighting/135356240</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135382466</v>
+        <v>135356837</v>
       </c>
       <c r="B68" t="n">
         <v>79441</v>
@@ -8415,17 +8419,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>598537</v>
+        <v>598555</v>
       </c>
       <c r="R68" t="n">
-        <v>7330657</v>
+        <v>7330375</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8449,22 +8453,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8479,12 +8483,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8494,13 +8498,13 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382466</t>
+          <t>https://artportalen.se/Sighting/135356837</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135384252</v>
+        <v>135382466</v>
       </c>
       <c r="B69" t="n">
         <v>79441</v>
@@ -8531,17 +8535,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>598474</v>
+        <v>598537</v>
       </c>
       <c r="R69" t="n">
-        <v>7330641</v>
+        <v>7330657</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8570,7 +8574,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8580,7 +8584,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8595,12 +8599,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8610,54 +8614,54 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384252</t>
+          <t>https://artportalen.se/Sighting/135382466</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135353509</v>
+        <v>135384252</v>
       </c>
       <c r="B70" t="n">
-        <v>83428</v>
+        <v>79441</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>598768</v>
+        <v>598474</v>
       </c>
       <c r="R70" t="n">
-        <v>7330331</v>
+        <v>7330641</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8681,22 +8685,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8711,12 +8715,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8726,13 +8730,13 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353509</t>
+          <t>https://artportalen.se/Sighting/135384252</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135356841</v>
+        <v>135353509</v>
       </c>
       <c r="B71" t="n">
         <v>83428</v>
@@ -8763,14 +8767,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>598580</v>
+        <v>598768</v>
       </c>
       <c r="R71" t="n">
-        <v>7330406</v>
+        <v>7330331</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8802,7 +8806,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8812,7 +8816,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8827,12 +8831,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8842,54 +8846,54 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356841</t>
+          <t>https://artportalen.se/Sighting/135353509</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135357126</v>
+        <v>135356841</v>
       </c>
       <c r="B72" t="n">
-        <v>80561</v>
+        <v>83428</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>598552</v>
+        <v>598580</v>
       </c>
       <c r="R72" t="n">
-        <v>7330359</v>
+        <v>7330406</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8918,7 +8922,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8928,7 +8932,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8943,12 +8947,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8958,59 +8962,54 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357126</t>
+          <t>https://artportalen.se/Sighting/135356841</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135353488</v>
+        <v>135357126</v>
       </c>
       <c r="B73" t="n">
-        <v>57980</v>
+        <v>80561</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>598564</v>
+        <v>598552</v>
       </c>
       <c r="R73" t="n">
-        <v>7330345</v>
+        <v>7330359</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9039,7 +9038,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9049,7 +9048,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9064,12 +9063,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -9079,13 +9078,13 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353488</t>
+          <t>https://artportalen.se/Sighting/135357126</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135353503</v>
+        <v>135353488</v>
       </c>
       <c r="B74" t="n">
         <v>57980</v>
@@ -9116,7 +9115,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9125,10 +9124,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>598672</v>
+        <v>598564</v>
       </c>
       <c r="R74" t="n">
-        <v>7330311</v>
+        <v>7330345</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9160,7 +9159,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9170,7 +9169,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9200,13 +9199,13 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353503</t>
+          <t>https://artportalen.se/Sighting/135353488</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135356216</v>
+        <v>135353503</v>
       </c>
       <c r="B75" t="n">
         <v>57980</v>
@@ -9235,19 +9234,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>598747</v>
+        <v>598672</v>
       </c>
       <c r="R75" t="n">
-        <v>7330309</v>
+        <v>7330311</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9276,7 +9280,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9286,12 +9290,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Gamla och nya ringhack</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9306,12 +9305,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -9321,13 +9320,13 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356216</t>
+          <t>https://artportalen.se/Sighting/135353503</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135356376</v>
+        <v>135356216</v>
       </c>
       <c r="B76" t="n">
         <v>57980</v>
@@ -9356,27 +9355,19 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>598614</v>
+        <v>598747</v>
       </c>
       <c r="R76" t="n">
-        <v>7330356</v>
+        <v>7330309</v>
       </c>
       <c r="S76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9405,7 +9396,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9415,19 +9406,19 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Gamla och nya ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
@@ -9435,12 +9426,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -9450,13 +9441,13 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356376</t>
+          <t>https://artportalen.se/Sighting/135356216</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135356380</v>
+        <v>135356376</v>
       </c>
       <c r="B77" t="n">
         <v>57980</v>
@@ -9499,13 +9490,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>598877</v>
+        <v>598614</v>
       </c>
       <c r="R77" t="n">
-        <v>7330349</v>
+        <v>7330356</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9534,7 +9525,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9544,19 +9535,19 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG77" t="b">
         <v>0</v>
@@ -9569,7 +9560,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9579,13 +9570,13 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356380</t>
+          <t>https://artportalen.se/Sighting/135356376</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135357127</v>
+        <v>135356380</v>
       </c>
       <c r="B78" t="n">
         <v>57980</v>
@@ -9614,19 +9605,27 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>598569</v>
+        <v>598877</v>
       </c>
       <c r="R78" t="n">
-        <v>7330352</v>
+        <v>7330349</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9655,7 +9654,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9665,12 +9664,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9685,12 +9684,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9700,13 +9699,13 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357127</t>
+          <t>https://artportalen.se/Sighting/135356380</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135358283</v>
+        <v>135357127</v>
       </c>
       <c r="B79" t="n">
         <v>57980</v>
@@ -9737,17 +9736,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>598609</v>
+        <v>598569</v>
       </c>
       <c r="R79" t="n">
-        <v>7330298</v>
+        <v>7330352</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9776,7 +9775,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9786,7 +9785,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -9806,12 +9805,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9821,13 +9820,13 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358283</t>
+          <t>https://artportalen.se/Sighting/135357127</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135382716</v>
+        <v>135358283</v>
       </c>
       <c r="B80" t="n">
         <v>57980</v>
@@ -9856,27 +9855,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>598482</v>
+        <v>598609</v>
       </c>
       <c r="R80" t="n">
-        <v>7330489</v>
+        <v>7330298</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9900,27 +9891,27 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9935,12 +9926,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9950,13 +9941,13 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382716</t>
+          <t>https://artportalen.se/Sighting/135358283</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135382779</v>
+        <v>135382716</v>
       </c>
       <c r="B81" t="n">
         <v>57980</v>
@@ -9989,7 +9980,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -9999,10 +9990,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>598462</v>
+        <v>598482</v>
       </c>
       <c r="R81" t="n">
-        <v>7330447</v>
+        <v>7330489</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10034,7 +10025,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10044,12 +10035,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10079,13 +10070,13 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382779</t>
+          <t>https://artportalen.se/Sighting/135382716</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135384126</v>
+        <v>135382779</v>
       </c>
       <c r="B82" t="n">
         <v>57980</v>
@@ -10128,10 +10119,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>598485</v>
+        <v>598462</v>
       </c>
       <c r="R82" t="n">
-        <v>7330673</v>
+        <v>7330447</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10163,7 +10154,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10173,19 +10164,19 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="b">
         <v>0</v>
@@ -10193,12 +10184,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -10208,16 +10199,16 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384126</t>
+          <t>https://artportalen.se/Sighting/135382779</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135357215</v>
+        <v>135384126</v>
       </c>
       <c r="B83" t="n">
-        <v>58141</v>
+        <v>57980</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10225,21 +10216,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10247,20 +10238,20 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>598501</v>
+        <v>598485</v>
       </c>
       <c r="R83" t="n">
-        <v>7330475</v>
+        <v>7330673</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10287,34 +10278,34 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG83" t="b">
         <v>0</v>
@@ -10322,12 +10313,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -10337,13 +10328,13 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357215</t>
+          <t>https://artportalen.se/Sighting/135384126</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135382711</v>
+        <v>135357215</v>
       </c>
       <c r="B84" t="n">
         <v>58141</v>
@@ -10382,14 +10373,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>598464</v>
+        <v>598501</v>
       </c>
       <c r="R84" t="n">
-        <v>7330416</v>
+        <v>7330475</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10416,22 +10407,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10461,13 +10457,13 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382711</t>
+          <t>https://artportalen.se/Sighting/135357215</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135385939</v>
+        <v>135382711</v>
       </c>
       <c r="B85" t="n">
         <v>58141</v>
@@ -10496,16 +10492,24 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>598491</v>
+        <v>598464</v>
       </c>
       <c r="R85" t="n">
-        <v>7330361</v>
+        <v>7330416</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10537,7 +10541,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10547,7 +10551,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10562,12 +10566,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -10577,54 +10581,54 @@
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135385939</t>
+          <t>https://artportalen.se/Sighting/135382711</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135382469</v>
+        <v>135385939</v>
       </c>
       <c r="B86" t="n">
-        <v>99193</v>
+        <v>58141</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>598453</v>
+        <v>598491</v>
       </c>
       <c r="R86" t="n">
-        <v>7330444</v>
+        <v>7330361</v>
       </c>
       <c r="S86" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10653,7 +10657,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10663,7 +10667,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10678,12 +10682,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10693,13 +10697,13 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382469</t>
+          <t>https://artportalen.se/Sighting/135385939</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135384124</v>
+        <v>135382469</v>
       </c>
       <c r="B87" t="n">
         <v>99193</v>
@@ -10730,17 +10734,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>598499</v>
+        <v>598453</v>
       </c>
       <c r="R87" t="n">
-        <v>7330637</v>
+        <v>7330444</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10769,7 +10773,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10779,7 +10783,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10794,12 +10798,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10809,13 +10813,13 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384124</t>
+          <t>https://artportalen.se/Sighting/135382469</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135384162</v>
+        <v>135384124</v>
       </c>
       <c r="B88" t="n">
         <v>99193</v>
@@ -10850,10 +10854,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>598449</v>
+        <v>598499</v>
       </c>
       <c r="R88" t="n">
-        <v>7330355</v>
+        <v>7330637</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10885,7 +10889,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10895,7 +10899,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10925,16 +10929,16 @@
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384162</t>
+          <t>https://artportalen.se/Sighting/135384124</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>94770073</v>
+        <v>135384162</v>
       </c>
       <c r="B89" t="n">
-        <v>99120</v>
+        <v>99193</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10942,43 +10946,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Laisan, Arjeplog, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>598453</v>
+        <v>598449</v>
       </c>
       <c r="R89" t="n">
-        <v>7330315</v>
+        <v>7330355</v>
       </c>
       <c r="S89" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11002,12 +11000,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11022,27 +11030,31 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Thomas Strid, Tiina Laantee</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94770073</t>
+          <t>https://artportalen.se/Sighting/135384162</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135356843</v>
+        <v>94770073</v>
       </c>
       <c r="B90" t="n">
-        <v>99180</v>
+        <v>99120</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11050,37 +11062,43 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Laisan, Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>598607</v>
+        <v>598453</v>
       </c>
       <c r="R90" t="n">
-        <v>7330382</v>
+        <v>7330315</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11104,22 +11122,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11134,31 +11142,27 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Thomas Strid, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356843</t>
+          <t>https://artportalen.se/Sighting/94770073</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135353481</v>
+        <v>135356843</v>
       </c>
       <c r="B91" t="n">
-        <v>110014</v>
+        <v>99180</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11166,34 +11170,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221184</v>
+        <v>220093</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>598529</v>
+        <v>598607</v>
       </c>
       <c r="R91" t="n">
-        <v>7330341</v>
+        <v>7330382</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -11225,7 +11229,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11235,7 +11239,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11250,12 +11254,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11265,13 +11269,13 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353481</t>
+          <t>https://artportalen.se/Sighting/135356843</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135353512</v>
+        <v>135353481</v>
       </c>
       <c r="B92" t="n">
         <v>110014</v>
@@ -11306,10 +11310,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>598793</v>
+        <v>598529</v>
       </c>
       <c r="R92" t="n">
-        <v>7330350</v>
+        <v>7330341</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -11341,7 +11345,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11351,7 +11355,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11381,13 +11385,13 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353512</t>
+          <t>https://artportalen.se/Sighting/135353481</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135356205</v>
+        <v>135353512</v>
       </c>
       <c r="B93" t="n">
         <v>110014</v>
@@ -11418,14 +11422,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>598518</v>
+        <v>598793</v>
       </c>
       <c r="R93" t="n">
-        <v>7330341</v>
+        <v>7330350</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11457,7 +11461,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11467,7 +11471,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11482,12 +11486,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -11497,13 +11501,13 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356205</t>
+          <t>https://artportalen.se/Sighting/135353512</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135356241</v>
+        <v>135356205</v>
       </c>
       <c r="B94" t="n">
         <v>110014</v>
@@ -11538,10 +11542,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>598490</v>
+        <v>598518</v>
       </c>
       <c r="R94" t="n">
-        <v>7330565</v>
+        <v>7330341</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11573,7 +11577,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11583,7 +11587,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11613,13 +11617,13 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356241</t>
+          <t>https://artportalen.se/Sighting/135356205</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135357137</v>
+        <v>135356241</v>
       </c>
       <c r="B95" t="n">
         <v>110014</v>
@@ -11650,17 +11654,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>598751</v>
+        <v>598490</v>
       </c>
       <c r="R95" t="n">
-        <v>7330316</v>
+        <v>7330565</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11689,7 +11693,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11699,7 +11703,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11714,12 +11718,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11729,13 +11733,13 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357137</t>
+          <t>https://artportalen.se/Sighting/135356241</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135357141</v>
+        <v>135357137</v>
       </c>
       <c r="B96" t="n">
         <v>110014</v>
@@ -11770,10 +11774,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>598770</v>
+        <v>598751</v>
       </c>
       <c r="R96" t="n">
-        <v>7330338</v>
+        <v>7330316</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11805,7 +11809,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11815,7 +11819,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11845,13 +11849,13 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357141</t>
+          <t>https://artportalen.se/Sighting/135357137</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135357201</v>
+        <v>135357141</v>
       </c>
       <c r="B97" t="n">
         <v>110014</v>
@@ -11886,10 +11890,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>598553</v>
+        <v>598770</v>
       </c>
       <c r="R97" t="n">
-        <v>7330578</v>
+        <v>7330338</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11921,7 +11925,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11931,7 +11935,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11961,13 +11965,13 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357201</t>
+          <t>https://artportalen.se/Sighting/135357141</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135357211</v>
+        <v>135357201</v>
       </c>
       <c r="B98" t="n">
         <v>110014</v>
@@ -12002,10 +12006,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>598501</v>
+        <v>598553</v>
       </c>
       <c r="R98" t="n">
-        <v>7330515</v>
+        <v>7330578</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12037,7 +12041,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12047,7 +12051,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12077,13 +12081,13 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357211</t>
+          <t>https://artportalen.se/Sighting/135357201</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135357212</v>
+        <v>135357211</v>
       </c>
       <c r="B99" t="n">
         <v>110014</v>
@@ -12118,10 +12122,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>598498</v>
+        <v>598501</v>
       </c>
       <c r="R99" t="n">
-        <v>7330492</v>
+        <v>7330515</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12153,7 +12157,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12163,7 +12167,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12193,13 +12197,13 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357212</t>
+          <t>https://artportalen.se/Sighting/135357211</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135358269</v>
+        <v>135357212</v>
       </c>
       <c r="B100" t="n">
         <v>110014</v>
@@ -12230,17 +12234,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>598578</v>
+        <v>598498</v>
       </c>
       <c r="R100" t="n">
-        <v>7330329</v>
+        <v>7330492</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12269,7 +12273,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12279,7 +12283,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12294,12 +12298,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12309,13 +12313,13 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358269</t>
+          <t>https://artportalen.se/Sighting/135357212</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135358276</v>
+        <v>135358269</v>
       </c>
       <c r="B101" t="n">
         <v>110014</v>
@@ -12350,10 +12354,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>598542</v>
+        <v>598578</v>
       </c>
       <c r="R101" t="n">
-        <v>7330305</v>
+        <v>7330329</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12385,7 +12389,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12395,7 +12399,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12425,13 +12429,13 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358276</t>
+          <t>https://artportalen.se/Sighting/135358269</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135358292</v>
+        <v>135358276</v>
       </c>
       <c r="B102" t="n">
         <v>110014</v>
@@ -12466,10 +12470,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>598827</v>
+        <v>598542</v>
       </c>
       <c r="R102" t="n">
-        <v>7330278</v>
+        <v>7330305</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12501,7 +12505,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12511,7 +12515,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12541,13 +12545,13 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358292</t>
+          <t>https://artportalen.se/Sighting/135358276</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135358342</v>
+        <v>135358292</v>
       </c>
       <c r="B103" t="n">
         <v>110014</v>
@@ -12582,10 +12586,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>598546</v>
+        <v>598827</v>
       </c>
       <c r="R103" t="n">
-        <v>7330653</v>
+        <v>7330278</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12617,7 +12621,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12627,7 +12631,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12657,13 +12661,13 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358342</t>
+          <t>https://artportalen.se/Sighting/135358292</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135382720</v>
+        <v>135358342</v>
       </c>
       <c r="B104" t="n">
         <v>110014</v>
@@ -12694,17 +12698,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>598507</v>
+        <v>598546</v>
       </c>
       <c r="R104" t="n">
-        <v>7330626</v>
+        <v>7330653</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12728,22 +12732,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12758,12 +12762,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12773,13 +12777,13 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382720</t>
+          <t>https://artportalen.se/Sighting/135358342</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135382723</v>
+        <v>135382720</v>
       </c>
       <c r="B105" t="n">
         <v>110014</v>
@@ -12814,10 +12818,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>598467</v>
+        <v>598507</v>
       </c>
       <c r="R105" t="n">
-        <v>7330649</v>
+        <v>7330626</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12849,7 +12853,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12859,7 +12863,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12889,16 +12893,16 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382723</t>
+          <t>https://artportalen.se/Sighting/135382720</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135353491</v>
+        <v>135382723</v>
       </c>
       <c r="B106" t="n">
-        <v>106398</v>
+        <v>110014</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12906,16 +12910,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221725</v>
+        <v>221184</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -12926,17 +12930,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>598592</v>
+        <v>598467</v>
       </c>
       <c r="R106" t="n">
-        <v>7330348</v>
+        <v>7330649</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12960,22 +12964,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12990,12 +12994,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -13005,13 +13009,13 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353491</t>
+          <t>https://artportalen.se/Sighting/135382723</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135356209</v>
+        <v>135353491</v>
       </c>
       <c r="B107" t="n">
         <v>106398</v>
@@ -13042,14 +13046,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>598597</v>
+        <v>598592</v>
       </c>
       <c r="R107" t="n">
-        <v>7330383</v>
+        <v>7330348</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -13081,7 +13085,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13091,7 +13095,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13106,12 +13110,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -13121,13 +13125,13 @@
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356209</t>
+          <t>https://artportalen.se/Sighting/135353491</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135356218</v>
+        <v>135356209</v>
       </c>
       <c r="B108" t="n">
         <v>106398</v>
@@ -13162,10 +13166,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>598785</v>
+        <v>598597</v>
       </c>
       <c r="R108" t="n">
-        <v>7330366</v>
+        <v>7330383</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -13197,7 +13201,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13207,7 +13211,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13237,13 +13241,13 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356218</t>
+          <t>https://artportalen.se/Sighting/135356209</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135356839</v>
+        <v>135356218</v>
       </c>
       <c r="B109" t="n">
         <v>106398</v>
@@ -13274,17 +13278,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>598557</v>
+        <v>598785</v>
       </c>
       <c r="R109" t="n">
-        <v>7330411</v>
+        <v>7330366</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13313,7 +13317,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13323,7 +13327,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13338,12 +13342,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -13353,13 +13357,13 @@
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356839</t>
+          <t>https://artportalen.se/Sighting/135356218</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135356886</v>
+        <v>135356839</v>
       </c>
       <c r="B110" t="n">
         <v>106398</v>
@@ -13394,13 +13398,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>598518</v>
+        <v>598557</v>
       </c>
       <c r="R110" t="n">
-        <v>7330476</v>
+        <v>7330411</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13429,7 +13433,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13439,7 +13443,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13469,13 +13473,13 @@
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356886</t>
+          <t>https://artportalen.se/Sighting/135356839</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135358270</v>
+        <v>135356886</v>
       </c>
       <c r="B111" t="n">
         <v>106398</v>
@@ -13506,17 +13510,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>598568</v>
+        <v>598518</v>
       </c>
       <c r="R111" t="n">
-        <v>7330339</v>
+        <v>7330476</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13545,7 +13549,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13555,7 +13559,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13570,12 +13574,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -13585,13 +13589,13 @@
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358270</t>
+          <t>https://artportalen.se/Sighting/135356886</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135358287</v>
+        <v>135358270</v>
       </c>
       <c r="B112" t="n">
         <v>106398</v>
@@ -13626,10 +13630,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>598754</v>
+        <v>598568</v>
       </c>
       <c r="R112" t="n">
-        <v>7330326</v>
+        <v>7330339</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13661,7 +13665,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13671,7 +13675,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13701,16 +13705,16 @@
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358287</t>
+          <t>https://artportalen.se/Sighting/135358270</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135356206</v>
+        <v>135358287</v>
       </c>
       <c r="B113" t="n">
-        <v>98138</v>
+        <v>106398</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13718,37 +13722,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>598569</v>
+        <v>598754</v>
       </c>
       <c r="R113" t="n">
-        <v>7330354</v>
+        <v>7330326</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13777,7 +13781,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13787,7 +13791,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13802,12 +13806,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13817,13 +13821,13 @@
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356206</t>
+          <t>https://artportalen.se/Sighting/135358287</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135356243</v>
+        <v>135356206</v>
       </c>
       <c r="B114" t="n">
         <v>98138</v>
@@ -13858,10 +13862,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>598482</v>
+        <v>598569</v>
       </c>
       <c r="R114" t="n">
-        <v>7330539</v>
+        <v>7330354</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13893,7 +13897,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13903,7 +13907,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13933,13 +13937,13 @@
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356243</t>
+          <t>https://artportalen.se/Sighting/135356206</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135356845</v>
+        <v>135356243</v>
       </c>
       <c r="B115" t="n">
         <v>98138</v>
@@ -13970,17 +13974,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>598624</v>
+        <v>598482</v>
       </c>
       <c r="R115" t="n">
-        <v>7330372</v>
+        <v>7330539</v>
       </c>
       <c r="S115" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14009,7 +14013,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14019,7 +14023,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14034,12 +14038,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -14049,13 +14053,13 @@
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356845</t>
+          <t>https://artportalen.se/Sighting/135356243</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135356884</v>
+        <v>135356845</v>
       </c>
       <c r="B116" t="n">
         <v>98138</v>
@@ -14090,13 +14094,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>598495</v>
+        <v>598624</v>
       </c>
       <c r="R116" t="n">
-        <v>7330628</v>
+        <v>7330372</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14125,7 +14129,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14135,7 +14139,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14165,13 +14169,13 @@
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356884</t>
+          <t>https://artportalen.se/Sighting/135356845</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135358281</v>
+        <v>135356884</v>
       </c>
       <c r="B117" t="n">
         <v>98138</v>
@@ -14202,14 +14206,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>598605</v>
+        <v>598495</v>
       </c>
       <c r="R117" t="n">
-        <v>7330324</v>
+        <v>7330628</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14241,7 +14245,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14251,7 +14255,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14266,12 +14270,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -14281,13 +14285,13 @@
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358281</t>
+          <t>https://artportalen.se/Sighting/135356884</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135382031</v>
+        <v>135358281</v>
       </c>
       <c r="B118" t="n">
         <v>98138</v>
@@ -14318,17 +14322,17 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>598459</v>
+        <v>598605</v>
       </c>
       <c r="R118" t="n">
-        <v>7330572</v>
+        <v>7330324</v>
       </c>
       <c r="S118" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14352,22 +14356,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14382,12 +14386,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -14397,13 +14401,13 @@
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382031</t>
+          <t>https://artportalen.se/Sighting/135358281</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135382032</v>
+        <v>135382031</v>
       </c>
       <c r="B119" t="n">
         <v>98138</v>
@@ -14438,13 +14442,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>598472</v>
+        <v>598459</v>
       </c>
       <c r="R119" t="n">
-        <v>7330674</v>
+        <v>7330572</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14513,13 +14517,13 @@
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382032</t>
+          <t>https://artportalen.se/Sighting/135382031</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135384245</v>
+        <v>135382032</v>
       </c>
       <c r="B120" t="n">
         <v>98138</v>
@@ -14550,14 +14554,14 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>598522</v>
+        <v>598472</v>
       </c>
       <c r="R120" t="n">
-        <v>7330575</v>
+        <v>7330674</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14589,7 +14593,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14599,7 +14603,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14614,12 +14618,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -14629,13 +14633,13 @@
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384245</t>
+          <t>https://artportalen.se/Sighting/135382032</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135384249</v>
+        <v>135384245</v>
       </c>
       <c r="B121" t="n">
         <v>98138</v>
@@ -14670,13 +14674,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>598492</v>
+        <v>598522</v>
       </c>
       <c r="R121" t="n">
-        <v>7330652</v>
+        <v>7330575</v>
       </c>
       <c r="S121" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14705,7 +14709,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14715,7 +14719,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14745,16 +14749,16 @@
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384249</t>
+          <t>https://artportalen.se/Sighting/135384245</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135353486</v>
+        <v>135384249</v>
       </c>
       <c r="B122" t="n">
-        <v>99298</v>
+        <v>98138</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14762,37 +14766,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>598555</v>
+        <v>598492</v>
       </c>
       <c r="R122" t="n">
-        <v>7330349</v>
+        <v>7330652</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14816,22 +14820,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14846,12 +14850,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -14861,13 +14865,13 @@
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353486</t>
+          <t>https://artportalen.se/Sighting/135384249</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135353494</v>
+        <v>135353486</v>
       </c>
       <c r="B123" t="n">
         <v>99298</v>
@@ -14902,10 +14906,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>598634</v>
+        <v>598555</v>
       </c>
       <c r="R123" t="n">
-        <v>7330375</v>
+        <v>7330349</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14937,7 +14941,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14947,7 +14951,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14977,13 +14981,13 @@
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353494</t>
+          <t>https://artportalen.se/Sighting/135353486</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135353497</v>
+        <v>135353494</v>
       </c>
       <c r="B124" t="n">
         <v>99298</v>
@@ -15018,10 +15022,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>598665</v>
+        <v>598634</v>
       </c>
       <c r="R124" t="n">
-        <v>7330360</v>
+        <v>7330375</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -15053,7 +15057,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15063,7 +15067,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15093,13 +15097,13 @@
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353497</t>
+          <t>https://artportalen.se/Sighting/135353494</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135356211</v>
+        <v>135353497</v>
       </c>
       <c r="B125" t="n">
         <v>99298</v>
@@ -15130,14 +15134,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>598644</v>
+        <v>598665</v>
       </c>
       <c r="R125" t="n">
-        <v>7330364</v>
+        <v>7330360</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15169,7 +15173,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15179,7 +15183,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15194,12 +15198,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -15209,13 +15213,13 @@
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356211</t>
+          <t>https://artportalen.se/Sighting/135353497</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135356213</v>
+        <v>135356211</v>
       </c>
       <c r="B126" t="n">
         <v>99298</v>
@@ -15250,13 +15254,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>598651</v>
+        <v>598644</v>
       </c>
       <c r="R126" t="n">
-        <v>7330373</v>
+        <v>7330364</v>
       </c>
       <c r="S126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15285,7 +15289,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15295,7 +15299,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15325,13 +15329,13 @@
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356213</t>
+          <t>https://artportalen.se/Sighting/135356211</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135356844</v>
+        <v>135356213</v>
       </c>
       <c r="B127" t="n">
         <v>99298</v>
@@ -15362,17 +15366,17 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>598607</v>
+        <v>598651</v>
       </c>
       <c r="R127" t="n">
-        <v>7330382</v>
+        <v>7330373</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15401,7 +15405,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15411,7 +15415,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15426,12 +15430,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -15441,13 +15445,13 @@
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356844</t>
+          <t>https://artportalen.se/Sighting/135356213</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135356846</v>
+        <v>135356844</v>
       </c>
       <c r="B128" t="n">
         <v>99298</v>
@@ -15482,10 +15486,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>598653</v>
+        <v>598607</v>
       </c>
       <c r="R128" t="n">
-        <v>7330343</v>
+        <v>7330382</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15517,7 +15521,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15527,7 +15531,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15557,13 +15561,13 @@
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356846</t>
+          <t>https://artportalen.se/Sighting/135356844</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>135356856</v>
+        <v>135356846</v>
       </c>
       <c r="B129" t="n">
         <v>99298</v>
@@ -15598,13 +15602,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>598841</v>
+        <v>598653</v>
       </c>
       <c r="R129" t="n">
-        <v>7330355</v>
+        <v>7330343</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15633,7 +15637,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15643,7 +15647,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15673,13 +15677,13 @@
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356856</t>
+          <t>https://artportalen.se/Sighting/135356846</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>135362163</v>
+        <v>135356856</v>
       </c>
       <c r="B130" t="n">
         <v>99298</v>
@@ -15710,17 +15714,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>598808</v>
+        <v>598841</v>
       </c>
       <c r="R130" t="n">
-        <v>7330337</v>
+        <v>7330355</v>
       </c>
       <c r="S130" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15747,9 +15751,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15764,12 +15778,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -15779,13 +15793,13 @@
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135362163</t>
+          <t>https://artportalen.se/Sighting/135356856</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>135382721</v>
+        <v>135362163</v>
       </c>
       <c r="B131" t="n">
         <v>99298</v>
@@ -15816,17 +15830,17 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>598467</v>
+        <v>598808</v>
       </c>
       <c r="R131" t="n">
-        <v>7330649</v>
+        <v>7330337</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15850,22 +15864,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15880,12 +15884,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -15895,13 +15899,13 @@
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382721</t>
+          <t>https://artportalen.se/Sighting/135362163</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>135384251</v>
+        <v>135382721</v>
       </c>
       <c r="B132" t="n">
         <v>99298</v>
@@ -15932,14 +15936,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>598482</v>
+        <v>598467</v>
       </c>
       <c r="R132" t="n">
-        <v>7330639</v>
+        <v>7330649</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15971,7 +15975,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15981,7 +15985,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15996,12 +16000,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -16011,16 +16015,16 @@
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384251</t>
+          <t>https://artportalen.se/Sighting/135382721</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135353490</v>
+        <v>135384251</v>
       </c>
       <c r="B133" t="n">
-        <v>104795</v>
+        <v>99298</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16028,37 +16032,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>222412</v>
+        <v>221952</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>598591</v>
+        <v>598482</v>
       </c>
       <c r="R133" t="n">
-        <v>7330353</v>
+        <v>7330639</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16082,22 +16086,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16112,12 +16116,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -16127,13 +16131,13 @@
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353490</t>
+          <t>https://artportalen.se/Sighting/135384251</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>135357136</v>
+        <v>135353490</v>
       </c>
       <c r="B134" t="n">
         <v>104795</v>
@@ -16164,17 +16168,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>598751</v>
+        <v>598591</v>
       </c>
       <c r="R134" t="n">
-        <v>7330316</v>
+        <v>7330353</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16203,7 +16207,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16213,7 +16217,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16228,12 +16232,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -16243,13 +16247,13 @@
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357136</t>
+          <t>https://artportalen.se/Sighting/135353490</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>135362160</v>
+        <v>135357136</v>
       </c>
       <c r="B135" t="n">
         <v>104795</v>
@@ -16284,13 +16288,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>598552</v>
+        <v>598751</v>
       </c>
       <c r="R135" t="n">
-        <v>7330368</v>
+        <v>7330316</v>
       </c>
       <c r="S135" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16317,9 +16321,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16334,12 +16348,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -16349,16 +16363,16 @@
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135362160</t>
+          <t>https://artportalen.se/Sighting/135357136</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135358271</v>
+        <v>135362160</v>
       </c>
       <c r="B136" t="n">
-        <v>99286</v>
+        <v>104795</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16366,41 +16380,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>222495</v>
+        <v>222412</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Myggblomster</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hammarbya paludosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Kuntze</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>598585</v>
+        <v>598552</v>
       </c>
       <c r="R136" t="n">
-        <v>7330354</v>
+        <v>7330368</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16427,40 +16437,29 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -16470,13 +16469,13 @@
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358271</t>
+          <t>https://artportalen.se/Sighting/135362160</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>135358274</v>
+        <v>135358271</v>
       </c>
       <c r="B137" t="n">
         <v>99286</v>
@@ -16515,13 +16514,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>598543</v>
+        <v>598585</v>
       </c>
       <c r="R137" t="n">
-        <v>7330322</v>
+        <v>7330354</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16550,7 +16549,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16560,7 +16559,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16591,13 +16590,13 @@
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358274</t>
+          <t>https://artportalen.se/Sighting/135358271</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>135358278</v>
+        <v>135358274</v>
       </c>
       <c r="B138" t="n">
         <v>99286</v>
@@ -16636,13 +16635,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>598566</v>
+        <v>598543</v>
       </c>
       <c r="R138" t="n">
-        <v>7330282</v>
+        <v>7330322</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16671,7 +16670,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16681,7 +16680,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16712,16 +16711,16 @@
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358278</t>
+          <t>https://artportalen.se/Sighting/135358274</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>135356838</v>
+        <v>135358278</v>
       </c>
       <c r="B139" t="n">
-        <v>98292</v>
+        <v>99286</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16729,37 +16728,41 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>222741</v>
+        <v>222495</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Myggblomster</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hammarbya paludosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Kuntze</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>598555</v>
+        <v>598566</v>
       </c>
       <c r="R139" t="n">
-        <v>7330375</v>
+        <v>7330282</v>
       </c>
       <c r="S139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16788,7 +16791,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16798,7 +16801,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16807,18 +16810,19 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -16828,13 +16832,13 @@
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356838</t>
+          <t>https://artportalen.se/Sighting/135358278</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>135357146</v>
+        <v>135356838</v>
       </c>
       <c r="B140" t="n">
         <v>98292</v>
@@ -16865,17 +16869,17 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>598911</v>
+        <v>598555</v>
       </c>
       <c r="R140" t="n">
-        <v>7330350</v>
+        <v>7330375</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16904,7 +16908,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16914,7 +16918,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16929,12 +16933,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -16944,13 +16948,13 @@
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357146</t>
+          <t>https://artportalen.se/Sighting/135356838</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>135357209</v>
+        <v>135357146</v>
       </c>
       <c r="B141" t="n">
         <v>98292</v>
@@ -16985,10 +16989,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>598519</v>
+        <v>598911</v>
       </c>
       <c r="R141" t="n">
-        <v>7330570</v>
+        <v>7330350</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17020,7 +17024,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17030,7 +17034,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17060,16 +17064,16 @@
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357209</t>
+          <t>https://artportalen.se/Sighting/135357146</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>135357123</v>
+        <v>135357209</v>
       </c>
       <c r="B142" t="n">
-        <v>102956</v>
+        <v>98292</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17077,21 +17081,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>223037</v>
+        <v>222741</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -17101,10 +17105,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>598552</v>
+        <v>598519</v>
       </c>
       <c r="R142" t="n">
-        <v>7330359</v>
+        <v>7330570</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17136,7 +17140,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17146,7 +17150,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17176,13 +17180,13 @@
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357123</t>
+          <t>https://artportalen.se/Sighting/135357209</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>135357202</v>
+        <v>135357123</v>
       </c>
       <c r="B143" t="n">
         <v>102956</v>
@@ -17217,10 +17221,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>598553</v>
+        <v>598552</v>
       </c>
       <c r="R143" t="n">
-        <v>7330578</v>
+        <v>7330359</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17252,7 +17256,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17262,7 +17266,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17292,13 +17296,13 @@
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357202</t>
+          <t>https://artportalen.se/Sighting/135357123</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>135382713</v>
+        <v>135357202</v>
       </c>
       <c r="B144" t="n">
         <v>102956</v>
@@ -17329,14 +17333,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>598464</v>
+        <v>598553</v>
       </c>
       <c r="R144" t="n">
-        <v>7330416</v>
+        <v>7330578</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17363,22 +17367,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17408,13 +17412,13 @@
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382713</t>
+          <t>https://artportalen.se/Sighting/135357202</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>135382724</v>
+        <v>135382713</v>
       </c>
       <c r="B145" t="n">
         <v>102956</v>
@@ -17449,10 +17453,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>598467</v>
+        <v>598464</v>
       </c>
       <c r="R145" t="n">
-        <v>7330649</v>
+        <v>7330416</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17484,7 +17488,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -17494,7 +17498,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17524,16 +17528,16 @@
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382724</t>
+          <t>https://artportalen.se/Sighting/135382713</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>135357122</v>
+        <v>135382724</v>
       </c>
       <c r="B146" t="n">
-        <v>98327</v>
+        <v>102956</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17541,34 +17545,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>223358</v>
+        <v>223037</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>598552</v>
+        <v>598467</v>
       </c>
       <c r="R146" t="n">
-        <v>7330359</v>
+        <v>7330649</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17595,22 +17599,22 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17640,13 +17644,13 @@
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357122</t>
+          <t>https://artportalen.se/Sighting/135382724</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>135357145</v>
+        <v>135357122</v>
       </c>
       <c r="B147" t="n">
         <v>98327</v>
@@ -17681,10 +17685,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>598911</v>
+        <v>598552</v>
       </c>
       <c r="R147" t="n">
-        <v>7330350</v>
+        <v>7330359</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17716,7 +17720,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17726,7 +17730,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17756,13 +17760,13 @@
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357145</t>
+          <t>https://artportalen.se/Sighting/135357122</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>135358277</v>
+        <v>135357145</v>
       </c>
       <c r="B148" t="n">
         <v>98327</v>
@@ -17793,17 +17797,17 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>598551</v>
+        <v>598911</v>
       </c>
       <c r="R148" t="n">
-        <v>7330296</v>
+        <v>7330350</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17832,7 +17836,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17842,7 +17846,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17857,12 +17861,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -17872,13 +17876,13 @@
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358277</t>
+          <t>https://artportalen.se/Sighting/135357145</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>135382718</v>
+        <v>135358277</v>
       </c>
       <c r="B149" t="n">
         <v>98327</v>
@@ -17909,17 +17913,17 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>598507</v>
+        <v>598551</v>
       </c>
       <c r="R149" t="n">
-        <v>7330626</v>
+        <v>7330296</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17943,22 +17947,22 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17973,12 +17977,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -17988,16 +17992,16 @@
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382718</t>
+          <t>https://artportalen.se/Sighting/135358277</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>135353482</v>
+        <v>135382718</v>
       </c>
       <c r="B150" t="n">
-        <v>101375</v>
+        <v>98327</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18005,37 +18009,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>598530</v>
+        <v>598507</v>
       </c>
       <c r="R150" t="n">
-        <v>7330340</v>
+        <v>7330626</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18059,22 +18063,22 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18089,12 +18093,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -18104,13 +18108,13 @@
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353482</t>
+          <t>https://artportalen.se/Sighting/135382718</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>135357117</v>
+        <v>135353482</v>
       </c>
       <c r="B151" t="n">
         <v>101375</v>
@@ -18141,17 +18145,17 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>598525</v>
+        <v>598530</v>
       </c>
       <c r="R151" t="n">
-        <v>7330346</v>
+        <v>7330340</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -18205,12 +18209,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -18220,13 +18224,13 @@
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357117</t>
+          <t>https://artportalen.se/Sighting/135353482</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>135357120</v>
+        <v>135357117</v>
       </c>
       <c r="B152" t="n">
         <v>101375</v>
@@ -18261,10 +18265,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>598552</v>
+        <v>598525</v>
       </c>
       <c r="R152" t="n">
-        <v>7330359</v>
+        <v>7330346</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18296,7 +18300,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18306,7 +18310,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18336,13 +18340,13 @@
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357120</t>
+          <t>https://artportalen.se/Sighting/135357117</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>135357138</v>
+        <v>135357120</v>
       </c>
       <c r="B153" t="n">
         <v>101375</v>
@@ -18377,10 +18381,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>598751</v>
+        <v>598552</v>
       </c>
       <c r="R153" t="n">
-        <v>7330316</v>
+        <v>7330359</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18412,7 +18416,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18422,7 +18426,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18452,13 +18456,13 @@
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357138</t>
+          <t>https://artportalen.se/Sighting/135357120</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>135357140</v>
+        <v>135357138</v>
       </c>
       <c r="B154" t="n">
         <v>101375</v>
@@ -18493,10 +18497,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>598770</v>
+        <v>598751</v>
       </c>
       <c r="R154" t="n">
-        <v>7330338</v>
+        <v>7330316</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18528,7 +18532,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -18538,7 +18542,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18568,13 +18572,13 @@
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357140</t>
+          <t>https://artportalen.se/Sighting/135357138</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>135357147</v>
+        <v>135357140</v>
       </c>
       <c r="B155" t="n">
         <v>101375</v>
@@ -18609,10 +18613,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>598911</v>
+        <v>598770</v>
       </c>
       <c r="R155" t="n">
-        <v>7330350</v>
+        <v>7330338</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18644,7 +18648,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18654,7 +18658,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18684,13 +18688,13 @@
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357147</t>
+          <t>https://artportalen.se/Sighting/135357140</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>135357205</v>
+        <v>135357147</v>
       </c>
       <c r="B156" t="n">
         <v>101375</v>
@@ -18725,10 +18729,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>598553</v>
+        <v>598911</v>
       </c>
       <c r="R156" t="n">
-        <v>7330578</v>
+        <v>7330350</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18760,7 +18764,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18770,7 +18774,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18800,13 +18804,13 @@
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357205</t>
+          <t>https://artportalen.se/Sighting/135357147</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>135357206</v>
+        <v>135357205</v>
       </c>
       <c r="B157" t="n">
         <v>101375</v>
@@ -18841,10 +18845,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>598521</v>
+        <v>598553</v>
       </c>
       <c r="R157" t="n">
-        <v>7330581</v>
+        <v>7330578</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18876,7 +18880,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18886,7 +18890,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18916,13 +18920,13 @@
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357206</t>
+          <t>https://artportalen.se/Sighting/135357205</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>135357213</v>
+        <v>135357206</v>
       </c>
       <c r="B158" t="n">
         <v>101375</v>
@@ -18957,10 +18961,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>598501</v>
+        <v>598521</v>
       </c>
       <c r="R158" t="n">
-        <v>7330475</v>
+        <v>7330581</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18992,7 +18996,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -19002,7 +19006,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19032,13 +19036,13 @@
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357213</t>
+          <t>https://artportalen.se/Sighting/135357206</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>135358268</v>
+        <v>135357213</v>
       </c>
       <c r="B159" t="n">
         <v>101375</v>
@@ -19069,17 +19073,17 @@
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>598580</v>
+        <v>598501</v>
       </c>
       <c r="R159" t="n">
-        <v>7330339</v>
+        <v>7330475</v>
       </c>
       <c r="S159" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -19108,7 +19112,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19118,7 +19122,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19133,12 +19137,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -19148,13 +19152,13 @@
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358268</t>
+          <t>https://artportalen.se/Sighting/135357213</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>135358284</v>
+        <v>135358268</v>
       </c>
       <c r="B160" t="n">
         <v>101375</v>
@@ -19189,10 +19193,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>598610</v>
+        <v>598580</v>
       </c>
       <c r="R160" t="n">
-        <v>7330295</v>
+        <v>7330339</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -19224,7 +19228,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19234,7 +19238,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19264,13 +19268,13 @@
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358284</t>
+          <t>https://artportalen.se/Sighting/135358268</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>135358293</v>
+        <v>135358284</v>
       </c>
       <c r="B161" t="n">
         <v>101375</v>
@@ -19305,10 +19309,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>598830</v>
+        <v>598610</v>
       </c>
       <c r="R161" t="n">
-        <v>7330303</v>
+        <v>7330295</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -19340,7 +19344,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19350,7 +19354,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19380,13 +19384,13 @@
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358293</t>
+          <t>https://artportalen.se/Sighting/135358284</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>135358341</v>
+        <v>135358293</v>
       </c>
       <c r="B162" t="n">
         <v>101375</v>
@@ -19421,10 +19425,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>598546</v>
+        <v>598830</v>
       </c>
       <c r="R162" t="n">
-        <v>7330653</v>
+        <v>7330303</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -19456,7 +19460,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19466,7 +19470,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19496,13 +19500,13 @@
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358341</t>
+          <t>https://artportalen.se/Sighting/135358293</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>135382388</v>
+        <v>135358341</v>
       </c>
       <c r="B163" t="n">
         <v>101375</v>
@@ -19533,14 +19537,14 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>598483</v>
+        <v>598546</v>
       </c>
       <c r="R163" t="n">
-        <v>7330403</v>
+        <v>7330653</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -19567,22 +19571,22 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19597,12 +19601,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -19612,13 +19616,13 @@
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382388</t>
+          <t>https://artportalen.se/Sighting/135358341</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>135382712</v>
+        <v>135382388</v>
       </c>
       <c r="B164" t="n">
         <v>101375</v>
@@ -19649,17 +19653,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>598464</v>
+        <v>598483</v>
       </c>
       <c r="R164" t="n">
-        <v>7330416</v>
+        <v>7330403</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -19713,12 +19717,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -19728,13 +19732,13 @@
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382712</t>
+          <t>https://artportalen.se/Sighting/135382388</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>135382717</v>
+        <v>135382712</v>
       </c>
       <c r="B165" t="n">
         <v>101375</v>
@@ -19769,10 +19773,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>598507</v>
+        <v>598464</v>
       </c>
       <c r="R165" t="n">
-        <v>7330626</v>
+        <v>7330416</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19804,7 +19808,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19814,7 +19818,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19844,13 +19848,13 @@
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382717</t>
+          <t>https://artportalen.se/Sighting/135382712</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>135382722</v>
+        <v>135382717</v>
       </c>
       <c r="B166" t="n">
         <v>101375</v>
@@ -19885,10 +19889,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>598467</v>
+        <v>598507</v>
       </c>
       <c r="R166" t="n">
-        <v>7330649</v>
+        <v>7330626</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19920,7 +19924,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19930,7 +19934,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19960,16 +19964,16 @@
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382722</t>
+          <t>https://artportalen.se/Sighting/135382717</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>135357130</v>
+        <v>135382722</v>
       </c>
       <c r="B167" t="n">
-        <v>102051</v>
+        <v>101375</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19977,34 +19981,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>225188</v>
+        <v>224885</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vanliga skogsvinbär</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Ribes spicatum subsp. spicatum</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr"/>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
       <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>598613</v>
+        <v>598467</v>
       </c>
       <c r="R167" t="n">
-        <v>7330353</v>
+        <v>7330649</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20031,22 +20035,22 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20055,7 +20059,6 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -20077,54 +20080,54 @@
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357130</t>
+          <t>https://artportalen.se/Sighting/135382722</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>135356852</v>
+        <v>135357130</v>
       </c>
       <c r="B168" t="n">
-        <v>92442</v>
+        <v>102051</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6040186</v>
+        <v>225188</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vanliga skogsvinbär</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
+          <t>Ribes spicatum subsp. spicatum</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>598735</v>
+        <v>598613</v>
       </c>
       <c r="R168" t="n">
-        <v>7330341</v>
+        <v>7330353</v>
       </c>
       <c r="S168" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -20153,7 +20156,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -20163,7 +20166,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20179,12 +20182,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -20194,13 +20197,13 @@
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356852</t>
+          <t>https://artportalen.se/Sighting/135357130</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>135357134</v>
+        <v>135356852</v>
       </c>
       <c r="B169" t="n">
         <v>92442</v>
@@ -20231,17 +20234,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>598723</v>
+        <v>598735</v>
       </c>
       <c r="R169" t="n">
-        <v>7330305</v>
+        <v>7330341</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -20270,7 +20273,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -20280,7 +20283,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20296,20 +20299,137 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356852</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>135357134</v>
+      </c>
+      <c r="B170" t="n">
+        <v>92442</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>598723</v>
+      </c>
+      <c r="R170" t="n">
+        <v>7330305</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AX169" t="inlineStr">
+      <c r="AX170" t="inlineStr">
         <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY169" t="inlineStr">
+      <c r="AY170" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
-      <c r="AZ169" t="inlineStr">
+      <c r="AZ170" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135357134</t>
         </is>
@@ -20485,6 +20605,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -7575,7 +7575,7 @@
         <v>135358275</v>
       </c>
       <c r="B61" t="n">
-        <v>87699</v>
+        <v>87700</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ170"/>
+  <dimension ref="A1:AZ169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7572,51 +7572,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135358275</v>
+        <v>135356210</v>
       </c>
       <c r="B61" t="n">
-        <v>87700</v>
+        <v>92446</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3639</v>
+        <v>4217</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rutspindling</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius ionophyllus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>598533</v>
+        <v>598603</v>
       </c>
       <c r="R61" t="n">
-        <v>7330307</v>
+        <v>7330411</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7645,7 +7642,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7655,7 +7652,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7664,19 +7661,18 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7686,13 +7682,13 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358275</t>
+          <t>https://artportalen.se/Sighting/135356210</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135356210</v>
+        <v>135356372</v>
       </c>
       <c r="B62" t="n">
         <v>92446</v>
@@ -7723,17 +7719,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>598603</v>
+        <v>598544</v>
       </c>
       <c r="R62" t="n">
-        <v>7330411</v>
+        <v>7330366</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7762,7 +7758,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7772,7 +7768,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7787,12 +7783,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7802,16 +7798,16 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356210</t>
+          <t>https://artportalen.se/Sighting/135356372</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135356372</v>
+        <v>135353513</v>
       </c>
       <c r="B63" t="n">
-        <v>92446</v>
+        <v>92013</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7819,37 +7815,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>598544</v>
+        <v>598811</v>
       </c>
       <c r="R63" t="n">
-        <v>7330366</v>
+        <v>7330371</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7878,7 +7874,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7888,7 +7884,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7903,12 +7899,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7918,38 +7914,38 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356372</t>
+          <t>https://artportalen.se/Sighting/135353513</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135353513</v>
+        <v>135353495</v>
       </c>
       <c r="B64" t="n">
-        <v>92013</v>
+        <v>79441</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7959,10 +7955,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>598811</v>
+        <v>598630</v>
       </c>
       <c r="R64" t="n">
-        <v>7330371</v>
+        <v>7330381</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7994,7 +7990,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8004,7 +8000,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8034,13 +8030,13 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353513</t>
+          <t>https://artportalen.se/Sighting/135353495</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135353495</v>
+        <v>135353515</v>
       </c>
       <c r="B65" t="n">
         <v>79441</v>
@@ -8075,10 +8071,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>598630</v>
+        <v>598809</v>
       </c>
       <c r="R65" t="n">
-        <v>7330381</v>
+        <v>7330378</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8110,7 +8106,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8120,7 +8116,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8150,13 +8146,13 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353495</t>
+          <t>https://artportalen.se/Sighting/135353515</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135353515</v>
+        <v>135356240</v>
       </c>
       <c r="B66" t="n">
         <v>79441</v>
@@ -8187,14 +8183,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>598809</v>
+        <v>598519</v>
       </c>
       <c r="R66" t="n">
-        <v>7330378</v>
+        <v>7330561</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8226,7 +8222,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8236,7 +8232,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8251,12 +8247,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -8266,13 +8262,13 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353515</t>
+          <t>https://artportalen.se/Sighting/135356240</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135356240</v>
+        <v>135356837</v>
       </c>
       <c r="B67" t="n">
         <v>79441</v>
@@ -8303,17 +8299,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>598519</v>
+        <v>598555</v>
       </c>
       <c r="R67" t="n">
-        <v>7330561</v>
+        <v>7330375</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8342,7 +8338,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8352,7 +8348,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8367,12 +8363,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8382,13 +8378,13 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356240</t>
+          <t>https://artportalen.se/Sighting/135356837</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135356837</v>
+        <v>135382466</v>
       </c>
       <c r="B68" t="n">
         <v>79441</v>
@@ -8419,17 +8415,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>598555</v>
+        <v>598537</v>
       </c>
       <c r="R68" t="n">
-        <v>7330375</v>
+        <v>7330657</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8453,22 +8449,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8483,12 +8479,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8498,13 +8494,13 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356837</t>
+          <t>https://artportalen.se/Sighting/135382466</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135382466</v>
+        <v>135384252</v>
       </c>
       <c r="B69" t="n">
         <v>79441</v>
@@ -8535,17 +8531,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>598537</v>
+        <v>598474</v>
       </c>
       <c r="R69" t="n">
-        <v>7330657</v>
+        <v>7330641</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8574,7 +8570,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8584,7 +8580,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8599,12 +8595,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8614,54 +8610,54 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382466</t>
+          <t>https://artportalen.se/Sighting/135384252</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135384252</v>
+        <v>135353509</v>
       </c>
       <c r="B70" t="n">
-        <v>79441</v>
+        <v>83428</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>598474</v>
+        <v>598768</v>
       </c>
       <c r="R70" t="n">
-        <v>7330641</v>
+        <v>7330331</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8685,22 +8681,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8715,12 +8711,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8730,13 +8726,13 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384252</t>
+          <t>https://artportalen.se/Sighting/135353509</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135353509</v>
+        <v>135356841</v>
       </c>
       <c r="B71" t="n">
         <v>83428</v>
@@ -8767,14 +8763,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>598768</v>
+        <v>598580</v>
       </c>
       <c r="R71" t="n">
-        <v>7330331</v>
+        <v>7330406</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8806,7 +8802,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8816,7 +8812,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8831,12 +8827,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8846,54 +8842,54 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353509</t>
+          <t>https://artportalen.se/Sighting/135356841</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135356841</v>
+        <v>135357126</v>
       </c>
       <c r="B72" t="n">
-        <v>83428</v>
+        <v>80561</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>598580</v>
+        <v>598552</v>
       </c>
       <c r="R72" t="n">
-        <v>7330406</v>
+        <v>7330359</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8922,7 +8918,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8932,7 +8928,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8947,12 +8943,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8962,54 +8958,59 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356841</t>
+          <t>https://artportalen.se/Sighting/135357126</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135357126</v>
+        <v>135353488</v>
       </c>
       <c r="B73" t="n">
-        <v>80561</v>
+        <v>57980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>598552</v>
+        <v>598564</v>
       </c>
       <c r="R73" t="n">
-        <v>7330359</v>
+        <v>7330345</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9038,7 +9039,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9048,7 +9049,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9063,12 +9064,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -9078,13 +9079,13 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357126</t>
+          <t>https://artportalen.se/Sighting/135353488</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135353488</v>
+        <v>135353503</v>
       </c>
       <c r="B74" t="n">
         <v>57980</v>
@@ -9115,7 +9116,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9124,10 +9125,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>598564</v>
+        <v>598672</v>
       </c>
       <c r="R74" t="n">
-        <v>7330345</v>
+        <v>7330311</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9159,7 +9160,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9169,7 +9170,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9199,13 +9200,13 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353488</t>
+          <t>https://artportalen.se/Sighting/135353503</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135353503</v>
+        <v>135356216</v>
       </c>
       <c r="B75" t="n">
         <v>57980</v>
@@ -9234,24 +9235,19 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>598672</v>
+        <v>598747</v>
       </c>
       <c r="R75" t="n">
-        <v>7330311</v>
+        <v>7330309</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9280,7 +9276,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9290,7 +9286,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Gamla och nya ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9305,12 +9306,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -9320,13 +9321,13 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353503</t>
+          <t>https://artportalen.se/Sighting/135356216</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135356216</v>
+        <v>135356376</v>
       </c>
       <c r="B76" t="n">
         <v>57980</v>
@@ -9355,19 +9356,27 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>598747</v>
+        <v>598614</v>
       </c>
       <c r="R76" t="n">
-        <v>7330309</v>
+        <v>7330356</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9396,7 +9405,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9406,19 +9415,19 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Gamla och nya ringhack</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
@@ -9426,12 +9435,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -9441,13 +9450,13 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356216</t>
+          <t>https://artportalen.se/Sighting/135356376</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135356376</v>
+        <v>135356380</v>
       </c>
       <c r="B77" t="n">
         <v>57980</v>
@@ -9490,13 +9499,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>598614</v>
+        <v>598877</v>
       </c>
       <c r="R77" t="n">
-        <v>7330356</v>
+        <v>7330349</v>
       </c>
       <c r="S77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9525,7 +9534,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9535,19 +9544,19 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="b">
         <v>0</v>
@@ -9560,7 +9569,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9570,13 +9579,13 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356376</t>
+          <t>https://artportalen.se/Sighting/135356380</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135356380</v>
+        <v>135357127</v>
       </c>
       <c r="B78" t="n">
         <v>57980</v>
@@ -9605,27 +9614,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>598877</v>
+        <v>598569</v>
       </c>
       <c r="R78" t="n">
-        <v>7330349</v>
+        <v>7330352</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9654,7 +9655,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9664,12 +9665,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9684,12 +9685,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9699,13 +9700,13 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356380</t>
+          <t>https://artportalen.se/Sighting/135357127</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135357127</v>
+        <v>135358283</v>
       </c>
       <c r="B79" t="n">
         <v>57980</v>
@@ -9736,17 +9737,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>598569</v>
+        <v>598609</v>
       </c>
       <c r="R79" t="n">
-        <v>7330352</v>
+        <v>7330298</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9775,7 +9776,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9785,7 +9786,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -9805,12 +9806,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9820,13 +9821,13 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357127</t>
+          <t>https://artportalen.se/Sighting/135358283</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135358283</v>
+        <v>135382716</v>
       </c>
       <c r="B80" t="n">
         <v>57980</v>
@@ -9855,19 +9856,27 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>598609</v>
+        <v>598482</v>
       </c>
       <c r="R80" t="n">
-        <v>7330298</v>
+        <v>7330489</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9891,27 +9900,27 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9926,12 +9935,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9941,13 +9950,13 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358283</t>
+          <t>https://artportalen.se/Sighting/135382716</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135382716</v>
+        <v>135382779</v>
       </c>
       <c r="B81" t="n">
         <v>57980</v>
@@ -9980,7 +9989,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -9990,10 +9999,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>598482</v>
+        <v>598462</v>
       </c>
       <c r="R81" t="n">
-        <v>7330489</v>
+        <v>7330447</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10025,7 +10034,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10035,12 +10044,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10070,13 +10079,13 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382716</t>
+          <t>https://artportalen.se/Sighting/135382779</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135382779</v>
+        <v>135384126</v>
       </c>
       <c r="B82" t="n">
         <v>57980</v>
@@ -10119,10 +10128,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>598462</v>
+        <v>598485</v>
       </c>
       <c r="R82" t="n">
-        <v>7330447</v>
+        <v>7330673</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10154,7 +10163,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10164,19 +10173,19 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG82" t="b">
         <v>0</v>
@@ -10184,12 +10193,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -10199,16 +10208,16 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382779</t>
+          <t>https://artportalen.se/Sighting/135384126</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135384126</v>
+        <v>135357215</v>
       </c>
       <c r="B83" t="n">
-        <v>57980</v>
+        <v>58141</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10216,21 +10225,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10238,20 +10247,20 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>598485</v>
+        <v>598501</v>
       </c>
       <c r="R83" t="n">
-        <v>7330673</v>
+        <v>7330475</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10278,34 +10287,34 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="b">
         <v>0</v>
@@ -10313,12 +10322,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -10328,13 +10337,13 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384126</t>
+          <t>https://artportalen.se/Sighting/135357215</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135357215</v>
+        <v>135382711</v>
       </c>
       <c r="B84" t="n">
         <v>58141</v>
@@ -10373,14 +10382,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>598501</v>
+        <v>598464</v>
       </c>
       <c r="R84" t="n">
-        <v>7330475</v>
+        <v>7330416</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10407,27 +10416,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10457,13 +10461,13 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357215</t>
+          <t>https://artportalen.se/Sighting/135382711</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135382711</v>
+        <v>135385939</v>
       </c>
       <c r="B85" t="n">
         <v>58141</v>
@@ -10492,24 +10496,16 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>598464</v>
+        <v>598491</v>
       </c>
       <c r="R85" t="n">
-        <v>7330416</v>
+        <v>7330361</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10541,7 +10537,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10551,7 +10547,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10566,12 +10562,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -10581,54 +10577,54 @@
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382711</t>
+          <t>https://artportalen.se/Sighting/135385939</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135385939</v>
+        <v>135382469</v>
       </c>
       <c r="B86" t="n">
-        <v>58141</v>
+        <v>99193</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>598491</v>
+        <v>598453</v>
       </c>
       <c r="R86" t="n">
-        <v>7330361</v>
+        <v>7330444</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10657,7 +10653,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10667,7 +10663,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10682,12 +10678,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10697,13 +10693,13 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135385939</t>
+          <t>https://artportalen.se/Sighting/135382469</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135382469</v>
+        <v>135384124</v>
       </c>
       <c r="B87" t="n">
         <v>99193</v>
@@ -10734,17 +10730,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>598453</v>
+        <v>598499</v>
       </c>
       <c r="R87" t="n">
-        <v>7330444</v>
+        <v>7330637</v>
       </c>
       <c r="S87" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10773,7 +10769,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10783,7 +10779,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10798,12 +10794,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10813,13 +10809,13 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382469</t>
+          <t>https://artportalen.se/Sighting/135384124</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135384124</v>
+        <v>135384162</v>
       </c>
       <c r="B88" t="n">
         <v>99193</v>
@@ -10854,10 +10850,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>598499</v>
+        <v>598449</v>
       </c>
       <c r="R88" t="n">
-        <v>7330637</v>
+        <v>7330355</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10889,7 +10885,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10899,7 +10895,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10929,16 +10925,16 @@
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384124</t>
+          <t>https://artportalen.se/Sighting/135384162</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135384162</v>
+        <v>94770073</v>
       </c>
       <c r="B89" t="n">
-        <v>99193</v>
+        <v>99120</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10946,37 +10942,43 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Laisan, Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>598449</v>
+        <v>598453</v>
       </c>
       <c r="R89" t="n">
-        <v>7330355</v>
+        <v>7330315</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11000,22 +11002,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11030,31 +11022,27 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Thomas Strid, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384162</t>
+          <t>https://artportalen.se/Sighting/94770073</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>94770073</v>
+        <v>135356843</v>
       </c>
       <c r="B90" t="n">
-        <v>99120</v>
+        <v>99180</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11062,43 +11050,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219811</v>
+        <v>220093</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Laisan, Arjeplog, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>598453</v>
+        <v>598607</v>
       </c>
       <c r="R90" t="n">
-        <v>7330315</v>
+        <v>7330382</v>
       </c>
       <c r="S90" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11122,12 +11104,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11142,27 +11134,31 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Thomas Strid, Tiina Laantee</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94770073</t>
+          <t>https://artportalen.se/Sighting/135356843</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135356843</v>
+        <v>135353481</v>
       </c>
       <c r="B91" t="n">
-        <v>99180</v>
+        <v>110014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11170,34 +11166,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220093</v>
+        <v>221184</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>598607</v>
+        <v>598529</v>
       </c>
       <c r="R91" t="n">
-        <v>7330382</v>
+        <v>7330341</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -11229,7 +11225,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11239,7 +11235,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11254,12 +11250,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11269,13 +11265,13 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356843</t>
+          <t>https://artportalen.se/Sighting/135353481</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135353481</v>
+        <v>135353512</v>
       </c>
       <c r="B92" t="n">
         <v>110014</v>
@@ -11310,10 +11306,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>598529</v>
+        <v>598793</v>
       </c>
       <c r="R92" t="n">
-        <v>7330341</v>
+        <v>7330350</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -11345,7 +11341,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11355,7 +11351,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11385,13 +11381,13 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353481</t>
+          <t>https://artportalen.se/Sighting/135353512</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135353512</v>
+        <v>135356205</v>
       </c>
       <c r="B93" t="n">
         <v>110014</v>
@@ -11422,14 +11418,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>598793</v>
+        <v>598518</v>
       </c>
       <c r="R93" t="n">
-        <v>7330350</v>
+        <v>7330341</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11461,7 +11457,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11471,7 +11467,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11486,12 +11482,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -11501,13 +11497,13 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353512</t>
+          <t>https://artportalen.se/Sighting/135356205</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135356205</v>
+        <v>135356241</v>
       </c>
       <c r="B94" t="n">
         <v>110014</v>
@@ -11542,10 +11538,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>598518</v>
+        <v>598490</v>
       </c>
       <c r="R94" t="n">
-        <v>7330341</v>
+        <v>7330565</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11577,7 +11573,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11587,7 +11583,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11617,13 +11613,13 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356205</t>
+          <t>https://artportalen.se/Sighting/135356241</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135356241</v>
+        <v>135357137</v>
       </c>
       <c r="B95" t="n">
         <v>110014</v>
@@ -11654,17 +11650,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>598490</v>
+        <v>598751</v>
       </c>
       <c r="R95" t="n">
-        <v>7330565</v>
+        <v>7330316</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11693,7 +11689,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11703,7 +11699,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11718,12 +11714,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11733,13 +11729,13 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356241</t>
+          <t>https://artportalen.se/Sighting/135357137</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135357137</v>
+        <v>135357141</v>
       </c>
       <c r="B96" t="n">
         <v>110014</v>
@@ -11774,10 +11770,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>598751</v>
+        <v>598770</v>
       </c>
       <c r="R96" t="n">
-        <v>7330316</v>
+        <v>7330338</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11809,7 +11805,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11819,7 +11815,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11849,13 +11845,13 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357137</t>
+          <t>https://artportalen.se/Sighting/135357141</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135357141</v>
+        <v>135357201</v>
       </c>
       <c r="B97" t="n">
         <v>110014</v>
@@ -11890,10 +11886,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>598770</v>
+        <v>598553</v>
       </c>
       <c r="R97" t="n">
-        <v>7330338</v>
+        <v>7330578</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11925,7 +11921,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11935,7 +11931,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11965,13 +11961,13 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357141</t>
+          <t>https://artportalen.se/Sighting/135357201</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135357201</v>
+        <v>135357211</v>
       </c>
       <c r="B98" t="n">
         <v>110014</v>
@@ -12006,10 +12002,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>598553</v>
+        <v>598501</v>
       </c>
       <c r="R98" t="n">
-        <v>7330578</v>
+        <v>7330515</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12041,7 +12037,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12051,7 +12047,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12081,13 +12077,13 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357201</t>
+          <t>https://artportalen.se/Sighting/135357211</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135357211</v>
+        <v>135357212</v>
       </c>
       <c r="B99" t="n">
         <v>110014</v>
@@ -12122,10 +12118,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>598501</v>
+        <v>598498</v>
       </c>
       <c r="R99" t="n">
-        <v>7330515</v>
+        <v>7330492</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12157,7 +12153,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12167,7 +12163,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12197,13 +12193,13 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357211</t>
+          <t>https://artportalen.se/Sighting/135357212</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135357212</v>
+        <v>135358269</v>
       </c>
       <c r="B100" t="n">
         <v>110014</v>
@@ -12234,17 +12230,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>598498</v>
+        <v>598578</v>
       </c>
       <c r="R100" t="n">
-        <v>7330492</v>
+        <v>7330329</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12273,7 +12269,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12283,7 +12279,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12298,12 +12294,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12313,13 +12309,13 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357212</t>
+          <t>https://artportalen.se/Sighting/135358269</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135358269</v>
+        <v>135358276</v>
       </c>
       <c r="B101" t="n">
         <v>110014</v>
@@ -12354,10 +12350,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>598578</v>
+        <v>598542</v>
       </c>
       <c r="R101" t="n">
-        <v>7330329</v>
+        <v>7330305</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12389,7 +12385,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12399,7 +12395,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12429,13 +12425,13 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358269</t>
+          <t>https://artportalen.se/Sighting/135358276</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135358276</v>
+        <v>135358292</v>
       </c>
       <c r="B102" t="n">
         <v>110014</v>
@@ -12470,10 +12466,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>598542</v>
+        <v>598827</v>
       </c>
       <c r="R102" t="n">
-        <v>7330305</v>
+        <v>7330278</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12505,7 +12501,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12515,7 +12511,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12545,13 +12541,13 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358276</t>
+          <t>https://artportalen.se/Sighting/135358292</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135358292</v>
+        <v>135358342</v>
       </c>
       <c r="B103" t="n">
         <v>110014</v>
@@ -12586,10 +12582,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>598827</v>
+        <v>598546</v>
       </c>
       <c r="R103" t="n">
-        <v>7330278</v>
+        <v>7330653</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12621,7 +12617,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12631,7 +12627,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12661,13 +12657,13 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358292</t>
+          <t>https://artportalen.se/Sighting/135358342</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135358342</v>
+        <v>135382720</v>
       </c>
       <c r="B104" t="n">
         <v>110014</v>
@@ -12698,17 +12694,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>598546</v>
+        <v>598507</v>
       </c>
       <c r="R104" t="n">
-        <v>7330653</v>
+        <v>7330626</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12732,22 +12728,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12762,12 +12758,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12777,13 +12773,13 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358342</t>
+          <t>https://artportalen.se/Sighting/135382720</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135382720</v>
+        <v>135382723</v>
       </c>
       <c r="B105" t="n">
         <v>110014</v>
@@ -12818,10 +12814,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>598507</v>
+        <v>598467</v>
       </c>
       <c r="R105" t="n">
-        <v>7330626</v>
+        <v>7330649</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12853,7 +12849,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12863,7 +12859,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12893,16 +12889,16 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382720</t>
+          <t>https://artportalen.se/Sighting/135382723</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135382723</v>
+        <v>135353491</v>
       </c>
       <c r="B106" t="n">
-        <v>110014</v>
+        <v>106398</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12910,16 +12906,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221184</v>
+        <v>221725</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -12930,17 +12926,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>598467</v>
+        <v>598592</v>
       </c>
       <c r="R106" t="n">
-        <v>7330649</v>
+        <v>7330348</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12964,22 +12960,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12994,12 +12990,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -13009,13 +13005,13 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382723</t>
+          <t>https://artportalen.se/Sighting/135353491</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135353491</v>
+        <v>135356209</v>
       </c>
       <c r="B107" t="n">
         <v>106398</v>
@@ -13046,14 +13042,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>598592</v>
+        <v>598597</v>
       </c>
       <c r="R107" t="n">
-        <v>7330348</v>
+        <v>7330383</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -13085,7 +13081,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13095,7 +13091,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13110,12 +13106,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -13125,13 +13121,13 @@
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353491</t>
+          <t>https://artportalen.se/Sighting/135356209</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135356209</v>
+        <v>135356218</v>
       </c>
       <c r="B108" t="n">
         <v>106398</v>
@@ -13166,10 +13162,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>598597</v>
+        <v>598785</v>
       </c>
       <c r="R108" t="n">
-        <v>7330383</v>
+        <v>7330366</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -13201,7 +13197,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13211,7 +13207,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13241,13 +13237,13 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356209</t>
+          <t>https://artportalen.se/Sighting/135356218</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135356218</v>
+        <v>135356839</v>
       </c>
       <c r="B109" t="n">
         <v>106398</v>
@@ -13278,17 +13274,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>598785</v>
+        <v>598557</v>
       </c>
       <c r="R109" t="n">
-        <v>7330366</v>
+        <v>7330411</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13317,7 +13313,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13327,7 +13323,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13342,12 +13338,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -13357,13 +13353,13 @@
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356218</t>
+          <t>https://artportalen.se/Sighting/135356839</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135356839</v>
+        <v>135356886</v>
       </c>
       <c r="B110" t="n">
         <v>106398</v>
@@ -13398,13 +13394,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>598557</v>
+        <v>598518</v>
       </c>
       <c r="R110" t="n">
-        <v>7330411</v>
+        <v>7330476</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13433,7 +13429,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13443,7 +13439,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13473,13 +13469,13 @@
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356839</t>
+          <t>https://artportalen.se/Sighting/135356886</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135356886</v>
+        <v>135358270</v>
       </c>
       <c r="B111" t="n">
         <v>106398</v>
@@ -13510,17 +13506,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>598518</v>
+        <v>598568</v>
       </c>
       <c r="R111" t="n">
-        <v>7330476</v>
+        <v>7330339</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13549,7 +13545,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13559,7 +13555,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13574,12 +13570,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -13589,13 +13585,13 @@
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356886</t>
+          <t>https://artportalen.se/Sighting/135358270</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135358270</v>
+        <v>135358287</v>
       </c>
       <c r="B112" t="n">
         <v>106398</v>
@@ -13630,10 +13626,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>598568</v>
+        <v>598754</v>
       </c>
       <c r="R112" t="n">
-        <v>7330339</v>
+        <v>7330326</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13665,7 +13661,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13675,7 +13671,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13705,16 +13701,16 @@
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358270</t>
+          <t>https://artportalen.se/Sighting/135358287</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135358287</v>
+        <v>135356206</v>
       </c>
       <c r="B113" t="n">
-        <v>106398</v>
+        <v>98138</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13722,37 +13718,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>598754</v>
+        <v>598569</v>
       </c>
       <c r="R113" t="n">
-        <v>7330326</v>
+        <v>7330354</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13781,7 +13777,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13791,7 +13787,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13806,12 +13802,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13821,13 +13817,13 @@
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358287</t>
+          <t>https://artportalen.se/Sighting/135356206</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135356206</v>
+        <v>135356243</v>
       </c>
       <c r="B114" t="n">
         <v>98138</v>
@@ -13862,10 +13858,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>598569</v>
+        <v>598482</v>
       </c>
       <c r="R114" t="n">
-        <v>7330354</v>
+        <v>7330539</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13897,7 +13893,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13907,7 +13903,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13937,13 +13933,13 @@
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356206</t>
+          <t>https://artportalen.se/Sighting/135356243</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135356243</v>
+        <v>135356845</v>
       </c>
       <c r="B115" t="n">
         <v>98138</v>
@@ -13974,17 +13970,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>598482</v>
+        <v>598624</v>
       </c>
       <c r="R115" t="n">
-        <v>7330539</v>
+        <v>7330372</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14013,7 +14009,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14023,7 +14019,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14038,12 +14034,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -14053,13 +14049,13 @@
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356243</t>
+          <t>https://artportalen.se/Sighting/135356845</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135356845</v>
+        <v>135356884</v>
       </c>
       <c r="B116" t="n">
         <v>98138</v>
@@ -14094,13 +14090,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>598624</v>
+        <v>598495</v>
       </c>
       <c r="R116" t="n">
-        <v>7330372</v>
+        <v>7330628</v>
       </c>
       <c r="S116" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14129,7 +14125,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14139,7 +14135,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14169,13 +14165,13 @@
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356845</t>
+          <t>https://artportalen.se/Sighting/135356884</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135356884</v>
+        <v>135358281</v>
       </c>
       <c r="B117" t="n">
         <v>98138</v>
@@ -14206,14 +14202,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>598495</v>
+        <v>598605</v>
       </c>
       <c r="R117" t="n">
-        <v>7330628</v>
+        <v>7330324</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14245,7 +14241,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14255,7 +14251,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14270,12 +14266,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -14285,13 +14281,13 @@
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356884</t>
+          <t>https://artportalen.se/Sighting/135358281</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135358281</v>
+        <v>135382031</v>
       </c>
       <c r="B118" t="n">
         <v>98138</v>
@@ -14322,17 +14318,17 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>598605</v>
+        <v>598459</v>
       </c>
       <c r="R118" t="n">
-        <v>7330324</v>
+        <v>7330572</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14356,22 +14352,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14386,12 +14382,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -14401,13 +14397,13 @@
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358281</t>
+          <t>https://artportalen.se/Sighting/135382031</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135382031</v>
+        <v>135382032</v>
       </c>
       <c r="B119" t="n">
         <v>98138</v>
@@ -14442,13 +14438,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>598459</v>
+        <v>598472</v>
       </c>
       <c r="R119" t="n">
-        <v>7330572</v>
+        <v>7330674</v>
       </c>
       <c r="S119" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14517,13 +14513,13 @@
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382031</t>
+          <t>https://artportalen.se/Sighting/135382032</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135382032</v>
+        <v>135384245</v>
       </c>
       <c r="B120" t="n">
         <v>98138</v>
@@ -14554,14 +14550,14 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>598472</v>
+        <v>598522</v>
       </c>
       <c r="R120" t="n">
-        <v>7330674</v>
+        <v>7330575</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14593,7 +14589,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14603,7 +14599,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14618,12 +14614,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -14633,13 +14629,13 @@
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382032</t>
+          <t>https://artportalen.se/Sighting/135384245</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135384245</v>
+        <v>135384249</v>
       </c>
       <c r="B121" t="n">
         <v>98138</v>
@@ -14674,13 +14670,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>598522</v>
+        <v>598492</v>
       </c>
       <c r="R121" t="n">
-        <v>7330575</v>
+        <v>7330652</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14709,7 +14705,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14719,7 +14715,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14749,16 +14745,16 @@
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384245</t>
+          <t>https://artportalen.se/Sighting/135384249</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135384249</v>
+        <v>135353486</v>
       </c>
       <c r="B122" t="n">
-        <v>98138</v>
+        <v>99298</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14766,37 +14762,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>598492</v>
+        <v>598555</v>
       </c>
       <c r="R122" t="n">
-        <v>7330652</v>
+        <v>7330349</v>
       </c>
       <c r="S122" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14820,22 +14816,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14850,12 +14846,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -14865,13 +14861,13 @@
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384249</t>
+          <t>https://artportalen.se/Sighting/135353486</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135353486</v>
+        <v>135353494</v>
       </c>
       <c r="B123" t="n">
         <v>99298</v>
@@ -14906,10 +14902,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>598555</v>
+        <v>598634</v>
       </c>
       <c r="R123" t="n">
-        <v>7330349</v>
+        <v>7330375</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14941,7 +14937,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14951,7 +14947,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14981,13 +14977,13 @@
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353486</t>
+          <t>https://artportalen.se/Sighting/135353494</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135353494</v>
+        <v>135353497</v>
       </c>
       <c r="B124" t="n">
         <v>99298</v>
@@ -15022,10 +15018,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>598634</v>
+        <v>598665</v>
       </c>
       <c r="R124" t="n">
-        <v>7330375</v>
+        <v>7330360</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -15057,7 +15053,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15067,7 +15063,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15097,13 +15093,13 @@
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353494</t>
+          <t>https://artportalen.se/Sighting/135353497</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135353497</v>
+        <v>135356211</v>
       </c>
       <c r="B125" t="n">
         <v>99298</v>
@@ -15134,14 +15130,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>598665</v>
+        <v>598644</v>
       </c>
       <c r="R125" t="n">
-        <v>7330360</v>
+        <v>7330364</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15173,7 +15169,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15183,7 +15179,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15198,12 +15194,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -15213,13 +15209,13 @@
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353497</t>
+          <t>https://artportalen.se/Sighting/135356211</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135356211</v>
+        <v>135356213</v>
       </c>
       <c r="B126" t="n">
         <v>99298</v>
@@ -15254,13 +15250,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>598644</v>
+        <v>598651</v>
       </c>
       <c r="R126" t="n">
-        <v>7330364</v>
+        <v>7330373</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15289,7 +15285,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15299,7 +15295,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15329,13 +15325,13 @@
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356211</t>
+          <t>https://artportalen.se/Sighting/135356213</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135356213</v>
+        <v>135356844</v>
       </c>
       <c r="B127" t="n">
         <v>99298</v>
@@ -15366,17 +15362,17 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>598651</v>
+        <v>598607</v>
       </c>
       <c r="R127" t="n">
-        <v>7330373</v>
+        <v>7330382</v>
       </c>
       <c r="S127" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15405,7 +15401,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15415,7 +15411,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15430,12 +15426,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -15445,13 +15441,13 @@
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356213</t>
+          <t>https://artportalen.se/Sighting/135356844</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135356844</v>
+        <v>135356846</v>
       </c>
       <c r="B128" t="n">
         <v>99298</v>
@@ -15486,10 +15482,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>598607</v>
+        <v>598653</v>
       </c>
       <c r="R128" t="n">
-        <v>7330382</v>
+        <v>7330343</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15521,7 +15517,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15531,7 +15527,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15561,13 +15557,13 @@
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356844</t>
+          <t>https://artportalen.se/Sighting/135356846</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>135356846</v>
+        <v>135356856</v>
       </c>
       <c r="B129" t="n">
         <v>99298</v>
@@ -15602,13 +15598,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>598653</v>
+        <v>598841</v>
       </c>
       <c r="R129" t="n">
-        <v>7330343</v>
+        <v>7330355</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15637,7 +15633,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15647,7 +15643,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15677,13 +15673,13 @@
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356846</t>
+          <t>https://artportalen.se/Sighting/135356856</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>135356856</v>
+        <v>135362163</v>
       </c>
       <c r="B130" t="n">
         <v>99298</v>
@@ -15714,17 +15710,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>598841</v>
+        <v>598808</v>
       </c>
       <c r="R130" t="n">
-        <v>7330355</v>
+        <v>7330337</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15751,19 +15747,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>11:49</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15778,12 +15764,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -15793,13 +15779,13 @@
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356856</t>
+          <t>https://artportalen.se/Sighting/135362163</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>135362163</v>
+        <v>135382721</v>
       </c>
       <c r="B131" t="n">
         <v>99298</v>
@@ -15830,17 +15816,17 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>598808</v>
+        <v>598467</v>
       </c>
       <c r="R131" t="n">
-        <v>7330337</v>
+        <v>7330649</v>
       </c>
       <c r="S131" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15864,12 +15850,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15884,12 +15880,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -15899,13 +15895,13 @@
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135362163</t>
+          <t>https://artportalen.se/Sighting/135382721</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>135382721</v>
+        <v>135384251</v>
       </c>
       <c r="B132" t="n">
         <v>99298</v>
@@ -15936,14 +15932,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>598467</v>
+        <v>598482</v>
       </c>
       <c r="R132" t="n">
-        <v>7330649</v>
+        <v>7330639</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15975,7 +15971,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15985,7 +15981,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16000,12 +15996,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -16015,16 +16011,16 @@
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382721</t>
+          <t>https://artportalen.se/Sighting/135384251</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135384251</v>
+        <v>135353490</v>
       </c>
       <c r="B133" t="n">
-        <v>99298</v>
+        <v>104795</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16032,37 +16028,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221952</v>
+        <v>222412</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>598482</v>
+        <v>598591</v>
       </c>
       <c r="R133" t="n">
-        <v>7330639</v>
+        <v>7330353</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16086,22 +16082,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16116,12 +16112,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -16131,13 +16127,13 @@
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384251</t>
+          <t>https://artportalen.se/Sighting/135353490</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>135353490</v>
+        <v>135357136</v>
       </c>
       <c r="B134" t="n">
         <v>104795</v>
@@ -16168,17 +16164,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>598591</v>
+        <v>598751</v>
       </c>
       <c r="R134" t="n">
-        <v>7330353</v>
+        <v>7330316</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16207,7 +16203,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16217,7 +16213,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16232,12 +16228,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -16247,13 +16243,13 @@
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353490</t>
+          <t>https://artportalen.se/Sighting/135357136</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>135357136</v>
+        <v>135362160</v>
       </c>
       <c r="B135" t="n">
         <v>104795</v>
@@ -16288,13 +16284,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>598751</v>
+        <v>598552</v>
       </c>
       <c r="R135" t="n">
-        <v>7330316</v>
+        <v>7330368</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16321,19 +16317,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16348,12 +16334,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -16363,16 +16349,16 @@
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357136</t>
+          <t>https://artportalen.se/Sighting/135362160</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135362160</v>
+        <v>135358271</v>
       </c>
       <c r="B136" t="n">
-        <v>104795</v>
+        <v>99286</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16380,37 +16366,41 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>222412</v>
+        <v>222495</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Myggblomster</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hammarbya paludosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Kuntze</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>598552</v>
+        <v>598585</v>
       </c>
       <c r="R136" t="n">
-        <v>7330368</v>
+        <v>7330354</v>
       </c>
       <c r="S136" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16437,29 +16427,40 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -16469,13 +16470,13 @@
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135362160</t>
+          <t>https://artportalen.se/Sighting/135358271</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>135358271</v>
+        <v>135358274</v>
       </c>
       <c r="B137" t="n">
         <v>99286</v>
@@ -16514,13 +16515,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>598585</v>
+        <v>598543</v>
       </c>
       <c r="R137" t="n">
-        <v>7330354</v>
+        <v>7330322</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16549,7 +16550,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16559,7 +16560,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16590,13 +16591,13 @@
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358271</t>
+          <t>https://artportalen.se/Sighting/135358274</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>135358274</v>
+        <v>135358278</v>
       </c>
       <c r="B138" t="n">
         <v>99286</v>
@@ -16635,13 +16636,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>598543</v>
+        <v>598566</v>
       </c>
       <c r="R138" t="n">
-        <v>7330322</v>
+        <v>7330282</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16670,7 +16671,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16680,7 +16681,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16711,16 +16712,16 @@
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358274</t>
+          <t>https://artportalen.se/Sighting/135358278</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>135358278</v>
+        <v>135356838</v>
       </c>
       <c r="B139" t="n">
-        <v>99286</v>
+        <v>98292</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16728,41 +16729,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>222495</v>
+        <v>222741</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Myggblomster</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hammarbya paludosa</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Kuntze</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>598566</v>
+        <v>598555</v>
       </c>
       <c r="R139" t="n">
-        <v>7330282</v>
+        <v>7330375</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16791,7 +16788,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16801,7 +16798,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16810,19 +16807,18 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -16832,13 +16828,13 @@
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358278</t>
+          <t>https://artportalen.se/Sighting/135356838</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>135356838</v>
+        <v>135357146</v>
       </c>
       <c r="B140" t="n">
         <v>98292</v>
@@ -16869,17 +16865,17 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>598555</v>
+        <v>598911</v>
       </c>
       <c r="R140" t="n">
-        <v>7330375</v>
+        <v>7330350</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16908,7 +16904,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16918,7 +16914,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16933,12 +16929,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -16948,13 +16944,13 @@
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356838</t>
+          <t>https://artportalen.se/Sighting/135357146</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>135357146</v>
+        <v>135357209</v>
       </c>
       <c r="B141" t="n">
         <v>98292</v>
@@ -16989,10 +16985,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>598911</v>
+        <v>598519</v>
       </c>
       <c r="R141" t="n">
-        <v>7330350</v>
+        <v>7330570</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17024,7 +17020,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17034,7 +17030,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17064,16 +17060,16 @@
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357146</t>
+          <t>https://artportalen.se/Sighting/135357209</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>135357209</v>
+        <v>135357123</v>
       </c>
       <c r="B142" t="n">
-        <v>98292</v>
+        <v>102956</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17081,21 +17077,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>222741</v>
+        <v>223037</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -17105,10 +17101,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>598519</v>
+        <v>598552</v>
       </c>
       <c r="R142" t="n">
-        <v>7330570</v>
+        <v>7330359</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17140,7 +17136,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17150,7 +17146,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17180,13 +17176,13 @@
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357209</t>
+          <t>https://artportalen.se/Sighting/135357123</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>135357123</v>
+        <v>135357202</v>
       </c>
       <c r="B143" t="n">
         <v>102956</v>
@@ -17221,10 +17217,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>598552</v>
+        <v>598553</v>
       </c>
       <c r="R143" t="n">
-        <v>7330359</v>
+        <v>7330578</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17256,7 +17252,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17266,7 +17262,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17296,13 +17292,13 @@
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357123</t>
+          <t>https://artportalen.se/Sighting/135357202</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>135357202</v>
+        <v>135382713</v>
       </c>
       <c r="B144" t="n">
         <v>102956</v>
@@ -17333,14 +17329,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>598553</v>
+        <v>598464</v>
       </c>
       <c r="R144" t="n">
-        <v>7330578</v>
+        <v>7330416</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17367,22 +17363,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17412,13 +17408,13 @@
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357202</t>
+          <t>https://artportalen.se/Sighting/135382713</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>135382713</v>
+        <v>135382724</v>
       </c>
       <c r="B145" t="n">
         <v>102956</v>
@@ -17453,10 +17449,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>598464</v>
+        <v>598467</v>
       </c>
       <c r="R145" t="n">
-        <v>7330416</v>
+        <v>7330649</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17488,7 +17484,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -17498,7 +17494,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17528,16 +17524,16 @@
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382713</t>
+          <t>https://artportalen.se/Sighting/135382724</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>135382724</v>
+        <v>135357122</v>
       </c>
       <c r="B146" t="n">
-        <v>102956</v>
+        <v>98327</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17545,34 +17541,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>223037</v>
+        <v>223358</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>598467</v>
+        <v>598552</v>
       </c>
       <c r="R146" t="n">
-        <v>7330649</v>
+        <v>7330359</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17599,22 +17595,22 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17644,13 +17640,13 @@
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382724</t>
+          <t>https://artportalen.se/Sighting/135357122</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>135357122</v>
+        <v>135357145</v>
       </c>
       <c r="B147" t="n">
         <v>98327</v>
@@ -17685,10 +17681,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>598552</v>
+        <v>598911</v>
       </c>
       <c r="R147" t="n">
-        <v>7330359</v>
+        <v>7330350</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17720,7 +17716,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17730,7 +17726,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17760,13 +17756,13 @@
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357122</t>
+          <t>https://artportalen.se/Sighting/135357145</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>135357145</v>
+        <v>135358277</v>
       </c>
       <c r="B148" t="n">
         <v>98327</v>
@@ -17797,17 +17793,17 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>598911</v>
+        <v>598551</v>
       </c>
       <c r="R148" t="n">
-        <v>7330350</v>
+        <v>7330296</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17836,7 +17832,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17846,7 +17842,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17861,12 +17857,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -17876,13 +17872,13 @@
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357145</t>
+          <t>https://artportalen.se/Sighting/135358277</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>135358277</v>
+        <v>135382718</v>
       </c>
       <c r="B149" t="n">
         <v>98327</v>
@@ -17913,17 +17909,17 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>598551</v>
+        <v>598507</v>
       </c>
       <c r="R149" t="n">
-        <v>7330296</v>
+        <v>7330626</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17947,22 +17943,22 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17977,12 +17973,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -17992,16 +17988,16 @@
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358277</t>
+          <t>https://artportalen.se/Sighting/135382718</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>135382718</v>
+        <v>135353482</v>
       </c>
       <c r="B150" t="n">
-        <v>98327</v>
+        <v>101375</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18009,37 +18005,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>598507</v>
+        <v>598530</v>
       </c>
       <c r="R150" t="n">
-        <v>7330626</v>
+        <v>7330340</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18063,22 +18059,22 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18093,12 +18089,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -18108,13 +18104,13 @@
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382718</t>
+          <t>https://artportalen.se/Sighting/135353482</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>135353482</v>
+        <v>135357117</v>
       </c>
       <c r="B151" t="n">
         <v>101375</v>
@@ -18145,17 +18141,17 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>598530</v>
+        <v>598525</v>
       </c>
       <c r="R151" t="n">
-        <v>7330340</v>
+        <v>7330346</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -18209,12 +18205,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -18224,13 +18220,13 @@
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353482</t>
+          <t>https://artportalen.se/Sighting/135357117</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>135357117</v>
+        <v>135357120</v>
       </c>
       <c r="B152" t="n">
         <v>101375</v>
@@ -18265,10 +18261,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>598525</v>
+        <v>598552</v>
       </c>
       <c r="R152" t="n">
-        <v>7330346</v>
+        <v>7330359</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18300,7 +18296,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18310,7 +18306,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18340,13 +18336,13 @@
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357117</t>
+          <t>https://artportalen.se/Sighting/135357120</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>135357120</v>
+        <v>135357138</v>
       </c>
       <c r="B153" t="n">
         <v>101375</v>
@@ -18381,10 +18377,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>598552</v>
+        <v>598751</v>
       </c>
       <c r="R153" t="n">
-        <v>7330359</v>
+        <v>7330316</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18416,7 +18412,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18426,7 +18422,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18456,13 +18452,13 @@
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357120</t>
+          <t>https://artportalen.se/Sighting/135357138</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>135357138</v>
+        <v>135357140</v>
       </c>
       <c r="B154" t="n">
         <v>101375</v>
@@ -18497,10 +18493,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>598751</v>
+        <v>598770</v>
       </c>
       <c r="R154" t="n">
-        <v>7330316</v>
+        <v>7330338</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18532,7 +18528,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -18542,7 +18538,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18572,13 +18568,13 @@
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357138</t>
+          <t>https://artportalen.se/Sighting/135357140</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>135357140</v>
+        <v>135357147</v>
       </c>
       <c r="B155" t="n">
         <v>101375</v>
@@ -18613,10 +18609,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>598770</v>
+        <v>598911</v>
       </c>
       <c r="R155" t="n">
-        <v>7330338</v>
+        <v>7330350</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18648,7 +18644,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18658,7 +18654,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18688,13 +18684,13 @@
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357140</t>
+          <t>https://artportalen.se/Sighting/135357147</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>135357147</v>
+        <v>135357205</v>
       </c>
       <c r="B156" t="n">
         <v>101375</v>
@@ -18729,10 +18725,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>598911</v>
+        <v>598553</v>
       </c>
       <c r="R156" t="n">
-        <v>7330350</v>
+        <v>7330578</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18764,7 +18760,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18774,7 +18770,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18804,13 +18800,13 @@
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357147</t>
+          <t>https://artportalen.se/Sighting/135357205</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>135357205</v>
+        <v>135357206</v>
       </c>
       <c r="B157" t="n">
         <v>101375</v>
@@ -18845,10 +18841,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>598553</v>
+        <v>598521</v>
       </c>
       <c r="R157" t="n">
-        <v>7330578</v>
+        <v>7330581</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18880,7 +18876,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18890,7 +18886,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18920,13 +18916,13 @@
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357205</t>
+          <t>https://artportalen.se/Sighting/135357206</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>135357206</v>
+        <v>135357213</v>
       </c>
       <c r="B158" t="n">
         <v>101375</v>
@@ -18961,10 +18957,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>598521</v>
+        <v>598501</v>
       </c>
       <c r="R158" t="n">
-        <v>7330581</v>
+        <v>7330475</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18996,7 +18992,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -19006,7 +19002,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19036,13 +19032,13 @@
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357206</t>
+          <t>https://artportalen.se/Sighting/135357213</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>135357213</v>
+        <v>135358268</v>
       </c>
       <c r="B159" t="n">
         <v>101375</v>
@@ -19073,17 +19069,17 @@
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>598501</v>
+        <v>598580</v>
       </c>
       <c r="R159" t="n">
-        <v>7330475</v>
+        <v>7330339</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -19112,7 +19108,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19122,7 +19118,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19137,12 +19133,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -19152,13 +19148,13 @@
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357213</t>
+          <t>https://artportalen.se/Sighting/135358268</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>135358268</v>
+        <v>135358284</v>
       </c>
       <c r="B160" t="n">
         <v>101375</v>
@@ -19193,10 +19189,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>598580</v>
+        <v>598610</v>
       </c>
       <c r="R160" t="n">
-        <v>7330339</v>
+        <v>7330295</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -19228,7 +19224,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19238,7 +19234,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19268,13 +19264,13 @@
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358268</t>
+          <t>https://artportalen.se/Sighting/135358284</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>135358284</v>
+        <v>135358293</v>
       </c>
       <c r="B161" t="n">
         <v>101375</v>
@@ -19309,10 +19305,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>598610</v>
+        <v>598830</v>
       </c>
       <c r="R161" t="n">
-        <v>7330295</v>
+        <v>7330303</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -19344,7 +19340,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19354,7 +19350,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19384,13 +19380,13 @@
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358284</t>
+          <t>https://artportalen.se/Sighting/135358293</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>135358293</v>
+        <v>135358341</v>
       </c>
       <c r="B162" t="n">
         <v>101375</v>
@@ -19425,10 +19421,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>598830</v>
+        <v>598546</v>
       </c>
       <c r="R162" t="n">
-        <v>7330303</v>
+        <v>7330653</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -19460,7 +19456,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19470,7 +19466,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19500,13 +19496,13 @@
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358293</t>
+          <t>https://artportalen.se/Sighting/135358341</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>135358341</v>
+        <v>135382388</v>
       </c>
       <c r="B163" t="n">
         <v>101375</v>
@@ -19537,14 +19533,14 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>598546</v>
+        <v>598483</v>
       </c>
       <c r="R163" t="n">
-        <v>7330653</v>
+        <v>7330403</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -19571,22 +19567,22 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19601,12 +19597,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -19616,13 +19612,13 @@
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358341</t>
+          <t>https://artportalen.se/Sighting/135382388</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>135382388</v>
+        <v>135382712</v>
       </c>
       <c r="B164" t="n">
         <v>101375</v>
@@ -19653,17 +19649,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>598483</v>
+        <v>598464</v>
       </c>
       <c r="R164" t="n">
-        <v>7330403</v>
+        <v>7330416</v>
       </c>
       <c r="S164" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -19717,12 +19713,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -19732,13 +19728,13 @@
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382388</t>
+          <t>https://artportalen.se/Sighting/135382712</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>135382712</v>
+        <v>135382717</v>
       </c>
       <c r="B165" t="n">
         <v>101375</v>
@@ -19773,10 +19769,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>598464</v>
+        <v>598507</v>
       </c>
       <c r="R165" t="n">
-        <v>7330416</v>
+        <v>7330626</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19808,7 +19804,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19818,7 +19814,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19848,13 +19844,13 @@
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382712</t>
+          <t>https://artportalen.se/Sighting/135382717</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>135382717</v>
+        <v>135382722</v>
       </c>
       <c r="B166" t="n">
         <v>101375</v>
@@ -19889,10 +19885,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>598507</v>
+        <v>598467</v>
       </c>
       <c r="R166" t="n">
-        <v>7330626</v>
+        <v>7330649</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19924,7 +19920,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19934,7 +19930,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19964,16 +19960,16 @@
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382717</t>
+          <t>https://artportalen.se/Sighting/135382722</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>135382722</v>
+        <v>135357130</v>
       </c>
       <c r="B167" t="n">
-        <v>101375</v>
+        <v>102051</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19981,34 +19977,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>224885</v>
+        <v>225188</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Vanliga skogsvinbär</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
+          <t>Ribes spicatum subsp. spicatum</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>598467</v>
+        <v>598613</v>
       </c>
       <c r="R167" t="n">
-        <v>7330649</v>
+        <v>7330353</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20035,22 +20031,22 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20059,6 +20055,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -20080,54 +20077,54 @@
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382722</t>
+          <t>https://artportalen.se/Sighting/135357130</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>135357130</v>
+        <v>135356852</v>
       </c>
       <c r="B168" t="n">
-        <v>102051</v>
+        <v>92442</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>225188</v>
+        <v>6040186</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vanliga skogsvinbär</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ribes spicatum subsp. spicatum</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr"/>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>598613</v>
+        <v>598735</v>
       </c>
       <c r="R168" t="n">
-        <v>7330353</v>
+        <v>7330341</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -20156,7 +20153,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -20166,7 +20163,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20182,12 +20179,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -20197,13 +20194,13 @@
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357130</t>
+          <t>https://artportalen.se/Sighting/135356852</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>135356852</v>
+        <v>135357134</v>
       </c>
       <c r="B169" t="n">
         <v>92442</v>
@@ -20234,17 +20231,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>598735</v>
+        <v>598723</v>
       </c>
       <c r="R169" t="n">
-        <v>7330341</v>
+        <v>7330305</v>
       </c>
       <c r="S169" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -20273,7 +20270,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -20283,7 +20280,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20299,12 +20296,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -20313,123 +20310,6 @@
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135356852</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>135357134</v>
-      </c>
-      <c r="B170" t="n">
-        <v>92442</v>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E170" t="n">
-        <v>6040186</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Kötticka</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="P170" t="inlineStr">
-        <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q170" t="n">
-        <v>598723</v>
-      </c>
-      <c r="R170" t="n">
-        <v>7330305</v>
-      </c>
-      <c r="S170" t="n">
-        <v>10</v>
-      </c>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AD170" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE170" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF170" t="inlineStr"/>
-      <c r="AG170" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT170" t="inlineStr"/>
-      <c r="AW170" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX170" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY170" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-      <c r="AZ170" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135357134</t>
         </is>
@@ -20605,7 +20485,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ169"/>
+  <dimension ref="A1:AZ170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7572,48 +7572,51 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135356210</v>
+        <v>135358275</v>
       </c>
       <c r="B61" t="n">
-        <v>92446</v>
+        <v>87701</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4217</v>
+        <v>3639</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rutspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Cortinarius ionophyllus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>598603</v>
+        <v>598533</v>
       </c>
       <c r="R61" t="n">
-        <v>7330411</v>
+        <v>7330307</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7642,7 +7645,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7652,7 +7655,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7661,18 +7664,19 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7682,13 +7686,13 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356210</t>
+          <t>https://artportalen.se/Sighting/135358275</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135356372</v>
+        <v>135356210</v>
       </c>
       <c r="B62" t="n">
         <v>92446</v>
@@ -7719,17 +7723,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>598544</v>
+        <v>598603</v>
       </c>
       <c r="R62" t="n">
-        <v>7330366</v>
+        <v>7330411</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7758,7 +7762,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7768,7 +7772,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7783,12 +7787,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7798,16 +7802,16 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356372</t>
+          <t>https://artportalen.se/Sighting/135356210</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135353513</v>
+        <v>135356372</v>
       </c>
       <c r="B63" t="n">
-        <v>92013</v>
+        <v>92446</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7815,37 +7819,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>598811</v>
+        <v>598544</v>
       </c>
       <c r="R63" t="n">
-        <v>7330371</v>
+        <v>7330366</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7874,7 +7878,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7884,7 +7888,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7899,12 +7903,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7914,38 +7918,38 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353513</t>
+          <t>https://artportalen.se/Sighting/135356372</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135353495</v>
+        <v>135353513</v>
       </c>
       <c r="B64" t="n">
-        <v>79441</v>
+        <v>92013</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7955,10 +7959,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>598630</v>
+        <v>598811</v>
       </c>
       <c r="R64" t="n">
-        <v>7330381</v>
+        <v>7330371</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7990,7 +7994,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8000,7 +8004,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8030,13 +8034,13 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353495</t>
+          <t>https://artportalen.se/Sighting/135353513</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135353515</v>
+        <v>135353495</v>
       </c>
       <c r="B65" t="n">
         <v>79441</v>
@@ -8071,10 +8075,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>598809</v>
+        <v>598630</v>
       </c>
       <c r="R65" t="n">
-        <v>7330378</v>
+        <v>7330381</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8106,7 +8110,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8116,7 +8120,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8146,13 +8150,13 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353515</t>
+          <t>https://artportalen.se/Sighting/135353495</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135356240</v>
+        <v>135353515</v>
       </c>
       <c r="B66" t="n">
         <v>79441</v>
@@ -8183,14 +8187,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>598519</v>
+        <v>598809</v>
       </c>
       <c r="R66" t="n">
-        <v>7330561</v>
+        <v>7330378</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8222,7 +8226,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8232,7 +8236,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8247,12 +8251,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -8262,13 +8266,13 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356240</t>
+          <t>https://artportalen.se/Sighting/135353515</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135356837</v>
+        <v>135356240</v>
       </c>
       <c r="B67" t="n">
         <v>79441</v>
@@ -8299,17 +8303,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>598555</v>
+        <v>598519</v>
       </c>
       <c r="R67" t="n">
-        <v>7330375</v>
+        <v>7330561</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8338,7 +8342,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8348,7 +8352,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8363,12 +8367,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8378,13 +8382,13 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356837</t>
+          <t>https://artportalen.se/Sighting/135356240</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135382466</v>
+        <v>135356837</v>
       </c>
       <c r="B68" t="n">
         <v>79441</v>
@@ -8415,17 +8419,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>598537</v>
+        <v>598555</v>
       </c>
       <c r="R68" t="n">
-        <v>7330657</v>
+        <v>7330375</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8449,22 +8453,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8479,12 +8483,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8494,13 +8498,13 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382466</t>
+          <t>https://artportalen.se/Sighting/135356837</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135384252</v>
+        <v>135382466</v>
       </c>
       <c r="B69" t="n">
         <v>79441</v>
@@ -8531,17 +8535,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>598474</v>
+        <v>598537</v>
       </c>
       <c r="R69" t="n">
-        <v>7330641</v>
+        <v>7330657</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8570,7 +8574,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8580,7 +8584,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8595,12 +8599,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8610,54 +8614,54 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384252</t>
+          <t>https://artportalen.se/Sighting/135382466</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135353509</v>
+        <v>135384252</v>
       </c>
       <c r="B70" t="n">
-        <v>83428</v>
+        <v>79441</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>598768</v>
+        <v>598474</v>
       </c>
       <c r="R70" t="n">
-        <v>7330331</v>
+        <v>7330641</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8681,22 +8685,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8711,12 +8715,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8726,13 +8730,13 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353509</t>
+          <t>https://artportalen.se/Sighting/135384252</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135356841</v>
+        <v>135353509</v>
       </c>
       <c r="B71" t="n">
         <v>83428</v>
@@ -8763,14 +8767,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>598580</v>
+        <v>598768</v>
       </c>
       <c r="R71" t="n">
-        <v>7330406</v>
+        <v>7330331</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8802,7 +8806,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8812,7 +8816,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8827,12 +8831,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8842,54 +8846,54 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356841</t>
+          <t>https://artportalen.se/Sighting/135353509</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135357126</v>
+        <v>135356841</v>
       </c>
       <c r="B72" t="n">
-        <v>80561</v>
+        <v>83428</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>598552</v>
+        <v>598580</v>
       </c>
       <c r="R72" t="n">
-        <v>7330359</v>
+        <v>7330406</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8918,7 +8922,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8928,7 +8932,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8943,12 +8947,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8958,59 +8962,54 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357126</t>
+          <t>https://artportalen.se/Sighting/135356841</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135353488</v>
+        <v>135357126</v>
       </c>
       <c r="B73" t="n">
-        <v>57980</v>
+        <v>80561</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>598564</v>
+        <v>598552</v>
       </c>
       <c r="R73" t="n">
-        <v>7330345</v>
+        <v>7330359</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9039,7 +9038,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9049,7 +9048,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9064,12 +9063,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -9079,13 +9078,13 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353488</t>
+          <t>https://artportalen.se/Sighting/135357126</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135353503</v>
+        <v>135353488</v>
       </c>
       <c r="B74" t="n">
         <v>57980</v>
@@ -9116,7 +9115,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9125,10 +9124,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>598672</v>
+        <v>598564</v>
       </c>
       <c r="R74" t="n">
-        <v>7330311</v>
+        <v>7330345</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9160,7 +9159,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9170,7 +9169,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9200,13 +9199,13 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353503</t>
+          <t>https://artportalen.se/Sighting/135353488</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135356216</v>
+        <v>135353503</v>
       </c>
       <c r="B75" t="n">
         <v>57980</v>
@@ -9235,19 +9234,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>598747</v>
+        <v>598672</v>
       </c>
       <c r="R75" t="n">
-        <v>7330309</v>
+        <v>7330311</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9276,7 +9280,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9286,12 +9290,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Gamla och nya ringhack</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9306,12 +9305,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -9321,13 +9320,13 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356216</t>
+          <t>https://artportalen.se/Sighting/135353503</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135356376</v>
+        <v>135356216</v>
       </c>
       <c r="B76" t="n">
         <v>57980</v>
@@ -9356,27 +9355,19 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>598614</v>
+        <v>598747</v>
       </c>
       <c r="R76" t="n">
-        <v>7330356</v>
+        <v>7330309</v>
       </c>
       <c r="S76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9405,7 +9396,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9415,19 +9406,19 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Gamla och nya ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
@@ -9435,12 +9426,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -9450,13 +9441,13 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356376</t>
+          <t>https://artportalen.se/Sighting/135356216</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135356380</v>
+        <v>135356376</v>
       </c>
       <c r="B77" t="n">
         <v>57980</v>
@@ -9499,13 +9490,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>598877</v>
+        <v>598614</v>
       </c>
       <c r="R77" t="n">
-        <v>7330349</v>
+        <v>7330356</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9534,7 +9525,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9544,19 +9535,19 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG77" t="b">
         <v>0</v>
@@ -9569,7 +9560,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9579,13 +9570,13 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356380</t>
+          <t>https://artportalen.se/Sighting/135356376</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135357127</v>
+        <v>135356380</v>
       </c>
       <c r="B78" t="n">
         <v>57980</v>
@@ -9614,19 +9605,27 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>598569</v>
+        <v>598877</v>
       </c>
       <c r="R78" t="n">
-        <v>7330352</v>
+        <v>7330349</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9655,7 +9654,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9665,12 +9664,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9685,12 +9684,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9700,13 +9699,13 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357127</t>
+          <t>https://artportalen.se/Sighting/135356380</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135358283</v>
+        <v>135357127</v>
       </c>
       <c r="B79" t="n">
         <v>57980</v>
@@ -9737,17 +9736,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>598609</v>
+        <v>598569</v>
       </c>
       <c r="R79" t="n">
-        <v>7330298</v>
+        <v>7330352</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9776,7 +9775,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9786,7 +9785,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -9806,12 +9805,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9821,13 +9820,13 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358283</t>
+          <t>https://artportalen.se/Sighting/135357127</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135382716</v>
+        <v>135358283</v>
       </c>
       <c r="B80" t="n">
         <v>57980</v>
@@ -9856,27 +9855,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>598482</v>
+        <v>598609</v>
       </c>
       <c r="R80" t="n">
-        <v>7330489</v>
+        <v>7330298</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9900,27 +9891,27 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9935,12 +9926,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9950,13 +9941,13 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382716</t>
+          <t>https://artportalen.se/Sighting/135358283</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135382779</v>
+        <v>135382716</v>
       </c>
       <c r="B81" t="n">
         <v>57980</v>
@@ -9989,7 +9980,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -9999,10 +9990,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>598462</v>
+        <v>598482</v>
       </c>
       <c r="R81" t="n">
-        <v>7330447</v>
+        <v>7330489</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10034,7 +10025,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10044,12 +10035,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10079,13 +10070,13 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382779</t>
+          <t>https://artportalen.se/Sighting/135382716</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135384126</v>
+        <v>135382779</v>
       </c>
       <c r="B82" t="n">
         <v>57980</v>
@@ -10128,10 +10119,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>598485</v>
+        <v>598462</v>
       </c>
       <c r="R82" t="n">
-        <v>7330673</v>
+        <v>7330447</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10163,7 +10154,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10173,19 +10164,19 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="b">
         <v>0</v>
@@ -10193,12 +10184,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -10208,16 +10199,16 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384126</t>
+          <t>https://artportalen.se/Sighting/135382779</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135357215</v>
+        <v>135384126</v>
       </c>
       <c r="B83" t="n">
-        <v>58141</v>
+        <v>57980</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10225,21 +10216,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10247,20 +10238,20 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>598501</v>
+        <v>598485</v>
       </c>
       <c r="R83" t="n">
-        <v>7330475</v>
+        <v>7330673</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10287,34 +10278,34 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG83" t="b">
         <v>0</v>
@@ -10322,12 +10313,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -10337,13 +10328,13 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357215</t>
+          <t>https://artportalen.se/Sighting/135384126</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135382711</v>
+        <v>135357215</v>
       </c>
       <c r="B84" t="n">
         <v>58141</v>
@@ -10382,14 +10373,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>598464</v>
+        <v>598501</v>
       </c>
       <c r="R84" t="n">
-        <v>7330416</v>
+        <v>7330475</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10416,22 +10407,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10461,13 +10457,13 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382711</t>
+          <t>https://artportalen.se/Sighting/135357215</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135385939</v>
+        <v>135382711</v>
       </c>
       <c r="B85" t="n">
         <v>58141</v>
@@ -10496,16 +10492,24 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>598491</v>
+        <v>598464</v>
       </c>
       <c r="R85" t="n">
-        <v>7330361</v>
+        <v>7330416</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10537,7 +10541,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10547,7 +10551,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10562,12 +10566,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -10577,54 +10581,54 @@
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135385939</t>
+          <t>https://artportalen.se/Sighting/135382711</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135382469</v>
+        <v>135385939</v>
       </c>
       <c r="B86" t="n">
-        <v>99193</v>
+        <v>58141</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>598453</v>
+        <v>598491</v>
       </c>
       <c r="R86" t="n">
-        <v>7330444</v>
+        <v>7330361</v>
       </c>
       <c r="S86" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10653,7 +10657,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10663,7 +10667,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10678,12 +10682,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10693,13 +10697,13 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382469</t>
+          <t>https://artportalen.se/Sighting/135385939</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135384124</v>
+        <v>135382469</v>
       </c>
       <c r="B87" t="n">
         <v>99193</v>
@@ -10730,17 +10734,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>598499</v>
+        <v>598453</v>
       </c>
       <c r="R87" t="n">
-        <v>7330637</v>
+        <v>7330444</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10769,7 +10773,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10779,7 +10783,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10794,12 +10798,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10809,13 +10813,13 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384124</t>
+          <t>https://artportalen.se/Sighting/135382469</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135384162</v>
+        <v>135384124</v>
       </c>
       <c r="B88" t="n">
         <v>99193</v>
@@ -10850,10 +10854,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>598449</v>
+        <v>598499</v>
       </c>
       <c r="R88" t="n">
-        <v>7330355</v>
+        <v>7330637</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10885,7 +10889,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10895,7 +10899,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10925,16 +10929,16 @@
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384162</t>
+          <t>https://artportalen.se/Sighting/135384124</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>94770073</v>
+        <v>135384162</v>
       </c>
       <c r="B89" t="n">
-        <v>99120</v>
+        <v>99193</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10942,43 +10946,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219811</v>
+        <v>219790</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Laisan, Arjeplog, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>598453</v>
+        <v>598449</v>
       </c>
       <c r="R89" t="n">
-        <v>7330315</v>
+        <v>7330355</v>
       </c>
       <c r="S89" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11002,12 +11000,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11022,27 +11030,31 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Thomas Strid, Tiina Laantee</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94770073</t>
+          <t>https://artportalen.se/Sighting/135384162</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135356843</v>
+        <v>94770073</v>
       </c>
       <c r="B90" t="n">
-        <v>99180</v>
+        <v>99120</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11050,37 +11062,43 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Laisan, Arjeplog, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>598607</v>
+        <v>598453</v>
       </c>
       <c r="R90" t="n">
-        <v>7330382</v>
+        <v>7330315</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11104,22 +11122,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11134,31 +11142,27 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Thomas Strid, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356843</t>
+          <t>https://artportalen.se/Sighting/94770073</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135353481</v>
+        <v>135356843</v>
       </c>
       <c r="B91" t="n">
-        <v>110014</v>
+        <v>99180</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11166,34 +11170,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221184</v>
+        <v>220093</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>598529</v>
+        <v>598607</v>
       </c>
       <c r="R91" t="n">
-        <v>7330341</v>
+        <v>7330382</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -11225,7 +11229,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11235,7 +11239,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11250,12 +11254,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11265,13 +11269,13 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353481</t>
+          <t>https://artportalen.se/Sighting/135356843</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135353512</v>
+        <v>135353481</v>
       </c>
       <c r="B92" t="n">
         <v>110014</v>
@@ -11306,10 +11310,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>598793</v>
+        <v>598529</v>
       </c>
       <c r="R92" t="n">
-        <v>7330350</v>
+        <v>7330341</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -11341,7 +11345,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11351,7 +11355,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11381,13 +11385,13 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353512</t>
+          <t>https://artportalen.se/Sighting/135353481</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135356205</v>
+        <v>135353512</v>
       </c>
       <c r="B93" t="n">
         <v>110014</v>
@@ -11418,14 +11422,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>598518</v>
+        <v>598793</v>
       </c>
       <c r="R93" t="n">
-        <v>7330341</v>
+        <v>7330350</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11457,7 +11461,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11467,7 +11471,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11482,12 +11486,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -11497,13 +11501,13 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356205</t>
+          <t>https://artportalen.se/Sighting/135353512</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135356241</v>
+        <v>135356205</v>
       </c>
       <c r="B94" t="n">
         <v>110014</v>
@@ -11538,10 +11542,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>598490</v>
+        <v>598518</v>
       </c>
       <c r="R94" t="n">
-        <v>7330565</v>
+        <v>7330341</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11573,7 +11577,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11583,7 +11587,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11613,13 +11617,13 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356241</t>
+          <t>https://artportalen.se/Sighting/135356205</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135357137</v>
+        <v>135356241</v>
       </c>
       <c r="B95" t="n">
         <v>110014</v>
@@ -11650,17 +11654,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>598751</v>
+        <v>598490</v>
       </c>
       <c r="R95" t="n">
-        <v>7330316</v>
+        <v>7330565</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11689,7 +11693,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11699,7 +11703,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11714,12 +11718,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11729,13 +11733,13 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357137</t>
+          <t>https://artportalen.se/Sighting/135356241</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135357141</v>
+        <v>135357137</v>
       </c>
       <c r="B96" t="n">
         <v>110014</v>
@@ -11770,10 +11774,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>598770</v>
+        <v>598751</v>
       </c>
       <c r="R96" t="n">
-        <v>7330338</v>
+        <v>7330316</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11805,7 +11809,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11815,7 +11819,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11845,13 +11849,13 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357141</t>
+          <t>https://artportalen.se/Sighting/135357137</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135357201</v>
+        <v>135357141</v>
       </c>
       <c r="B97" t="n">
         <v>110014</v>
@@ -11886,10 +11890,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>598553</v>
+        <v>598770</v>
       </c>
       <c r="R97" t="n">
-        <v>7330578</v>
+        <v>7330338</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11921,7 +11925,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11931,7 +11935,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11961,13 +11965,13 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357201</t>
+          <t>https://artportalen.se/Sighting/135357141</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135357211</v>
+        <v>135357201</v>
       </c>
       <c r="B98" t="n">
         <v>110014</v>
@@ -12002,10 +12006,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>598501</v>
+        <v>598553</v>
       </c>
       <c r="R98" t="n">
-        <v>7330515</v>
+        <v>7330578</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12037,7 +12041,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12047,7 +12051,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12077,13 +12081,13 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357211</t>
+          <t>https://artportalen.se/Sighting/135357201</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135357212</v>
+        <v>135357211</v>
       </c>
       <c r="B99" t="n">
         <v>110014</v>
@@ -12118,10 +12122,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>598498</v>
+        <v>598501</v>
       </c>
       <c r="R99" t="n">
-        <v>7330492</v>
+        <v>7330515</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12153,7 +12157,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12163,7 +12167,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12193,13 +12197,13 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357212</t>
+          <t>https://artportalen.se/Sighting/135357211</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135358269</v>
+        <v>135357212</v>
       </c>
       <c r="B100" t="n">
         <v>110014</v>
@@ -12230,17 +12234,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>598578</v>
+        <v>598498</v>
       </c>
       <c r="R100" t="n">
-        <v>7330329</v>
+        <v>7330492</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12269,7 +12273,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12279,7 +12283,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12294,12 +12298,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12309,13 +12313,13 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358269</t>
+          <t>https://artportalen.se/Sighting/135357212</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135358276</v>
+        <v>135358269</v>
       </c>
       <c r="B101" t="n">
         <v>110014</v>
@@ -12350,10 +12354,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>598542</v>
+        <v>598578</v>
       </c>
       <c r="R101" t="n">
-        <v>7330305</v>
+        <v>7330329</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12385,7 +12389,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12395,7 +12399,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12425,13 +12429,13 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358276</t>
+          <t>https://artportalen.se/Sighting/135358269</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135358292</v>
+        <v>135358276</v>
       </c>
       <c r="B102" t="n">
         <v>110014</v>
@@ -12466,10 +12470,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>598827</v>
+        <v>598542</v>
       </c>
       <c r="R102" t="n">
-        <v>7330278</v>
+        <v>7330305</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12501,7 +12505,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12511,7 +12515,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12541,13 +12545,13 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358292</t>
+          <t>https://artportalen.se/Sighting/135358276</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135358342</v>
+        <v>135358292</v>
       </c>
       <c r="B103" t="n">
         <v>110014</v>
@@ -12582,10 +12586,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>598546</v>
+        <v>598827</v>
       </c>
       <c r="R103" t="n">
-        <v>7330653</v>
+        <v>7330278</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12617,7 +12621,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12627,7 +12631,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12657,13 +12661,13 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358342</t>
+          <t>https://artportalen.se/Sighting/135358292</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135382720</v>
+        <v>135358342</v>
       </c>
       <c r="B104" t="n">
         <v>110014</v>
@@ -12694,17 +12698,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>598507</v>
+        <v>598546</v>
       </c>
       <c r="R104" t="n">
-        <v>7330626</v>
+        <v>7330653</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12728,22 +12732,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12758,12 +12762,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12773,13 +12777,13 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382720</t>
+          <t>https://artportalen.se/Sighting/135358342</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135382723</v>
+        <v>135382720</v>
       </c>
       <c r="B105" t="n">
         <v>110014</v>
@@ -12814,10 +12818,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>598467</v>
+        <v>598507</v>
       </c>
       <c r="R105" t="n">
-        <v>7330649</v>
+        <v>7330626</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12849,7 +12853,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12859,7 +12863,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12889,16 +12893,16 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382723</t>
+          <t>https://artportalen.se/Sighting/135382720</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135353491</v>
+        <v>135382723</v>
       </c>
       <c r="B106" t="n">
-        <v>106398</v>
+        <v>110014</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12906,16 +12910,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221725</v>
+        <v>221184</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -12926,17 +12930,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>598592</v>
+        <v>598467</v>
       </c>
       <c r="R106" t="n">
-        <v>7330348</v>
+        <v>7330649</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12960,22 +12964,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12990,12 +12994,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -13005,13 +13009,13 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353491</t>
+          <t>https://artportalen.se/Sighting/135382723</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135356209</v>
+        <v>135353491</v>
       </c>
       <c r="B107" t="n">
         <v>106398</v>
@@ -13042,14 +13046,14 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>598597</v>
+        <v>598592</v>
       </c>
       <c r="R107" t="n">
-        <v>7330383</v>
+        <v>7330348</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -13081,7 +13085,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13091,7 +13095,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13106,12 +13110,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -13121,13 +13125,13 @@
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356209</t>
+          <t>https://artportalen.se/Sighting/135353491</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135356218</v>
+        <v>135356209</v>
       </c>
       <c r="B108" t="n">
         <v>106398</v>
@@ -13162,10 +13166,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>598785</v>
+        <v>598597</v>
       </c>
       <c r="R108" t="n">
-        <v>7330366</v>
+        <v>7330383</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -13197,7 +13201,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13207,7 +13211,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13237,13 +13241,13 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356218</t>
+          <t>https://artportalen.se/Sighting/135356209</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135356839</v>
+        <v>135356218</v>
       </c>
       <c r="B109" t="n">
         <v>106398</v>
@@ -13274,17 +13278,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>598557</v>
+        <v>598785</v>
       </c>
       <c r="R109" t="n">
-        <v>7330411</v>
+        <v>7330366</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13313,7 +13317,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13323,7 +13327,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13338,12 +13342,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -13353,13 +13357,13 @@
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356839</t>
+          <t>https://artportalen.se/Sighting/135356218</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135356886</v>
+        <v>135356839</v>
       </c>
       <c r="B110" t="n">
         <v>106398</v>
@@ -13394,13 +13398,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>598518</v>
+        <v>598557</v>
       </c>
       <c r="R110" t="n">
-        <v>7330476</v>
+        <v>7330411</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13429,7 +13433,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13439,7 +13443,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13469,13 +13473,13 @@
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356886</t>
+          <t>https://artportalen.se/Sighting/135356839</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135358270</v>
+        <v>135356886</v>
       </c>
       <c r="B111" t="n">
         <v>106398</v>
@@ -13506,17 +13510,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>598568</v>
+        <v>598518</v>
       </c>
       <c r="R111" t="n">
-        <v>7330339</v>
+        <v>7330476</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13545,7 +13549,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13555,7 +13559,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13570,12 +13574,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -13585,13 +13589,13 @@
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358270</t>
+          <t>https://artportalen.se/Sighting/135356886</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135358287</v>
+        <v>135358270</v>
       </c>
       <c r="B112" t="n">
         <v>106398</v>
@@ -13626,10 +13630,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>598754</v>
+        <v>598568</v>
       </c>
       <c r="R112" t="n">
-        <v>7330326</v>
+        <v>7330339</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13661,7 +13665,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13671,7 +13675,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13701,16 +13705,16 @@
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358287</t>
+          <t>https://artportalen.se/Sighting/135358270</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135356206</v>
+        <v>135358287</v>
       </c>
       <c r="B113" t="n">
-        <v>98138</v>
+        <v>106398</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13718,37 +13722,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>598569</v>
+        <v>598754</v>
       </c>
       <c r="R113" t="n">
-        <v>7330354</v>
+        <v>7330326</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13777,7 +13781,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13787,7 +13791,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13802,12 +13806,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13817,13 +13821,13 @@
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356206</t>
+          <t>https://artportalen.se/Sighting/135358287</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135356243</v>
+        <v>135356206</v>
       </c>
       <c r="B114" t="n">
         <v>98138</v>
@@ -13858,10 +13862,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>598482</v>
+        <v>598569</v>
       </c>
       <c r="R114" t="n">
-        <v>7330539</v>
+        <v>7330354</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13893,7 +13897,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13903,7 +13907,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13933,13 +13937,13 @@
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356243</t>
+          <t>https://artportalen.se/Sighting/135356206</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135356845</v>
+        <v>135356243</v>
       </c>
       <c r="B115" t="n">
         <v>98138</v>
@@ -13970,17 +13974,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>598624</v>
+        <v>598482</v>
       </c>
       <c r="R115" t="n">
-        <v>7330372</v>
+        <v>7330539</v>
       </c>
       <c r="S115" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14009,7 +14013,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14019,7 +14023,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14034,12 +14038,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -14049,13 +14053,13 @@
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356845</t>
+          <t>https://artportalen.se/Sighting/135356243</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135356884</v>
+        <v>135356845</v>
       </c>
       <c r="B116" t="n">
         <v>98138</v>
@@ -14090,13 +14094,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>598495</v>
+        <v>598624</v>
       </c>
       <c r="R116" t="n">
-        <v>7330628</v>
+        <v>7330372</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14125,7 +14129,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14135,7 +14139,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14165,13 +14169,13 @@
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356884</t>
+          <t>https://artportalen.se/Sighting/135356845</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135358281</v>
+        <v>135356884</v>
       </c>
       <c r="B117" t="n">
         <v>98138</v>
@@ -14202,14 +14206,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>598605</v>
+        <v>598495</v>
       </c>
       <c r="R117" t="n">
-        <v>7330324</v>
+        <v>7330628</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14241,7 +14245,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14251,7 +14255,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14266,12 +14270,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -14281,13 +14285,13 @@
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358281</t>
+          <t>https://artportalen.se/Sighting/135356884</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135382031</v>
+        <v>135358281</v>
       </c>
       <c r="B118" t="n">
         <v>98138</v>
@@ -14318,17 +14322,17 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>598459</v>
+        <v>598605</v>
       </c>
       <c r="R118" t="n">
-        <v>7330572</v>
+        <v>7330324</v>
       </c>
       <c r="S118" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -14352,22 +14356,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14382,12 +14386,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -14397,13 +14401,13 @@
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382031</t>
+          <t>https://artportalen.se/Sighting/135358281</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135382032</v>
+        <v>135382031</v>
       </c>
       <c r="B119" t="n">
         <v>98138</v>
@@ -14438,13 +14442,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>598472</v>
+        <v>598459</v>
       </c>
       <c r="R119" t="n">
-        <v>7330674</v>
+        <v>7330572</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14513,13 +14517,13 @@
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382032</t>
+          <t>https://artportalen.se/Sighting/135382031</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135384245</v>
+        <v>135382032</v>
       </c>
       <c r="B120" t="n">
         <v>98138</v>
@@ -14550,14 +14554,14 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>598522</v>
+        <v>598472</v>
       </c>
       <c r="R120" t="n">
-        <v>7330575</v>
+        <v>7330674</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14589,7 +14593,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14599,7 +14603,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14614,12 +14618,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -14629,13 +14633,13 @@
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384245</t>
+          <t>https://artportalen.se/Sighting/135382032</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135384249</v>
+        <v>135384245</v>
       </c>
       <c r="B121" t="n">
         <v>98138</v>
@@ -14670,13 +14674,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>598492</v>
+        <v>598522</v>
       </c>
       <c r="R121" t="n">
-        <v>7330652</v>
+        <v>7330575</v>
       </c>
       <c r="S121" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14705,7 +14709,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14715,7 +14719,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14745,16 +14749,16 @@
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384249</t>
+          <t>https://artportalen.se/Sighting/135384245</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135353486</v>
+        <v>135384249</v>
       </c>
       <c r="B122" t="n">
-        <v>99298</v>
+        <v>98138</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14762,37 +14766,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>598555</v>
+        <v>598492</v>
       </c>
       <c r="R122" t="n">
-        <v>7330349</v>
+        <v>7330652</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14816,22 +14820,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14846,12 +14850,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -14861,13 +14865,13 @@
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353486</t>
+          <t>https://artportalen.se/Sighting/135384249</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135353494</v>
+        <v>135353486</v>
       </c>
       <c r="B123" t="n">
         <v>99298</v>
@@ -14902,10 +14906,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>598634</v>
+        <v>598555</v>
       </c>
       <c r="R123" t="n">
-        <v>7330375</v>
+        <v>7330349</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14937,7 +14941,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14947,7 +14951,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14977,13 +14981,13 @@
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353494</t>
+          <t>https://artportalen.se/Sighting/135353486</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135353497</v>
+        <v>135353494</v>
       </c>
       <c r="B124" t="n">
         <v>99298</v>
@@ -15018,10 +15022,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>598665</v>
+        <v>598634</v>
       </c>
       <c r="R124" t="n">
-        <v>7330360</v>
+        <v>7330375</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -15053,7 +15057,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15063,7 +15067,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15093,13 +15097,13 @@
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353497</t>
+          <t>https://artportalen.se/Sighting/135353494</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135356211</v>
+        <v>135353497</v>
       </c>
       <c r="B125" t="n">
         <v>99298</v>
@@ -15130,14 +15134,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>598644</v>
+        <v>598665</v>
       </c>
       <c r="R125" t="n">
-        <v>7330364</v>
+        <v>7330360</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15169,7 +15173,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15179,7 +15183,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15194,12 +15198,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -15209,13 +15213,13 @@
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356211</t>
+          <t>https://artportalen.se/Sighting/135353497</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135356213</v>
+        <v>135356211</v>
       </c>
       <c r="B126" t="n">
         <v>99298</v>
@@ -15250,13 +15254,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>598651</v>
+        <v>598644</v>
       </c>
       <c r="R126" t="n">
-        <v>7330373</v>
+        <v>7330364</v>
       </c>
       <c r="S126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15285,7 +15289,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15295,7 +15299,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15325,13 +15329,13 @@
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356213</t>
+          <t>https://artportalen.se/Sighting/135356211</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135356844</v>
+        <v>135356213</v>
       </c>
       <c r="B127" t="n">
         <v>99298</v>
@@ -15362,17 +15366,17 @@
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>598607</v>
+        <v>598651</v>
       </c>
       <c r="R127" t="n">
-        <v>7330382</v>
+        <v>7330373</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15401,7 +15405,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15411,7 +15415,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15426,12 +15430,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -15441,13 +15445,13 @@
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356844</t>
+          <t>https://artportalen.se/Sighting/135356213</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135356846</v>
+        <v>135356844</v>
       </c>
       <c r="B128" t="n">
         <v>99298</v>
@@ -15482,10 +15486,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>598653</v>
+        <v>598607</v>
       </c>
       <c r="R128" t="n">
-        <v>7330343</v>
+        <v>7330382</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15517,7 +15521,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15527,7 +15531,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15557,13 +15561,13 @@
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356846</t>
+          <t>https://artportalen.se/Sighting/135356844</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>135356856</v>
+        <v>135356846</v>
       </c>
       <c r="B129" t="n">
         <v>99298</v>
@@ -15598,13 +15602,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>598841</v>
+        <v>598653</v>
       </c>
       <c r="R129" t="n">
-        <v>7330355</v>
+        <v>7330343</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15633,7 +15637,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15643,7 +15647,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15673,13 +15677,13 @@
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356856</t>
+          <t>https://artportalen.se/Sighting/135356846</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>135362163</v>
+        <v>135356856</v>
       </c>
       <c r="B130" t="n">
         <v>99298</v>
@@ -15710,17 +15714,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>598808</v>
+        <v>598841</v>
       </c>
       <c r="R130" t="n">
-        <v>7330337</v>
+        <v>7330355</v>
       </c>
       <c r="S130" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15747,9 +15751,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15764,12 +15778,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -15779,13 +15793,13 @@
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135362163</t>
+          <t>https://artportalen.se/Sighting/135356856</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>135382721</v>
+        <v>135362163</v>
       </c>
       <c r="B131" t="n">
         <v>99298</v>
@@ -15816,17 +15830,17 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>598467</v>
+        <v>598808</v>
       </c>
       <c r="R131" t="n">
-        <v>7330649</v>
+        <v>7330337</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15850,22 +15864,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>10:43</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15880,12 +15884,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -15895,13 +15899,13 @@
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382721</t>
+          <t>https://artportalen.se/Sighting/135362163</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>135384251</v>
+        <v>135382721</v>
       </c>
       <c r="B132" t="n">
         <v>99298</v>
@@ -15932,14 +15936,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>598482</v>
+        <v>598467</v>
       </c>
       <c r="R132" t="n">
-        <v>7330639</v>
+        <v>7330649</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15971,7 +15975,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15981,7 +15985,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15996,12 +16000,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -16011,16 +16015,16 @@
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384251</t>
+          <t>https://artportalen.se/Sighting/135382721</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135353490</v>
+        <v>135384251</v>
       </c>
       <c r="B133" t="n">
-        <v>104795</v>
+        <v>99298</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16028,37 +16032,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>222412</v>
+        <v>221952</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>598591</v>
+        <v>598482</v>
       </c>
       <c r="R133" t="n">
-        <v>7330353</v>
+        <v>7330639</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -16082,22 +16086,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16112,12 +16116,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -16127,13 +16131,13 @@
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353490</t>
+          <t>https://artportalen.se/Sighting/135384251</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>135357136</v>
+        <v>135353490</v>
       </c>
       <c r="B134" t="n">
         <v>104795</v>
@@ -16164,17 +16168,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>598751</v>
+        <v>598591</v>
       </c>
       <c r="R134" t="n">
-        <v>7330316</v>
+        <v>7330353</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16203,7 +16207,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16213,7 +16217,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16228,12 +16232,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -16243,13 +16247,13 @@
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357136</t>
+          <t>https://artportalen.se/Sighting/135353490</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>135362160</v>
+        <v>135357136</v>
       </c>
       <c r="B135" t="n">
         <v>104795</v>
@@ -16284,13 +16288,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>598552</v>
+        <v>598751</v>
       </c>
       <c r="R135" t="n">
-        <v>7330368</v>
+        <v>7330316</v>
       </c>
       <c r="S135" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16317,9 +16321,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16334,12 +16348,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -16349,16 +16363,16 @@
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135362160</t>
+          <t>https://artportalen.se/Sighting/135357136</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135358271</v>
+        <v>135362160</v>
       </c>
       <c r="B136" t="n">
-        <v>99286</v>
+        <v>104795</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16366,41 +16380,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>222495</v>
+        <v>222412</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Myggblomster</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hammarbya paludosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Kuntze</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>598585</v>
+        <v>598552</v>
       </c>
       <c r="R136" t="n">
-        <v>7330354</v>
+        <v>7330368</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16427,40 +16437,29 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -16470,13 +16469,13 @@
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358271</t>
+          <t>https://artportalen.se/Sighting/135362160</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>135358274</v>
+        <v>135358271</v>
       </c>
       <c r="B137" t="n">
         <v>99286</v>
@@ -16515,13 +16514,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>598543</v>
+        <v>598585</v>
       </c>
       <c r="R137" t="n">
-        <v>7330322</v>
+        <v>7330354</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16550,7 +16549,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16560,7 +16559,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16591,13 +16590,13 @@
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358274</t>
+          <t>https://artportalen.se/Sighting/135358271</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>135358278</v>
+        <v>135358274</v>
       </c>
       <c r="B138" t="n">
         <v>99286</v>
@@ -16636,13 +16635,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>598566</v>
+        <v>598543</v>
       </c>
       <c r="R138" t="n">
-        <v>7330282</v>
+        <v>7330322</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16671,7 +16670,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -16681,7 +16680,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16712,16 +16711,16 @@
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358278</t>
+          <t>https://artportalen.se/Sighting/135358274</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>135356838</v>
+        <v>135358278</v>
       </c>
       <c r="B139" t="n">
-        <v>98292</v>
+        <v>99286</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16729,37 +16728,41 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>222741</v>
+        <v>222495</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Myggblomster</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hammarbya paludosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Kuntze</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>598555</v>
+        <v>598566</v>
       </c>
       <c r="R139" t="n">
-        <v>7330375</v>
+        <v>7330282</v>
       </c>
       <c r="S139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16788,7 +16791,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16798,7 +16801,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16807,18 +16810,19 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -16828,13 +16832,13 @@
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356838</t>
+          <t>https://artportalen.se/Sighting/135358278</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>135357146</v>
+        <v>135356838</v>
       </c>
       <c r="B140" t="n">
         <v>98292</v>
@@ -16865,17 +16869,17 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>598911</v>
+        <v>598555</v>
       </c>
       <c r="R140" t="n">
-        <v>7330350</v>
+        <v>7330375</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16904,7 +16908,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16914,7 +16918,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16929,12 +16933,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -16944,13 +16948,13 @@
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357146</t>
+          <t>https://artportalen.se/Sighting/135356838</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>135357209</v>
+        <v>135357146</v>
       </c>
       <c r="B141" t="n">
         <v>98292</v>
@@ -16985,10 +16989,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>598519</v>
+        <v>598911</v>
       </c>
       <c r="R141" t="n">
-        <v>7330570</v>
+        <v>7330350</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -17020,7 +17024,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17030,7 +17034,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17060,16 +17064,16 @@
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357209</t>
+          <t>https://artportalen.se/Sighting/135357146</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>135357123</v>
+        <v>135357209</v>
       </c>
       <c r="B142" t="n">
-        <v>102956</v>
+        <v>98292</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17077,21 +17081,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>223037</v>
+        <v>222741</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -17101,10 +17105,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>598552</v>
+        <v>598519</v>
       </c>
       <c r="R142" t="n">
-        <v>7330359</v>
+        <v>7330570</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -17136,7 +17140,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17146,7 +17150,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17176,13 +17180,13 @@
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357123</t>
+          <t>https://artportalen.se/Sighting/135357209</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>135357202</v>
+        <v>135357123</v>
       </c>
       <c r="B143" t="n">
         <v>102956</v>
@@ -17217,10 +17221,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>598553</v>
+        <v>598552</v>
       </c>
       <c r="R143" t="n">
-        <v>7330578</v>
+        <v>7330359</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17252,7 +17256,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17262,7 +17266,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17292,13 +17296,13 @@
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357202</t>
+          <t>https://artportalen.se/Sighting/135357123</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>135382713</v>
+        <v>135357202</v>
       </c>
       <c r="B144" t="n">
         <v>102956</v>
@@ -17329,14 +17333,14 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>598464</v>
+        <v>598553</v>
       </c>
       <c r="R144" t="n">
-        <v>7330416</v>
+        <v>7330578</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17363,22 +17367,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17408,13 +17412,13 @@
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382713</t>
+          <t>https://artportalen.se/Sighting/135357202</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>135382724</v>
+        <v>135382713</v>
       </c>
       <c r="B145" t="n">
         <v>102956</v>
@@ -17449,10 +17453,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>598467</v>
+        <v>598464</v>
       </c>
       <c r="R145" t="n">
-        <v>7330649</v>
+        <v>7330416</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17484,7 +17488,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -17494,7 +17498,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17524,16 +17528,16 @@
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382724</t>
+          <t>https://artportalen.se/Sighting/135382713</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>135357122</v>
+        <v>135382724</v>
       </c>
       <c r="B146" t="n">
-        <v>98327</v>
+        <v>102956</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17541,34 +17545,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>223358</v>
+        <v>223037</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>598552</v>
+        <v>598467</v>
       </c>
       <c r="R146" t="n">
-        <v>7330359</v>
+        <v>7330649</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17595,22 +17599,22 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17640,13 +17644,13 @@
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357122</t>
+          <t>https://artportalen.se/Sighting/135382724</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>135357145</v>
+        <v>135357122</v>
       </c>
       <c r="B147" t="n">
         <v>98327</v>
@@ -17681,10 +17685,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>598911</v>
+        <v>598552</v>
       </c>
       <c r="R147" t="n">
-        <v>7330350</v>
+        <v>7330359</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17716,7 +17720,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17726,7 +17730,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17756,13 +17760,13 @@
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357145</t>
+          <t>https://artportalen.se/Sighting/135357122</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>135358277</v>
+        <v>135357145</v>
       </c>
       <c r="B148" t="n">
         <v>98327</v>
@@ -17793,17 +17797,17 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>598551</v>
+        <v>598911</v>
       </c>
       <c r="R148" t="n">
-        <v>7330296</v>
+        <v>7330350</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17832,7 +17836,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17842,7 +17846,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17857,12 +17861,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -17872,13 +17876,13 @@
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358277</t>
+          <t>https://artportalen.se/Sighting/135357145</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>135382718</v>
+        <v>135358277</v>
       </c>
       <c r="B149" t="n">
         <v>98327</v>
@@ -17909,17 +17913,17 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>598507</v>
+        <v>598551</v>
       </c>
       <c r="R149" t="n">
-        <v>7330626</v>
+        <v>7330296</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17943,22 +17947,22 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17973,12 +17977,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -17988,16 +17992,16 @@
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382718</t>
+          <t>https://artportalen.se/Sighting/135358277</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>135353482</v>
+        <v>135382718</v>
       </c>
       <c r="B150" t="n">
-        <v>101375</v>
+        <v>98327</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18005,37 +18009,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>598530</v>
+        <v>598507</v>
       </c>
       <c r="R150" t="n">
-        <v>7330340</v>
+        <v>7330626</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -18059,22 +18063,22 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18089,12 +18093,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -18104,13 +18108,13 @@
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135353482</t>
+          <t>https://artportalen.se/Sighting/135382718</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>135357117</v>
+        <v>135353482</v>
       </c>
       <c r="B151" t="n">
         <v>101375</v>
@@ -18141,17 +18145,17 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>598525</v>
+        <v>598530</v>
       </c>
       <c r="R151" t="n">
-        <v>7330346</v>
+        <v>7330340</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -18205,12 +18209,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -18220,13 +18224,13 @@
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357117</t>
+          <t>https://artportalen.se/Sighting/135353482</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>135357120</v>
+        <v>135357117</v>
       </c>
       <c r="B152" t="n">
         <v>101375</v>
@@ -18261,10 +18265,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>598552</v>
+        <v>598525</v>
       </c>
       <c r="R152" t="n">
-        <v>7330359</v>
+        <v>7330346</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18296,7 +18300,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18306,7 +18310,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18336,13 +18340,13 @@
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357120</t>
+          <t>https://artportalen.se/Sighting/135357117</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>135357138</v>
+        <v>135357120</v>
       </c>
       <c r="B153" t="n">
         <v>101375</v>
@@ -18377,10 +18381,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>598751</v>
+        <v>598552</v>
       </c>
       <c r="R153" t="n">
-        <v>7330316</v>
+        <v>7330359</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18412,7 +18416,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18422,7 +18426,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18452,13 +18456,13 @@
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357138</t>
+          <t>https://artportalen.se/Sighting/135357120</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>135357140</v>
+        <v>135357138</v>
       </c>
       <c r="B154" t="n">
         <v>101375</v>
@@ -18493,10 +18497,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>598770</v>
+        <v>598751</v>
       </c>
       <c r="R154" t="n">
-        <v>7330338</v>
+        <v>7330316</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18528,7 +18532,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -18538,7 +18542,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18568,13 +18572,13 @@
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357140</t>
+          <t>https://artportalen.se/Sighting/135357138</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>135357147</v>
+        <v>135357140</v>
       </c>
       <c r="B155" t="n">
         <v>101375</v>
@@ -18609,10 +18613,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>598911</v>
+        <v>598770</v>
       </c>
       <c r="R155" t="n">
-        <v>7330350</v>
+        <v>7330338</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18644,7 +18648,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18654,7 +18658,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18684,13 +18688,13 @@
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357147</t>
+          <t>https://artportalen.se/Sighting/135357140</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>135357205</v>
+        <v>135357147</v>
       </c>
       <c r="B156" t="n">
         <v>101375</v>
@@ -18725,10 +18729,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>598553</v>
+        <v>598911</v>
       </c>
       <c r="R156" t="n">
-        <v>7330578</v>
+        <v>7330350</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18760,7 +18764,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18770,7 +18774,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18800,13 +18804,13 @@
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357205</t>
+          <t>https://artportalen.se/Sighting/135357147</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>135357206</v>
+        <v>135357205</v>
       </c>
       <c r="B157" t="n">
         <v>101375</v>
@@ -18841,10 +18845,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>598521</v>
+        <v>598553</v>
       </c>
       <c r="R157" t="n">
-        <v>7330581</v>
+        <v>7330578</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18876,7 +18880,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18886,7 +18890,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18916,13 +18920,13 @@
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357206</t>
+          <t>https://artportalen.se/Sighting/135357205</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>135357213</v>
+        <v>135357206</v>
       </c>
       <c r="B158" t="n">
         <v>101375</v>
@@ -18957,10 +18961,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>598501</v>
+        <v>598521</v>
       </c>
       <c r="R158" t="n">
-        <v>7330475</v>
+        <v>7330581</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18992,7 +18996,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -19002,7 +19006,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19032,13 +19036,13 @@
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357213</t>
+          <t>https://artportalen.se/Sighting/135357206</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>135358268</v>
+        <v>135357213</v>
       </c>
       <c r="B159" t="n">
         <v>101375</v>
@@ -19069,17 +19073,17 @@
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>598580</v>
+        <v>598501</v>
       </c>
       <c r="R159" t="n">
-        <v>7330339</v>
+        <v>7330475</v>
       </c>
       <c r="S159" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -19108,7 +19112,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -19118,7 +19122,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19133,12 +19137,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -19148,13 +19152,13 @@
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358268</t>
+          <t>https://artportalen.se/Sighting/135357213</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>135358284</v>
+        <v>135358268</v>
       </c>
       <c r="B160" t="n">
         <v>101375</v>
@@ -19189,10 +19193,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>598610</v>
+        <v>598580</v>
       </c>
       <c r="R160" t="n">
-        <v>7330295</v>
+        <v>7330339</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -19224,7 +19228,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -19234,7 +19238,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -19264,13 +19268,13 @@
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358284</t>
+          <t>https://artportalen.se/Sighting/135358268</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>135358293</v>
+        <v>135358284</v>
       </c>
       <c r="B161" t="n">
         <v>101375</v>
@@ -19305,10 +19309,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>598830</v>
+        <v>598610</v>
       </c>
       <c r="R161" t="n">
-        <v>7330303</v>
+        <v>7330295</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -19340,7 +19344,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19350,7 +19354,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19380,13 +19384,13 @@
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358293</t>
+          <t>https://artportalen.se/Sighting/135358284</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>135358341</v>
+        <v>135358293</v>
       </c>
       <c r="B162" t="n">
         <v>101375</v>
@@ -19421,10 +19425,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>598546</v>
+        <v>598830</v>
       </c>
       <c r="R162" t="n">
-        <v>7330653</v>
+        <v>7330303</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -19456,7 +19460,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -19466,7 +19470,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19496,13 +19500,13 @@
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358341</t>
+          <t>https://artportalen.se/Sighting/135358293</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>135382388</v>
+        <v>135358341</v>
       </c>
       <c r="B163" t="n">
         <v>101375</v>
@@ -19533,14 +19537,14 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>598483</v>
+        <v>598546</v>
       </c>
       <c r="R163" t="n">
-        <v>7330403</v>
+        <v>7330653</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -19567,22 +19571,22 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19597,12 +19601,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -19612,13 +19616,13 @@
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382388</t>
+          <t>https://artportalen.se/Sighting/135358341</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>135382712</v>
+        <v>135382388</v>
       </c>
       <c r="B164" t="n">
         <v>101375</v>
@@ -19649,17 +19653,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>598464</v>
+        <v>598483</v>
       </c>
       <c r="R164" t="n">
-        <v>7330416</v>
+        <v>7330403</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -19713,12 +19717,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -19728,13 +19732,13 @@
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382712</t>
+          <t>https://artportalen.se/Sighting/135382388</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>135382717</v>
+        <v>135382712</v>
       </c>
       <c r="B165" t="n">
         <v>101375</v>
@@ -19769,10 +19773,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>598507</v>
+        <v>598464</v>
       </c>
       <c r="R165" t="n">
-        <v>7330626</v>
+        <v>7330416</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19804,7 +19808,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -19814,7 +19818,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19844,13 +19848,13 @@
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382717</t>
+          <t>https://artportalen.se/Sighting/135382712</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>135382722</v>
+        <v>135382717</v>
       </c>
       <c r="B166" t="n">
         <v>101375</v>
@@ -19885,10 +19889,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>598467</v>
+        <v>598507</v>
       </c>
       <c r="R166" t="n">
-        <v>7330649</v>
+        <v>7330626</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19920,7 +19924,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19930,7 +19934,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19960,16 +19964,16 @@
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382722</t>
+          <t>https://artportalen.se/Sighting/135382717</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>135357130</v>
+        <v>135382722</v>
       </c>
       <c r="B167" t="n">
-        <v>102051</v>
+        <v>101375</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19977,34 +19981,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>225188</v>
+        <v>224885</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vanliga skogsvinbär</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Ribes spicatum subsp. spicatum</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr"/>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
       <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>598613</v>
+        <v>598467</v>
       </c>
       <c r="R167" t="n">
-        <v>7330353</v>
+        <v>7330649</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20031,22 +20035,22 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -20055,7 +20059,6 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -20077,54 +20080,54 @@
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357130</t>
+          <t>https://artportalen.se/Sighting/135382722</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>135356852</v>
+        <v>135357130</v>
       </c>
       <c r="B168" t="n">
-        <v>92442</v>
+        <v>102051</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6040186</v>
+        <v>225188</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vanliga skogsvinbär</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
+          <t>Ribes spicatum subsp. spicatum</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>598735</v>
+        <v>598613</v>
       </c>
       <c r="R168" t="n">
-        <v>7330341</v>
+        <v>7330353</v>
       </c>
       <c r="S168" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -20153,7 +20156,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -20163,7 +20166,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -20179,12 +20182,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -20194,13 +20197,13 @@
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356852</t>
+          <t>https://artportalen.se/Sighting/135357130</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>135357134</v>
+        <v>135356852</v>
       </c>
       <c r="B169" t="n">
         <v>92442</v>
@@ -20231,17 +20234,17 @@
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>598723</v>
+        <v>598735</v>
       </c>
       <c r="R169" t="n">
-        <v>7330305</v>
+        <v>7330341</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -20270,7 +20273,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -20280,7 +20283,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20296,20 +20299,137 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356852</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>135357134</v>
+      </c>
+      <c r="B170" t="n">
+        <v>92442</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>598723</v>
+      </c>
+      <c r="R170" t="n">
+        <v>7330305</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AX169" t="inlineStr">
+      <c r="AX170" t="inlineStr">
         <is>
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY169" t="inlineStr">
+      <c r="AY170" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
-      <c r="AZ169" t="inlineStr">
+      <c r="AZ170" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135357134</t>
         </is>
@@ -20485,6 +20605,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -7575,7 +7575,7 @@
         <v>135358275</v>
       </c>
       <c r="B61" t="n">
-        <v>87701</v>
+        <v>87702</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -7575,7 +7575,7 @@
         <v>135358275</v>
       </c>
       <c r="B61" t="n">
-        <v>87702</v>
+        <v>87708</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -7575,7 +7575,7 @@
         <v>135358275</v>
       </c>
       <c r="B61" t="n">
-        <v>87708</v>
+        <v>87709</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -7575,7 +7575,7 @@
         <v>135358275</v>
       </c>
       <c r="B61" t="n">
-        <v>87709</v>
+        <v>87715</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -7575,7 +7575,7 @@
         <v>135358275</v>
       </c>
       <c r="B61" t="n">
-        <v>87715</v>
+        <v>87722</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -7575,7 +7575,7 @@
         <v>135358275</v>
       </c>
       <c r="B61" t="n">
-        <v>87722</v>
+        <v>87735</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 73880-2021 artfynd.xlsx
+++ b/artfynd/A 73880-2021 artfynd.xlsx
@@ -7575,7 +7575,7 @@
         <v>135358275</v>
       </c>
       <c r="B61" t="n">
-        <v>87735</v>
+        <v>87736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
